--- a/2024年_スキル検索モデル（仮）/04.テーブル設計/テーブル定義.xlsx
+++ b/2024年_スキル検索モデル（仮）/04.テーブル設計/テーブル定義.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/beaming-boy/growth/プロジェクト/ドキュメント共有フォルダ/2024年_スキル検索モデル（仮）/04.テーブル設計/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1884A038-2B68-6543-87B8-441BEDD847C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8999FCCA-5DD2-6F4E-BCCC-B039DDC947C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-33600" yWindow="500" windowWidth="33600" windowHeight="19840" activeTab="3" xr2:uid="{3C8D862C-6145-E842-B259-880AA5F992AF}"/>
+    <workbookView xWindow="-72000" yWindow="500" windowWidth="38400" windowHeight="21100" activeTab="3" xr2:uid="{3C8D862C-6145-E842-B259-880AA5F992AF}"/>
   </bookViews>
   <sheets>
     <sheet name="改訂履歴" sheetId="3" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="76">
   <si>
     <t>No.</t>
     <phoneticPr fontId="1"/>
@@ -379,10 +379,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>no</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>age</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -502,6 +498,24 @@
   </si>
   <si>
     <t>-</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>経験言語</t>
+    <rPh sb="0" eb="2">
+      <t>ケイケｎン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ゲンｇオ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">coding_languages </t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>engineer_id</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -798,7 +812,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="116">
+  <cellXfs count="115">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -925,6 +939,18 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -997,6 +1023,24 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1027,124 +1071,91 @@
     <xf numFmtId="0" fontId="11" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1200,7 +1211,7 @@
               <a:picLocks noChangeAspect="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="ヘッダー!A1:AY3" spid="_x0000_s3365"/>
+                  <a14:cameraTool cellRange="ヘッダー!A1:AY3" spid="_x0000_s3372"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -1259,7 +1270,7 @@
               <a:picLocks noChangeAspect="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="ヘッダー!A1:AY3" spid="_x0000_s7370"/>
+                  <a14:cameraTool cellRange="ヘッダー!A1:AY3" spid="_x0000_s7377"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -1677,13 +1688,13 @@
       <c r="D8" s="4"/>
       <c r="E8" s="4"/>
       <c r="F8" s="5"/>
-      <c r="G8" s="114">
+      <c r="G8" s="43">
         <v>45459</v>
       </c>
-      <c r="H8" s="113"/>
-      <c r="I8" s="113"/>
-      <c r="J8" s="113"/>
-      <c r="K8" s="115"/>
+      <c r="H8" s="44"/>
+      <c r="I8" s="44"/>
+      <c r="J8" s="44"/>
+      <c r="K8" s="45"/>
       <c r="L8" s="11" t="s">
         <v>45</v>
       </c>
@@ -1716,7 +1727,7 @@
       <c r="AK8" s="4"/>
       <c r="AL8" s="5"/>
       <c r="AM8" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AN8" s="4"/>
       <c r="AO8" s="4"/>
@@ -3292,187 +3303,187 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="3.33203125" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:54" ht="15" customHeight="1">
-      <c r="A1" s="57" t="s">
+      <c r="A1" s="61" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="58"/>
-      <c r="C1" s="58"/>
-      <c r="D1" s="58"/>
-      <c r="E1" s="59"/>
-      <c r="F1" s="42" t="s">
+      <c r="B1" s="62"/>
+      <c r="C1" s="62"/>
+      <c r="D1" s="62"/>
+      <c r="E1" s="63"/>
+      <c r="F1" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="G1" s="43"/>
-      <c r="H1" s="43"/>
-      <c r="I1" s="43"/>
-      <c r="J1" s="44"/>
-      <c r="K1" s="42" t="s">
+      <c r="G1" s="47"/>
+      <c r="H1" s="47"/>
+      <c r="I1" s="47"/>
+      <c r="J1" s="48"/>
+      <c r="K1" s="46" t="s">
         <v>2</v>
       </c>
-      <c r="L1" s="43"/>
-      <c r="M1" s="43"/>
-      <c r="N1" s="43"/>
-      <c r="O1" s="43"/>
-      <c r="P1" s="43"/>
-      <c r="Q1" s="43"/>
-      <c r="R1" s="43"/>
-      <c r="S1" s="43"/>
-      <c r="T1" s="43"/>
-      <c r="U1" s="43"/>
-      <c r="V1" s="43"/>
-      <c r="W1" s="43"/>
-      <c r="X1" s="43"/>
-      <c r="Y1" s="43"/>
-      <c r="Z1" s="43"/>
-      <c r="AA1" s="43"/>
-      <c r="AB1" s="43"/>
-      <c r="AC1" s="43"/>
-      <c r="AD1" s="43"/>
-      <c r="AE1" s="44"/>
-      <c r="AF1" s="42" t="s">
+      <c r="L1" s="47"/>
+      <c r="M1" s="47"/>
+      <c r="N1" s="47"/>
+      <c r="O1" s="47"/>
+      <c r="P1" s="47"/>
+      <c r="Q1" s="47"/>
+      <c r="R1" s="47"/>
+      <c r="S1" s="47"/>
+      <c r="T1" s="47"/>
+      <c r="U1" s="47"/>
+      <c r="V1" s="47"/>
+      <c r="W1" s="47"/>
+      <c r="X1" s="47"/>
+      <c r="Y1" s="47"/>
+      <c r="Z1" s="47"/>
+      <c r="AA1" s="47"/>
+      <c r="AB1" s="47"/>
+      <c r="AC1" s="47"/>
+      <c r="AD1" s="47"/>
+      <c r="AE1" s="48"/>
+      <c r="AF1" s="46" t="s">
         <v>3</v>
       </c>
-      <c r="AG1" s="43"/>
-      <c r="AH1" s="43"/>
-      <c r="AI1" s="43"/>
-      <c r="AJ1" s="44"/>
-      <c r="AK1" s="42" t="s">
+      <c r="AG1" s="47"/>
+      <c r="AH1" s="47"/>
+      <c r="AI1" s="47"/>
+      <c r="AJ1" s="48"/>
+      <c r="AK1" s="46" t="s">
         <v>4</v>
       </c>
-      <c r="AL1" s="43"/>
-      <c r="AM1" s="43"/>
-      <c r="AN1" s="43"/>
-      <c r="AO1" s="44"/>
-      <c r="AP1" s="42" t="s">
+      <c r="AL1" s="47"/>
+      <c r="AM1" s="47"/>
+      <c r="AN1" s="47"/>
+      <c r="AO1" s="48"/>
+      <c r="AP1" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="AQ1" s="43"/>
-      <c r="AR1" s="43"/>
-      <c r="AS1" s="43"/>
-      <c r="AT1" s="44"/>
-      <c r="AU1" s="42" t="s">
+      <c r="AQ1" s="47"/>
+      <c r="AR1" s="47"/>
+      <c r="AS1" s="47"/>
+      <c r="AT1" s="48"/>
+      <c r="AU1" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="AV1" s="43"/>
-      <c r="AW1" s="43"/>
-      <c r="AX1" s="43"/>
-      <c r="AY1" s="44"/>
+      <c r="AV1" s="47"/>
+      <c r="AW1" s="47"/>
+      <c r="AX1" s="47"/>
+      <c r="AY1" s="48"/>
       <c r="BB1" s="2"/>
     </row>
     <row r="2" spans="1:54" ht="15" customHeight="1">
-      <c r="A2" s="60"/>
-      <c r="B2" s="61"/>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
-      <c r="E2" s="62"/>
-      <c r="F2" s="102" t="s">
+      <c r="A2" s="64"/>
+      <c r="B2" s="65"/>
+      <c r="C2" s="65"/>
+      <c r="D2" s="65"/>
+      <c r="E2" s="66"/>
+      <c r="F2" s="70" t="s">
         <v>44</v>
       </c>
-      <c r="G2" s="103"/>
-      <c r="H2" s="103"/>
-      <c r="I2" s="103"/>
-      <c r="J2" s="104"/>
-      <c r="K2" s="45" t="s">
+      <c r="G2" s="71"/>
+      <c r="H2" s="71"/>
+      <c r="I2" s="71"/>
+      <c r="J2" s="72"/>
+      <c r="K2" s="49" t="s">
         <v>18</v>
       </c>
-      <c r="L2" s="46"/>
-      <c r="M2" s="46"/>
-      <c r="N2" s="46"/>
-      <c r="O2" s="46"/>
-      <c r="P2" s="46"/>
-      <c r="Q2" s="46"/>
-      <c r="R2" s="46"/>
-      <c r="S2" s="46"/>
-      <c r="T2" s="46"/>
-      <c r="U2" s="46"/>
-      <c r="V2" s="46"/>
-      <c r="W2" s="46"/>
-      <c r="X2" s="46"/>
-      <c r="Y2" s="46"/>
-      <c r="Z2" s="46"/>
-      <c r="AA2" s="46"/>
-      <c r="AB2" s="46"/>
-      <c r="AC2" s="46"/>
-      <c r="AD2" s="46"/>
-      <c r="AE2" s="47"/>
-      <c r="AF2" s="51">
+      <c r="L2" s="50"/>
+      <c r="M2" s="50"/>
+      <c r="N2" s="50"/>
+      <c r="O2" s="50"/>
+      <c r="P2" s="50"/>
+      <c r="Q2" s="50"/>
+      <c r="R2" s="50"/>
+      <c r="S2" s="50"/>
+      <c r="T2" s="50"/>
+      <c r="U2" s="50"/>
+      <c r="V2" s="50"/>
+      <c r="W2" s="50"/>
+      <c r="X2" s="50"/>
+      <c r="Y2" s="50"/>
+      <c r="Z2" s="50"/>
+      <c r="AA2" s="50"/>
+      <c r="AB2" s="50"/>
+      <c r="AC2" s="50"/>
+      <c r="AD2" s="50"/>
+      <c r="AE2" s="51"/>
+      <c r="AF2" s="55">
         <v>45459</v>
       </c>
-      <c r="AG2" s="52"/>
-      <c r="AH2" s="52"/>
-      <c r="AI2" s="52"/>
-      <c r="AJ2" s="53"/>
-      <c r="AK2" s="45" t="s">
+      <c r="AG2" s="56"/>
+      <c r="AH2" s="56"/>
+      <c r="AI2" s="56"/>
+      <c r="AJ2" s="57"/>
+      <c r="AK2" s="49" t="s">
         <v>45</v>
       </c>
-      <c r="AL2" s="46"/>
-      <c r="AM2" s="46"/>
-      <c r="AN2" s="46"/>
-      <c r="AO2" s="47"/>
-      <c r="AP2" s="51"/>
-      <c r="AQ2" s="52"/>
-      <c r="AR2" s="52"/>
-      <c r="AS2" s="52"/>
-      <c r="AT2" s="53"/>
-      <c r="AU2" s="45"/>
-      <c r="AV2" s="46"/>
-      <c r="AW2" s="46"/>
-      <c r="AX2" s="46"/>
-      <c r="AY2" s="47"/>
+      <c r="AL2" s="50"/>
+      <c r="AM2" s="50"/>
+      <c r="AN2" s="50"/>
+      <c r="AO2" s="51"/>
+      <c r="AP2" s="55"/>
+      <c r="AQ2" s="56"/>
+      <c r="AR2" s="56"/>
+      <c r="AS2" s="56"/>
+      <c r="AT2" s="57"/>
+      <c r="AU2" s="49"/>
+      <c r="AV2" s="50"/>
+      <c r="AW2" s="50"/>
+      <c r="AX2" s="50"/>
+      <c r="AY2" s="51"/>
       <c r="BB2" s="2"/>
     </row>
     <row r="3" spans="1:54" ht="15" customHeight="1">
-      <c r="A3" s="63"/>
-      <c r="B3" s="64"/>
-      <c r="C3" s="64"/>
-      <c r="D3" s="64"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="105"/>
-      <c r="G3" s="106"/>
-      <c r="H3" s="106"/>
-      <c r="I3" s="106"/>
-      <c r="J3" s="107"/>
-      <c r="K3" s="48"/>
-      <c r="L3" s="49"/>
-      <c r="M3" s="49"/>
-      <c r="N3" s="49"/>
-      <c r="O3" s="49"/>
-      <c r="P3" s="49"/>
-      <c r="Q3" s="49"/>
-      <c r="R3" s="49"/>
-      <c r="S3" s="49"/>
-      <c r="T3" s="49"/>
-      <c r="U3" s="49"/>
-      <c r="V3" s="49"/>
-      <c r="W3" s="49"/>
-      <c r="X3" s="49"/>
-      <c r="Y3" s="49"/>
-      <c r="Z3" s="49"/>
-      <c r="AA3" s="49"/>
-      <c r="AB3" s="49"/>
-      <c r="AC3" s="49"/>
-      <c r="AD3" s="49"/>
-      <c r="AE3" s="50"/>
-      <c r="AF3" s="54"/>
-      <c r="AG3" s="55"/>
-      <c r="AH3" s="55"/>
-      <c r="AI3" s="55"/>
-      <c r="AJ3" s="56"/>
-      <c r="AK3" s="48"/>
-      <c r="AL3" s="49"/>
-      <c r="AM3" s="49"/>
-      <c r="AN3" s="49"/>
-      <c r="AO3" s="50"/>
-      <c r="AP3" s="54"/>
-      <c r="AQ3" s="55"/>
-      <c r="AR3" s="55"/>
-      <c r="AS3" s="55"/>
-      <c r="AT3" s="56"/>
-      <c r="AU3" s="48"/>
-      <c r="AV3" s="49"/>
-      <c r="AW3" s="49"/>
-      <c r="AX3" s="49"/>
-      <c r="AY3" s="50"/>
+      <c r="A3" s="67"/>
+      <c r="B3" s="68"/>
+      <c r="C3" s="68"/>
+      <c r="D3" s="68"/>
+      <c r="E3" s="69"/>
+      <c r="F3" s="73"/>
+      <c r="G3" s="74"/>
+      <c r="H3" s="74"/>
+      <c r="I3" s="74"/>
+      <c r="J3" s="75"/>
+      <c r="K3" s="52"/>
+      <c r="L3" s="53"/>
+      <c r="M3" s="53"/>
+      <c r="N3" s="53"/>
+      <c r="O3" s="53"/>
+      <c r="P3" s="53"/>
+      <c r="Q3" s="53"/>
+      <c r="R3" s="53"/>
+      <c r="S3" s="53"/>
+      <c r="T3" s="53"/>
+      <c r="U3" s="53"/>
+      <c r="V3" s="53"/>
+      <c r="W3" s="53"/>
+      <c r="X3" s="53"/>
+      <c r="Y3" s="53"/>
+      <c r="Z3" s="53"/>
+      <c r="AA3" s="53"/>
+      <c r="AB3" s="53"/>
+      <c r="AC3" s="53"/>
+      <c r="AD3" s="53"/>
+      <c r="AE3" s="54"/>
+      <c r="AF3" s="58"/>
+      <c r="AG3" s="59"/>
+      <c r="AH3" s="59"/>
+      <c r="AI3" s="59"/>
+      <c r="AJ3" s="60"/>
+      <c r="AK3" s="52"/>
+      <c r="AL3" s="53"/>
+      <c r="AM3" s="53"/>
+      <c r="AN3" s="53"/>
+      <c r="AO3" s="54"/>
+      <c r="AP3" s="58"/>
+      <c r="AQ3" s="59"/>
+      <c r="AR3" s="59"/>
+      <c r="AS3" s="59"/>
+      <c r="AT3" s="60"/>
+      <c r="AU3" s="52"/>
+      <c r="AV3" s="53"/>
+      <c r="AW3" s="53"/>
+      <c r="AX3" s="53"/>
+      <c r="AY3" s="54"/>
       <c r="BB3" s="2"/>
     </row>
     <row r="4" spans="1:54" ht="15" customHeight="1">
@@ -3584,92 +3595,92 @@
       <c r="A6" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="66" t="s">
+      <c r="B6" s="76" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="73" t="s">
+      <c r="C6" s="83" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="73" t="s">
+      <c r="D6" s="83" t="s">
         <v>15</v>
       </c>
-      <c r="E6" s="73" t="s">
+      <c r="E6" s="83" t="s">
         <v>15</v>
       </c>
-      <c r="F6" s="73" t="s">
+      <c r="F6" s="83" t="s">
         <v>15</v>
       </c>
-      <c r="G6" s="73" t="s">
+      <c r="G6" s="83" t="s">
         <v>15</v>
       </c>
-      <c r="H6" s="67" t="s">
+      <c r="H6" s="77" t="s">
         <v>15</v>
       </c>
-      <c r="I6" s="74" t="s">
+      <c r="I6" s="84" t="s">
         <v>21</v>
       </c>
-      <c r="J6" s="75" t="s">
+      <c r="J6" s="85" t="s">
         <v>16</v>
       </c>
-      <c r="K6" s="75" t="s">
+      <c r="K6" s="85" t="s">
         <v>16</v>
       </c>
-      <c r="L6" s="75" t="s">
+      <c r="L6" s="85" t="s">
         <v>16</v>
       </c>
-      <c r="M6" s="75" t="s">
+      <c r="M6" s="85" t="s">
         <v>16</v>
       </c>
-      <c r="N6" s="75" t="s">
+      <c r="N6" s="85" t="s">
         <v>16</v>
       </c>
-      <c r="O6" s="75" t="s">
+      <c r="O6" s="85" t="s">
         <v>16</v>
       </c>
-      <c r="P6" s="75" t="s">
+      <c r="P6" s="85" t="s">
         <v>16</v>
       </c>
-      <c r="Q6" s="66" t="s">
+      <c r="Q6" s="76" t="s">
         <v>22</v>
       </c>
-      <c r="R6" s="67"/>
-      <c r="S6" s="68" t="s">
+      <c r="R6" s="77"/>
+      <c r="S6" s="78" t="s">
         <v>24</v>
       </c>
-      <c r="T6" s="69"/>
-      <c r="U6" s="69"/>
-      <c r="V6" s="69"/>
-      <c r="W6" s="69"/>
-      <c r="X6" s="69"/>
-      <c r="Y6" s="69"/>
-      <c r="Z6" s="69"/>
-      <c r="AA6" s="69"/>
-      <c r="AB6" s="69"/>
-      <c r="AC6" s="69"/>
-      <c r="AD6" s="69"/>
-      <c r="AE6" s="69"/>
-      <c r="AF6" s="69"/>
-      <c r="AG6" s="69"/>
-      <c r="AH6" s="69"/>
-      <c r="AI6" s="69"/>
-      <c r="AJ6" s="69"/>
-      <c r="AK6" s="69"/>
-      <c r="AL6" s="69"/>
-      <c r="AM6" s="69"/>
-      <c r="AN6" s="69"/>
-      <c r="AO6" s="69"/>
-      <c r="AP6" s="70"/>
-      <c r="AQ6" s="66" t="s">
+      <c r="T6" s="79"/>
+      <c r="U6" s="79"/>
+      <c r="V6" s="79"/>
+      <c r="W6" s="79"/>
+      <c r="X6" s="79"/>
+      <c r="Y6" s="79"/>
+      <c r="Z6" s="79"/>
+      <c r="AA6" s="79"/>
+      <c r="AB6" s="79"/>
+      <c r="AC6" s="79"/>
+      <c r="AD6" s="79"/>
+      <c r="AE6" s="79"/>
+      <c r="AF6" s="79"/>
+      <c r="AG6" s="79"/>
+      <c r="AH6" s="79"/>
+      <c r="AI6" s="79"/>
+      <c r="AJ6" s="79"/>
+      <c r="AK6" s="79"/>
+      <c r="AL6" s="79"/>
+      <c r="AM6" s="79"/>
+      <c r="AN6" s="79"/>
+      <c r="AO6" s="79"/>
+      <c r="AP6" s="80"/>
+      <c r="AQ6" s="76" t="s">
         <v>14</v>
       </c>
-      <c r="AR6" s="73"/>
-      <c r="AS6" s="73"/>
-      <c r="AT6" s="73"/>
-      <c r="AU6" s="73"/>
-      <c r="AV6" s="73"/>
-      <c r="AW6" s="73"/>
-      <c r="AX6" s="73"/>
-      <c r="AY6" s="67"/>
+      <c r="AR6" s="83"/>
+      <c r="AS6" s="83"/>
+      <c r="AT6" s="83"/>
+      <c r="AU6" s="83"/>
+      <c r="AV6" s="83"/>
+      <c r="AW6" s="83"/>
+      <c r="AX6" s="83"/>
+      <c r="AY6" s="77"/>
     </row>
     <row r="7" spans="1:53" ht="17" customHeight="1">
       <c r="A7" s="34">
@@ -3695,10 +3706,10 @@
       <c r="N7" s="35"/>
       <c r="O7" s="35"/>
       <c r="P7" s="36"/>
-      <c r="Q7" s="71" t="s">
+      <c r="Q7" s="81" t="s">
         <v>47</v>
       </c>
-      <c r="R7" s="72"/>
+      <c r="R7" s="82"/>
       <c r="S7" s="35" t="s">
         <v>48</v>
       </c>
@@ -4724,76 +4735,76 @@
       </c>
     </row>
     <row r="2" spans="1:55">
-      <c r="B2" s="66" t="s">
+      <c r="B2" s="76" t="s">
         <v>27</v>
       </c>
-      <c r="C2" s="73" t="s">
+      <c r="C2" s="83" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="73" t="s">
+      <c r="D2" s="83" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="73" t="s">
+      <c r="E2" s="83" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="73" t="s">
+      <c r="F2" s="83" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="67" t="s">
+      <c r="G2" s="77" t="s">
         <v>15</v>
       </c>
-      <c r="H2" s="108">
+      <c r="H2" s="86">
         <v>45459</v>
       </c>
-      <c r="I2" s="88"/>
-      <c r="J2" s="88"/>
-      <c r="K2" s="88"/>
-      <c r="L2" s="88"/>
-      <c r="M2" s="89"/>
-      <c r="N2" s="66" t="s">
+      <c r="I2" s="87"/>
+      <c r="J2" s="87"/>
+      <c r="K2" s="87"/>
+      <c r="L2" s="87"/>
+      <c r="M2" s="88"/>
+      <c r="N2" s="76" t="s">
         <v>26</v>
       </c>
-      <c r="O2" s="73" t="s">
+      <c r="O2" s="83" t="s">
         <v>15</v>
       </c>
-      <c r="P2" s="73" t="s">
+      <c r="P2" s="83" t="s">
         <v>15</v>
       </c>
-      <c r="Q2" s="73" t="s">
+      <c r="Q2" s="83" t="s">
         <v>15</v>
       </c>
-      <c r="R2" s="73" t="s">
+      <c r="R2" s="83" t="s">
         <v>15</v>
       </c>
-      <c r="S2" s="67" t="s">
+      <c r="S2" s="77" t="s">
         <v>15</v>
       </c>
-      <c r="T2" s="87" t="s">
+      <c r="T2" s="89" t="s">
         <v>45</v>
       </c>
-      <c r="U2" s="88"/>
-      <c r="V2" s="88"/>
-      <c r="W2" s="88"/>
-      <c r="X2" s="88"/>
-      <c r="Y2" s="89"/>
+      <c r="U2" s="87"/>
+      <c r="V2" s="87"/>
+      <c r="W2" s="87"/>
+      <c r="X2" s="87"/>
+      <c r="Y2" s="88"/>
     </row>
     <row r="3" spans="1:55">
-      <c r="B3" s="74" t="s">
+      <c r="B3" s="84" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="75" t="s">
+      <c r="C3" s="85" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="75" t="s">
+      <c r="D3" s="85" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="75" t="s">
+      <c r="E3" s="85" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="75" t="s">
+      <c r="F3" s="85" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="75" t="s">
+      <c r="G3" s="85" t="s">
         <v>16</v>
       </c>
       <c r="H3" s="90"/>
@@ -4802,22 +4813,22 @@
       <c r="K3" s="91"/>
       <c r="L3" s="91"/>
       <c r="M3" s="91"/>
-      <c r="N3" s="74" t="s">
+      <c r="N3" s="84" t="s">
         <v>29</v>
       </c>
-      <c r="O3" s="75" t="s">
+      <c r="O3" s="85" t="s">
         <v>16</v>
       </c>
-      <c r="P3" s="75" t="s">
+      <c r="P3" s="85" t="s">
         <v>16</v>
       </c>
-      <c r="Q3" s="75" t="s">
+      <c r="Q3" s="85" t="s">
         <v>16</v>
       </c>
-      <c r="R3" s="75" t="s">
+      <c r="R3" s="85" t="s">
         <v>16</v>
       </c>
-      <c r="S3" s="75" t="s">
+      <c r="S3" s="85" t="s">
         <v>16</v>
       </c>
       <c r="T3" s="90"/>
@@ -4869,22 +4880,22 @@
       <c r="Y4" s="21"/>
     </row>
     <row r="5" spans="1:55">
-      <c r="B5" s="74" t="s">
+      <c r="B5" s="84" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="75" t="s">
+      <c r="C5" s="85" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="75" t="s">
+      <c r="D5" s="85" t="s">
         <v>16</v>
       </c>
-      <c r="E5" s="75" t="s">
+      <c r="E5" s="85" t="s">
         <v>16</v>
       </c>
-      <c r="F5" s="75" t="s">
+      <c r="F5" s="85" t="s">
         <v>16</v>
       </c>
-      <c r="G5" s="75" t="s">
+      <c r="G5" s="85" t="s">
         <v>16</v>
       </c>
       <c r="H5" s="22" t="str">
@@ -4910,34 +4921,34 @@
       <c r="Y5" s="24"/>
     </row>
     <row r="6" spans="1:55">
-      <c r="B6" s="66" t="s">
+      <c r="B6" s="76" t="s">
         <v>30</v>
       </c>
-      <c r="C6" s="73"/>
-      <c r="D6" s="73"/>
-      <c r="E6" s="73"/>
-      <c r="F6" s="73"/>
-      <c r="G6" s="67"/>
-      <c r="H6" s="78" t="s">
+      <c r="C6" s="83"/>
+      <c r="D6" s="83"/>
+      <c r="E6" s="83"/>
+      <c r="F6" s="83"/>
+      <c r="G6" s="77"/>
+      <c r="H6" s="102" t="s">
         <v>50</v>
       </c>
-      <c r="I6" s="79"/>
-      <c r="J6" s="79"/>
-      <c r="K6" s="79"/>
-      <c r="L6" s="79"/>
-      <c r="M6" s="79"/>
-      <c r="N6" s="79"/>
-      <c r="O6" s="79"/>
-      <c r="P6" s="79"/>
-      <c r="Q6" s="79"/>
-      <c r="R6" s="79"/>
-      <c r="S6" s="79"/>
-      <c r="T6" s="79"/>
-      <c r="U6" s="79"/>
-      <c r="V6" s="79"/>
-      <c r="W6" s="79"/>
-      <c r="X6" s="79"/>
-      <c r="Y6" s="80"/>
+      <c r="I6" s="103"/>
+      <c r="J6" s="103"/>
+      <c r="K6" s="103"/>
+      <c r="L6" s="103"/>
+      <c r="M6" s="103"/>
+      <c r="N6" s="103"/>
+      <c r="O6" s="103"/>
+      <c r="P6" s="103"/>
+      <c r="Q6" s="103"/>
+      <c r="R6" s="103"/>
+      <c r="S6" s="103"/>
+      <c r="T6" s="103"/>
+      <c r="U6" s="103"/>
+      <c r="V6" s="103"/>
+      <c r="W6" s="103"/>
+      <c r="X6" s="103"/>
+      <c r="Y6" s="104"/>
     </row>
     <row r="7" spans="1:55">
       <c r="B7" s="96"/>
@@ -4946,24 +4957,24 @@
       <c r="E7" s="97"/>
       <c r="F7" s="97"/>
       <c r="G7" s="98"/>
-      <c r="H7" s="81"/>
-      <c r="I7" s="82"/>
-      <c r="J7" s="82"/>
-      <c r="K7" s="82"/>
-      <c r="L7" s="82"/>
-      <c r="M7" s="82"/>
-      <c r="N7" s="82"/>
-      <c r="O7" s="82"/>
-      <c r="P7" s="82"/>
-      <c r="Q7" s="82"/>
-      <c r="R7" s="82"/>
-      <c r="S7" s="82"/>
-      <c r="T7" s="82"/>
-      <c r="U7" s="82"/>
-      <c r="V7" s="82"/>
-      <c r="W7" s="82"/>
-      <c r="X7" s="82"/>
-      <c r="Y7" s="83"/>
+      <c r="H7" s="105"/>
+      <c r="I7" s="106"/>
+      <c r="J7" s="106"/>
+      <c r="K7" s="106"/>
+      <c r="L7" s="106"/>
+      <c r="M7" s="106"/>
+      <c r="N7" s="106"/>
+      <c r="O7" s="106"/>
+      <c r="P7" s="106"/>
+      <c r="Q7" s="106"/>
+      <c r="R7" s="106"/>
+      <c r="S7" s="106"/>
+      <c r="T7" s="106"/>
+      <c r="U7" s="106"/>
+      <c r="V7" s="106"/>
+      <c r="W7" s="106"/>
+      <c r="X7" s="106"/>
+      <c r="Y7" s="107"/>
     </row>
     <row r="8" spans="1:55">
       <c r="B8" s="99"/>
@@ -4972,24 +4983,24 @@
       <c r="E8" s="100"/>
       <c r="F8" s="100"/>
       <c r="G8" s="101"/>
-      <c r="H8" s="84"/>
-      <c r="I8" s="85"/>
-      <c r="J8" s="85"/>
-      <c r="K8" s="85"/>
-      <c r="L8" s="85"/>
-      <c r="M8" s="85"/>
-      <c r="N8" s="85"/>
-      <c r="O8" s="85"/>
-      <c r="P8" s="85"/>
-      <c r="Q8" s="85"/>
-      <c r="R8" s="85"/>
-      <c r="S8" s="85"/>
-      <c r="T8" s="85"/>
-      <c r="U8" s="85"/>
-      <c r="V8" s="85"/>
-      <c r="W8" s="85"/>
-      <c r="X8" s="85"/>
-      <c r="Y8" s="86"/>
+      <c r="H8" s="108"/>
+      <c r="I8" s="109"/>
+      <c r="J8" s="109"/>
+      <c r="K8" s="109"/>
+      <c r="L8" s="109"/>
+      <c r="M8" s="109"/>
+      <c r="N8" s="109"/>
+      <c r="O8" s="109"/>
+      <c r="P8" s="109"/>
+      <c r="Q8" s="109"/>
+      <c r="R8" s="109"/>
+      <c r="S8" s="109"/>
+      <c r="T8" s="109"/>
+      <c r="U8" s="109"/>
+      <c r="V8" s="109"/>
+      <c r="W8" s="109"/>
+      <c r="X8" s="109"/>
+      <c r="Y8" s="110"/>
     </row>
     <row r="10" spans="1:55" ht="20">
       <c r="A10" s="41" t="s">
@@ -5076,7 +5087,7 @@
         <v>1</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D12" s="20"/>
       <c r="E12" s="20"/>
@@ -5087,7 +5098,7 @@
       <c r="J12" s="20"/>
       <c r="K12" s="21"/>
       <c r="L12" s="19" t="s">
-        <v>51</v>
+        <v>75</v>
       </c>
       <c r="M12" s="20"/>
       <c r="N12" s="20"/>
@@ -5098,34 +5109,34 @@
       <c r="S12" s="20"/>
       <c r="T12" s="21"/>
       <c r="U12" s="19" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="V12" s="20"/>
       <c r="W12" s="20"/>
       <c r="X12" s="20"/>
       <c r="Y12" s="20"/>
       <c r="Z12" s="21"/>
-      <c r="AA12" s="76" t="s">
-        <v>70</v>
-      </c>
-      <c r="AB12" s="77"/>
-      <c r="AC12" s="76" t="s">
-        <v>70</v>
-      </c>
-      <c r="AD12" s="77"/>
-      <c r="AE12" s="76" t="s">
-        <v>70</v>
-      </c>
-      <c r="AF12" s="77"/>
+      <c r="AA12" s="111" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB12" s="112"/>
+      <c r="AC12" s="111" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD12" s="112"/>
+      <c r="AE12" s="111" t="s">
+        <v>69</v>
+      </c>
+      <c r="AF12" s="112"/>
       <c r="AG12" s="19" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AH12" s="20"/>
       <c r="AI12" s="20"/>
       <c r="AJ12" s="20"/>
       <c r="AK12" s="21"/>
       <c r="AL12" s="19" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AM12" s="20"/>
       <c r="AN12" s="20"/>
@@ -5151,7 +5162,7 @@
         <v>2</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D13" s="20"/>
       <c r="E13" s="20"/>
@@ -5162,7 +5173,7 @@
       <c r="J13" s="20"/>
       <c r="K13" s="21"/>
       <c r="L13" s="19" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="M13" s="20"/>
       <c r="N13" s="20"/>
@@ -5173,34 +5184,34 @@
       <c r="S13" s="20"/>
       <c r="T13" s="21"/>
       <c r="U13" s="19" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="V13" s="20"/>
       <c r="W13" s="20"/>
       <c r="X13" s="20"/>
       <c r="Y13" s="20"/>
       <c r="Z13" s="21"/>
-      <c r="AA13" s="76" t="s">
-        <v>71</v>
-      </c>
-      <c r="AB13" s="77"/>
-      <c r="AC13" s="76" t="s">
-        <v>71</v>
-      </c>
-      <c r="AD13" s="77"/>
-      <c r="AE13" s="76" t="s">
+      <c r="AA13" s="111" t="s">
         <v>70</v>
       </c>
-      <c r="AF13" s="77"/>
+      <c r="AB13" s="112"/>
+      <c r="AC13" s="111" t="s">
+        <v>70</v>
+      </c>
+      <c r="AD13" s="112"/>
+      <c r="AE13" s="111" t="s">
+        <v>69</v>
+      </c>
+      <c r="AF13" s="112"/>
       <c r="AG13" s="19" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AH13" s="20"/>
       <c r="AI13" s="20"/>
       <c r="AJ13" s="20"/>
       <c r="AK13" s="21"/>
-      <c r="AL13" s="112" t="s">
-        <v>71</v>
+      <c r="AL13" s="42" t="s">
+        <v>70</v>
       </c>
       <c r="AM13" s="20"/>
       <c r="AN13" s="20"/>
@@ -5226,7 +5237,7 @@
         <v>3</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D14" s="20"/>
       <c r="E14" s="20"/>
@@ -5237,7 +5248,7 @@
       <c r="J14" s="20"/>
       <c r="K14" s="21"/>
       <c r="L14" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="M14" s="20"/>
       <c r="N14" s="20"/>
@@ -5248,34 +5259,34 @@
       <c r="S14" s="20"/>
       <c r="T14" s="21"/>
       <c r="U14" s="19" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="V14" s="20"/>
       <c r="W14" s="20"/>
       <c r="X14" s="20"/>
       <c r="Y14" s="20"/>
       <c r="Z14" s="21"/>
-      <c r="AA14" s="76" t="s">
-        <v>71</v>
-      </c>
-      <c r="AB14" s="77"/>
-      <c r="AC14" s="76" t="s">
-        <v>71</v>
-      </c>
-      <c r="AD14" s="77"/>
-      <c r="AE14" s="76" t="s">
+      <c r="AA14" s="111" t="s">
         <v>70</v>
       </c>
-      <c r="AF14" s="77"/>
+      <c r="AB14" s="112"/>
+      <c r="AC14" s="111" t="s">
+        <v>70</v>
+      </c>
+      <c r="AD14" s="112"/>
+      <c r="AE14" s="111" t="s">
+        <v>69</v>
+      </c>
+      <c r="AF14" s="112"/>
       <c r="AG14" s="19" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AH14" s="20"/>
       <c r="AI14" s="20"/>
       <c r="AJ14" s="20"/>
       <c r="AK14" s="21"/>
-      <c r="AL14" s="112" t="s">
-        <v>71</v>
+      <c r="AL14" s="42" t="s">
+        <v>70</v>
       </c>
       <c r="AM14" s="20"/>
       <c r="AN14" s="20"/>
@@ -5301,7 +5312,7 @@
         <v>4</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D15" s="20"/>
       <c r="E15" s="20"/>
@@ -5312,7 +5323,7 @@
       <c r="J15" s="20"/>
       <c r="K15" s="21"/>
       <c r="L15" s="19" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M15" s="20"/>
       <c r="N15" s="20"/>
@@ -5323,34 +5334,34 @@
       <c r="S15" s="20"/>
       <c r="T15" s="21"/>
       <c r="U15" s="19" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="V15" s="20"/>
       <c r="W15" s="20"/>
       <c r="X15" s="20"/>
       <c r="Y15" s="20"/>
       <c r="Z15" s="21"/>
-      <c r="AA15" s="76" t="s">
-        <v>71</v>
-      </c>
-      <c r="AB15" s="77"/>
-      <c r="AC15" s="76" t="s">
-        <v>71</v>
-      </c>
-      <c r="AD15" s="77"/>
-      <c r="AE15" s="76" t="s">
+      <c r="AA15" s="111" t="s">
         <v>70</v>
       </c>
-      <c r="AF15" s="77"/>
+      <c r="AB15" s="112"/>
+      <c r="AC15" s="111" t="s">
+        <v>70</v>
+      </c>
+      <c r="AD15" s="112"/>
+      <c r="AE15" s="111" t="s">
+        <v>69</v>
+      </c>
+      <c r="AF15" s="112"/>
       <c r="AG15" s="19" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AH15" s="20"/>
       <c r="AI15" s="20"/>
       <c r="AJ15" s="20"/>
       <c r="AK15" s="21"/>
-      <c r="AL15" s="112" t="s">
-        <v>71</v>
+      <c r="AL15" s="42" t="s">
+        <v>70</v>
       </c>
       <c r="AM15" s="20"/>
       <c r="AN15" s="20"/>
@@ -5376,7 +5387,7 @@
         <v>5</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D16" s="20"/>
       <c r="E16" s="20"/>
@@ -5387,7 +5398,7 @@
       <c r="J16" s="20"/>
       <c r="K16" s="21"/>
       <c r="L16" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M16" s="20"/>
       <c r="N16" s="20"/>
@@ -5398,34 +5409,34 @@
       <c r="S16" s="20"/>
       <c r="T16" s="21"/>
       <c r="U16" s="19" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="V16" s="20"/>
       <c r="W16" s="20"/>
       <c r="X16" s="20"/>
       <c r="Y16" s="20"/>
       <c r="Z16" s="21"/>
-      <c r="AA16" s="76" t="s">
-        <v>71</v>
-      </c>
-      <c r="AB16" s="77"/>
-      <c r="AC16" s="76" t="s">
-        <v>71</v>
-      </c>
-      <c r="AD16" s="77"/>
-      <c r="AE16" s="76" t="s">
-        <v>71</v>
-      </c>
-      <c r="AF16" s="77"/>
+      <c r="AA16" s="111" t="s">
+        <v>70</v>
+      </c>
+      <c r="AB16" s="112"/>
+      <c r="AC16" s="111" t="s">
+        <v>70</v>
+      </c>
+      <c r="AD16" s="112"/>
+      <c r="AE16" s="111" t="s">
+        <v>70</v>
+      </c>
+      <c r="AF16" s="112"/>
       <c r="AG16" s="19" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AH16" s="20"/>
       <c r="AI16" s="20"/>
       <c r="AJ16" s="20"/>
       <c r="AK16" s="21"/>
-      <c r="AL16" s="112" t="s">
-        <v>71</v>
+      <c r="AL16" s="42" t="s">
+        <v>70</v>
       </c>
       <c r="AM16" s="20"/>
       <c r="AN16" s="20"/>
@@ -5451,7 +5462,7 @@
         <v>6</v>
       </c>
       <c r="C17" s="19" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D17" s="20"/>
       <c r="E17" s="20"/>
@@ -5461,8 +5472,8 @@
       <c r="I17" s="20"/>
       <c r="J17" s="20"/>
       <c r="K17" s="21"/>
-      <c r="L17" s="109" t="s">
-        <v>68</v>
+      <c r="L17" s="19" t="s">
+        <v>67</v>
       </c>
       <c r="M17" s="20"/>
       <c r="N17" s="20"/>
@@ -5473,34 +5484,34 @@
       <c r="S17" s="20"/>
       <c r="T17" s="21"/>
       <c r="U17" s="19" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="V17" s="20"/>
       <c r="W17" s="20"/>
       <c r="X17" s="20"/>
       <c r="Y17" s="20"/>
       <c r="Z17" s="21"/>
-      <c r="AA17" s="76" t="s">
-        <v>71</v>
-      </c>
-      <c r="AB17" s="77"/>
-      <c r="AC17" s="76" t="s">
-        <v>71</v>
-      </c>
-      <c r="AD17" s="77"/>
-      <c r="AE17" s="110" t="s">
-        <v>71</v>
-      </c>
-      <c r="AF17" s="111"/>
+      <c r="AA17" s="111" t="s">
+        <v>70</v>
+      </c>
+      <c r="AB17" s="112"/>
+      <c r="AC17" s="111" t="s">
+        <v>70</v>
+      </c>
+      <c r="AD17" s="112"/>
+      <c r="AE17" s="113" t="s">
+        <v>70</v>
+      </c>
+      <c r="AF17" s="114"/>
       <c r="AG17" s="19" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AH17" s="20"/>
       <c r="AI17" s="20"/>
       <c r="AJ17" s="20"/>
       <c r="AK17" s="21"/>
-      <c r="AL17" s="112" t="s">
-        <v>71</v>
+      <c r="AL17" s="42" t="s">
+        <v>70</v>
       </c>
       <c r="AM17" s="20"/>
       <c r="AN17" s="20"/>
@@ -5526,7 +5537,7 @@
         <v>7</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D18" s="20"/>
       <c r="E18" s="20"/>
@@ -5536,8 +5547,8 @@
       <c r="I18" s="20"/>
       <c r="J18" s="20"/>
       <c r="K18" s="21"/>
-      <c r="L18" s="109" t="s">
-        <v>67</v>
+      <c r="L18" s="19" t="s">
+        <v>66</v>
       </c>
       <c r="M18" s="20"/>
       <c r="N18" s="20"/>
@@ -5548,34 +5559,34 @@
       <c r="S18" s="20"/>
       <c r="T18" s="21"/>
       <c r="U18" s="19" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="V18" s="20"/>
       <c r="W18" s="20"/>
       <c r="X18" s="20"/>
       <c r="Y18" s="20"/>
       <c r="Z18" s="21"/>
-      <c r="AA18" s="76" t="s">
-        <v>71</v>
-      </c>
-      <c r="AB18" s="77"/>
-      <c r="AC18" s="76" t="s">
-        <v>71</v>
-      </c>
-      <c r="AD18" s="77"/>
-      <c r="AE18" s="110" t="s">
-        <v>71</v>
-      </c>
-      <c r="AF18" s="111"/>
+      <c r="AA18" s="111" t="s">
+        <v>70</v>
+      </c>
+      <c r="AB18" s="112"/>
+      <c r="AC18" s="111" t="s">
+        <v>70</v>
+      </c>
+      <c r="AD18" s="112"/>
+      <c r="AE18" s="113" t="s">
+        <v>70</v>
+      </c>
+      <c r="AF18" s="114"/>
       <c r="AG18" s="19" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AH18" s="20"/>
       <c r="AI18" s="20"/>
       <c r="AJ18" s="20"/>
       <c r="AK18" s="21"/>
-      <c r="AL18" s="112" t="s">
-        <v>71</v>
+      <c r="AL18" s="42" t="s">
+        <v>70</v>
       </c>
       <c r="AM18" s="20"/>
       <c r="AN18" s="20"/>
@@ -5600,7 +5611,9 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C19" s="19"/>
+      <c r="C19" s="19" t="s">
+        <v>73</v>
+      </c>
       <c r="D19" s="20"/>
       <c r="E19" s="20"/>
       <c r="F19" s="20"/>
@@ -5609,7 +5622,9 @@
       <c r="I19" s="20"/>
       <c r="J19" s="20"/>
       <c r="K19" s="21"/>
-      <c r="L19" s="19"/>
+      <c r="L19" s="19" t="s">
+        <v>74</v>
+      </c>
       <c r="M19" s="20"/>
       <c r="N19" s="20"/>
       <c r="O19" s="20"/>
@@ -5618,24 +5633,36 @@
       <c r="R19" s="20"/>
       <c r="S19" s="20"/>
       <c r="T19" s="21"/>
-      <c r="U19" s="19"/>
+      <c r="U19" s="19" t="s">
+        <v>61</v>
+      </c>
       <c r="V19" s="20"/>
       <c r="W19" s="20"/>
       <c r="X19" s="20"/>
       <c r="Y19" s="20"/>
       <c r="Z19" s="21"/>
-      <c r="AA19" s="76"/>
-      <c r="AB19" s="77"/>
-      <c r="AC19" s="76"/>
-      <c r="AD19" s="77"/>
-      <c r="AE19" s="76"/>
-      <c r="AF19" s="77"/>
-      <c r="AG19" s="19"/>
+      <c r="AA19" s="111" t="s">
+        <v>70</v>
+      </c>
+      <c r="AB19" s="112"/>
+      <c r="AC19" s="111" t="s">
+        <v>70</v>
+      </c>
+      <c r="AD19" s="112"/>
+      <c r="AE19" s="113" t="s">
+        <v>70</v>
+      </c>
+      <c r="AF19" s="114"/>
+      <c r="AG19" s="19" t="s">
+        <v>72</v>
+      </c>
       <c r="AH19" s="20"/>
       <c r="AI19" s="20"/>
       <c r="AJ19" s="20"/>
       <c r="AK19" s="21"/>
-      <c r="AL19" s="19"/>
+      <c r="AL19" s="42" t="s">
+        <v>70</v>
+      </c>
       <c r="AM19" s="20"/>
       <c r="AN19" s="20"/>
       <c r="AO19" s="20"/>
@@ -5683,12 +5710,12 @@
       <c r="X20" s="20"/>
       <c r="Y20" s="20"/>
       <c r="Z20" s="21"/>
-      <c r="AA20" s="76"/>
-      <c r="AB20" s="77"/>
-      <c r="AC20" s="76"/>
-      <c r="AD20" s="77"/>
-      <c r="AE20" s="76"/>
-      <c r="AF20" s="77"/>
+      <c r="AA20" s="111"/>
+      <c r="AB20" s="112"/>
+      <c r="AC20" s="111"/>
+      <c r="AD20" s="112"/>
+      <c r="AE20" s="111"/>
+      <c r="AF20" s="112"/>
       <c r="AG20" s="19"/>
       <c r="AH20" s="20"/>
       <c r="AI20" s="20"/>
@@ -5742,12 +5769,12 @@
       <c r="X21" s="20"/>
       <c r="Y21" s="20"/>
       <c r="Z21" s="21"/>
-      <c r="AA21" s="76"/>
-      <c r="AB21" s="77"/>
-      <c r="AC21" s="76"/>
-      <c r="AD21" s="77"/>
-      <c r="AE21" s="76"/>
-      <c r="AF21" s="77"/>
+      <c r="AA21" s="111"/>
+      <c r="AB21" s="112"/>
+      <c r="AC21" s="111"/>
+      <c r="AD21" s="112"/>
+      <c r="AE21" s="111"/>
+      <c r="AF21" s="112"/>
       <c r="AG21" s="19"/>
       <c r="AH21" s="20"/>
       <c r="AI21" s="20"/>
@@ -5801,12 +5828,12 @@
       <c r="X22" s="20"/>
       <c r="Y22" s="20"/>
       <c r="Z22" s="21"/>
-      <c r="AA22" s="76"/>
-      <c r="AB22" s="77"/>
-      <c r="AC22" s="76"/>
-      <c r="AD22" s="77"/>
-      <c r="AE22" s="76"/>
-      <c r="AF22" s="77"/>
+      <c r="AA22" s="111"/>
+      <c r="AB22" s="112"/>
+      <c r="AC22" s="111"/>
+      <c r="AD22" s="112"/>
+      <c r="AE22" s="111"/>
+      <c r="AF22" s="112"/>
       <c r="AG22" s="19"/>
       <c r="AH22" s="20"/>
       <c r="AI22" s="20"/>
@@ -5860,12 +5887,12 @@
       <c r="X23" s="20"/>
       <c r="Y23" s="20"/>
       <c r="Z23" s="21"/>
-      <c r="AA23" s="76"/>
-      <c r="AB23" s="77"/>
-      <c r="AC23" s="76"/>
-      <c r="AD23" s="77"/>
-      <c r="AE23" s="76"/>
-      <c r="AF23" s="77"/>
+      <c r="AA23" s="111"/>
+      <c r="AB23" s="112"/>
+      <c r="AC23" s="111"/>
+      <c r="AD23" s="112"/>
+      <c r="AE23" s="111"/>
+      <c r="AF23" s="112"/>
       <c r="AG23" s="19"/>
       <c r="AH23" s="20"/>
       <c r="AI23" s="20"/>
@@ -5919,12 +5946,12 @@
       <c r="X24" s="20"/>
       <c r="Y24" s="20"/>
       <c r="Z24" s="21"/>
-      <c r="AA24" s="76"/>
-      <c r="AB24" s="77"/>
-      <c r="AC24" s="76"/>
-      <c r="AD24" s="77"/>
-      <c r="AE24" s="76"/>
-      <c r="AF24" s="77"/>
+      <c r="AA24" s="111"/>
+      <c r="AB24" s="112"/>
+      <c r="AC24" s="111"/>
+      <c r="AD24" s="112"/>
+      <c r="AE24" s="111"/>
+      <c r="AF24" s="112"/>
       <c r="AG24" s="19"/>
       <c r="AH24" s="20"/>
       <c r="AI24" s="20"/>
@@ -5978,12 +6005,12 @@
       <c r="X25" s="20"/>
       <c r="Y25" s="20"/>
       <c r="Z25" s="21"/>
-      <c r="AA25" s="76"/>
-      <c r="AB25" s="77"/>
-      <c r="AC25" s="76"/>
-      <c r="AD25" s="77"/>
-      <c r="AE25" s="76"/>
-      <c r="AF25" s="77"/>
+      <c r="AA25" s="111"/>
+      <c r="AB25" s="112"/>
+      <c r="AC25" s="111"/>
+      <c r="AD25" s="112"/>
+      <c r="AE25" s="111"/>
+      <c r="AF25" s="112"/>
       <c r="AG25" s="19"/>
       <c r="AH25" s="20"/>
       <c r="AI25" s="20"/>
@@ -6064,10 +6091,10 @@
     </row>
     <row r="29" spans="1:55">
       <c r="B29" s="39" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C29" s="19" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D29" s="20"/>
       <c r="E29" s="20"/>
@@ -6078,7 +6105,7 @@
       <c r="J29" s="20"/>
       <c r="K29" s="21"/>
       <c r="L29" s="19" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="M29" s="20"/>
       <c r="N29" s="20"/>
@@ -6089,7 +6116,7 @@
       <c r="S29" s="20"/>
       <c r="T29" s="21"/>
       <c r="U29" s="19" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="V29" s="20"/>
       <c r="W29" s="20"/>
@@ -6100,7 +6127,7 @@
       <c r="AB29" s="20"/>
       <c r="AC29" s="21"/>
       <c r="AD29" s="19" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AE29" s="20"/>
       <c r="AF29" s="20"/>
@@ -6113,12 +6140,12 @@
     </row>
   </sheetData>
   <mergeCells count="54">
-    <mergeCell ref="AA17:AB17"/>
-    <mergeCell ref="AC17:AD17"/>
-    <mergeCell ref="AE17:AF17"/>
-    <mergeCell ref="AA24:AB24"/>
-    <mergeCell ref="AC24:AD24"/>
-    <mergeCell ref="AE24:AF24"/>
+    <mergeCell ref="AA20:AB20"/>
+    <mergeCell ref="AC20:AD20"/>
+    <mergeCell ref="AE20:AF20"/>
+    <mergeCell ref="AA21:AB21"/>
+    <mergeCell ref="AC21:AD21"/>
+    <mergeCell ref="AE21:AF21"/>
     <mergeCell ref="AA25:AB25"/>
     <mergeCell ref="AC25:AD25"/>
     <mergeCell ref="AE25:AF25"/>
@@ -6128,16 +6155,9 @@
     <mergeCell ref="AA23:AB23"/>
     <mergeCell ref="AC23:AD23"/>
     <mergeCell ref="AE23:AF23"/>
-    <mergeCell ref="AA20:AB20"/>
-    <mergeCell ref="AC20:AD20"/>
-    <mergeCell ref="AE20:AF20"/>
-    <mergeCell ref="AA21:AB21"/>
-    <mergeCell ref="AC21:AD21"/>
-    <mergeCell ref="AE21:AF21"/>
-    <mergeCell ref="AA18:AB18"/>
-    <mergeCell ref="AC18:AD18"/>
-    <mergeCell ref="AE18:AF18"/>
-    <mergeCell ref="AA19:AB19"/>
+    <mergeCell ref="AA24:AB24"/>
+    <mergeCell ref="AC24:AD24"/>
+    <mergeCell ref="AE24:AF24"/>
     <mergeCell ref="AC19:AD19"/>
     <mergeCell ref="AE19:AF19"/>
     <mergeCell ref="AA15:AB15"/>
@@ -6146,6 +6166,13 @@
     <mergeCell ref="AA16:AB16"/>
     <mergeCell ref="AC16:AD16"/>
     <mergeCell ref="AE16:AF16"/>
+    <mergeCell ref="AA17:AB17"/>
+    <mergeCell ref="AC17:AD17"/>
+    <mergeCell ref="AE17:AF17"/>
+    <mergeCell ref="AA18:AB18"/>
+    <mergeCell ref="AC18:AD18"/>
+    <mergeCell ref="AE18:AF18"/>
+    <mergeCell ref="AA19:AB19"/>
     <mergeCell ref="AE12:AF12"/>
     <mergeCell ref="AA13:AB13"/>
     <mergeCell ref="AC13:AD13"/>
@@ -6153,12 +6180,12 @@
     <mergeCell ref="AA14:AB14"/>
     <mergeCell ref="AC14:AD14"/>
     <mergeCell ref="AE14:AF14"/>
+    <mergeCell ref="AC12:AD12"/>
     <mergeCell ref="B4:G4"/>
     <mergeCell ref="B5:G5"/>
     <mergeCell ref="B6:G8"/>
     <mergeCell ref="H6:Y8"/>
     <mergeCell ref="AA12:AB12"/>
-    <mergeCell ref="AC12:AD12"/>
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="H2:M2"/>
     <mergeCell ref="N2:S2"/>
@@ -6170,7 +6197,7 @@
   </mergeCells>
   <phoneticPr fontId="1"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AA12:AD25 AE12:AF16 AE19:AF25" xr:uid="{185F62DD-DD48-0446-94A1-F28EB9AD87E2}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AE20:AF25 AE12:AF16 AA12:AD25" xr:uid="{185F62DD-DD48-0446-94A1-F28EB9AD87E2}">
       <formula1>"-,○"</formula1>
     </dataValidation>
   </dataValidations>
@@ -6192,72 +6219,72 @@
       </c>
     </row>
     <row r="2" spans="1:55">
-      <c r="B2" s="66" t="s">
+      <c r="B2" s="76" t="s">
         <v>27</v>
       </c>
-      <c r="C2" s="73" t="s">
+      <c r="C2" s="83" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="73" t="s">
+      <c r="D2" s="83" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="73" t="s">
+      <c r="E2" s="83" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="73" t="s">
+      <c r="F2" s="83" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="67" t="s">
+      <c r="G2" s="77" t="s">
         <v>15</v>
       </c>
-      <c r="H2" s="87"/>
-      <c r="I2" s="88"/>
-      <c r="J2" s="88"/>
-      <c r="K2" s="88"/>
-      <c r="L2" s="88"/>
-      <c r="M2" s="89"/>
-      <c r="N2" s="66" t="s">
+      <c r="H2" s="89"/>
+      <c r="I2" s="87"/>
+      <c r="J2" s="87"/>
+      <c r="K2" s="87"/>
+      <c r="L2" s="87"/>
+      <c r="M2" s="88"/>
+      <c r="N2" s="76" t="s">
         <v>26</v>
       </c>
-      <c r="O2" s="73" t="s">
+      <c r="O2" s="83" t="s">
         <v>15</v>
       </c>
-      <c r="P2" s="73" t="s">
+      <c r="P2" s="83" t="s">
         <v>15</v>
       </c>
-      <c r="Q2" s="73" t="s">
+      <c r="Q2" s="83" t="s">
         <v>15</v>
       </c>
-      <c r="R2" s="73" t="s">
+      <c r="R2" s="83" t="s">
         <v>15</v>
       </c>
-      <c r="S2" s="67" t="s">
+      <c r="S2" s="77" t="s">
         <v>15</v>
       </c>
-      <c r="T2" s="87"/>
-      <c r="U2" s="88"/>
-      <c r="V2" s="88"/>
-      <c r="W2" s="88"/>
-      <c r="X2" s="88"/>
-      <c r="Y2" s="89"/>
+      <c r="T2" s="89"/>
+      <c r="U2" s="87"/>
+      <c r="V2" s="87"/>
+      <c r="W2" s="87"/>
+      <c r="X2" s="87"/>
+      <c r="Y2" s="88"/>
     </row>
     <row r="3" spans="1:55">
-      <c r="B3" s="74" t="s">
+      <c r="B3" s="84" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="75" t="s">
+      <c r="C3" s="85" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="75" t="s">
+      <c r="D3" s="85" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="75" t="s">
+      <c r="E3" s="85" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="75" t="s">
+      <c r="F3" s="85" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="75" t="s">
+      <c r="G3" s="85" t="s">
         <v>16</v>
       </c>
       <c r="H3" s="90"/>
@@ -6266,22 +6293,22 @@
       <c r="K3" s="91"/>
       <c r="L3" s="91"/>
       <c r="M3" s="91"/>
-      <c r="N3" s="74" t="s">
+      <c r="N3" s="84" t="s">
         <v>29</v>
       </c>
-      <c r="O3" s="75" t="s">
+      <c r="O3" s="85" t="s">
         <v>16</v>
       </c>
-      <c r="P3" s="75" t="s">
+      <c r="P3" s="85" t="s">
         <v>16</v>
       </c>
-      <c r="Q3" s="75" t="s">
+      <c r="Q3" s="85" t="s">
         <v>16</v>
       </c>
-      <c r="R3" s="75" t="s">
+      <c r="R3" s="85" t="s">
         <v>16</v>
       </c>
-      <c r="S3" s="75" t="s">
+      <c r="S3" s="85" t="s">
         <v>16</v>
       </c>
       <c r="T3" s="90"/>
@@ -6330,22 +6357,22 @@
       <c r="Y4" s="21"/>
     </row>
     <row r="5" spans="1:55">
-      <c r="B5" s="74" t="s">
+      <c r="B5" s="84" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="75" t="s">
+      <c r="C5" s="85" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="75" t="s">
+      <c r="D5" s="85" t="s">
         <v>16</v>
       </c>
-      <c r="E5" s="75" t="s">
+      <c r="E5" s="85" t="s">
         <v>16</v>
       </c>
-      <c r="F5" s="75" t="s">
+      <c r="F5" s="85" t="s">
         <v>16</v>
       </c>
-      <c r="G5" s="75" t="s">
+      <c r="G5" s="85" t="s">
         <v>16</v>
       </c>
       <c r="H5" s="22"/>
@@ -6368,32 +6395,32 @@
       <c r="Y5" s="24"/>
     </row>
     <row r="6" spans="1:55">
-      <c r="B6" s="66" t="s">
+      <c r="B6" s="76" t="s">
         <v>30</v>
       </c>
-      <c r="C6" s="73"/>
-      <c r="D6" s="73"/>
-      <c r="E6" s="73"/>
-      <c r="F6" s="73"/>
-      <c r="G6" s="67"/>
-      <c r="H6" s="78"/>
-      <c r="I6" s="79"/>
-      <c r="J6" s="79"/>
-      <c r="K6" s="79"/>
-      <c r="L6" s="79"/>
-      <c r="M6" s="79"/>
-      <c r="N6" s="79"/>
-      <c r="O6" s="79"/>
-      <c r="P6" s="79"/>
-      <c r="Q6" s="79"/>
-      <c r="R6" s="79"/>
-      <c r="S6" s="79"/>
-      <c r="T6" s="79"/>
-      <c r="U6" s="79"/>
-      <c r="V6" s="79"/>
-      <c r="W6" s="79"/>
-      <c r="X6" s="79"/>
-      <c r="Y6" s="80"/>
+      <c r="C6" s="83"/>
+      <c r="D6" s="83"/>
+      <c r="E6" s="83"/>
+      <c r="F6" s="83"/>
+      <c r="G6" s="77"/>
+      <c r="H6" s="102"/>
+      <c r="I6" s="103"/>
+      <c r="J6" s="103"/>
+      <c r="K6" s="103"/>
+      <c r="L6" s="103"/>
+      <c r="M6" s="103"/>
+      <c r="N6" s="103"/>
+      <c r="O6" s="103"/>
+      <c r="P6" s="103"/>
+      <c r="Q6" s="103"/>
+      <c r="R6" s="103"/>
+      <c r="S6" s="103"/>
+      <c r="T6" s="103"/>
+      <c r="U6" s="103"/>
+      <c r="V6" s="103"/>
+      <c r="W6" s="103"/>
+      <c r="X6" s="103"/>
+      <c r="Y6" s="104"/>
     </row>
     <row r="7" spans="1:55">
       <c r="B7" s="96"/>
@@ -6402,24 +6429,24 @@
       <c r="E7" s="97"/>
       <c r="F7" s="97"/>
       <c r="G7" s="98"/>
-      <c r="H7" s="81"/>
-      <c r="I7" s="82"/>
-      <c r="J7" s="82"/>
-      <c r="K7" s="82"/>
-      <c r="L7" s="82"/>
-      <c r="M7" s="82"/>
-      <c r="N7" s="82"/>
-      <c r="O7" s="82"/>
-      <c r="P7" s="82"/>
-      <c r="Q7" s="82"/>
-      <c r="R7" s="82"/>
-      <c r="S7" s="82"/>
-      <c r="T7" s="82"/>
-      <c r="U7" s="82"/>
-      <c r="V7" s="82"/>
-      <c r="W7" s="82"/>
-      <c r="X7" s="82"/>
-      <c r="Y7" s="83"/>
+      <c r="H7" s="105"/>
+      <c r="I7" s="106"/>
+      <c r="J7" s="106"/>
+      <c r="K7" s="106"/>
+      <c r="L7" s="106"/>
+      <c r="M7" s="106"/>
+      <c r="N7" s="106"/>
+      <c r="O7" s="106"/>
+      <c r="P7" s="106"/>
+      <c r="Q7" s="106"/>
+      <c r="R7" s="106"/>
+      <c r="S7" s="106"/>
+      <c r="T7" s="106"/>
+      <c r="U7" s="106"/>
+      <c r="V7" s="106"/>
+      <c r="W7" s="106"/>
+      <c r="X7" s="106"/>
+      <c r="Y7" s="107"/>
     </row>
     <row r="8" spans="1:55">
       <c r="B8" s="99"/>
@@ -6428,24 +6455,24 @@
       <c r="E8" s="100"/>
       <c r="F8" s="100"/>
       <c r="G8" s="101"/>
-      <c r="H8" s="84"/>
-      <c r="I8" s="85"/>
-      <c r="J8" s="85"/>
-      <c r="K8" s="85"/>
-      <c r="L8" s="85"/>
-      <c r="M8" s="85"/>
-      <c r="N8" s="85"/>
-      <c r="O8" s="85"/>
-      <c r="P8" s="85"/>
-      <c r="Q8" s="85"/>
-      <c r="R8" s="85"/>
-      <c r="S8" s="85"/>
-      <c r="T8" s="85"/>
-      <c r="U8" s="85"/>
-      <c r="V8" s="85"/>
-      <c r="W8" s="85"/>
-      <c r="X8" s="85"/>
-      <c r="Y8" s="86"/>
+      <c r="H8" s="108"/>
+      <c r="I8" s="109"/>
+      <c r="J8" s="109"/>
+      <c r="K8" s="109"/>
+      <c r="L8" s="109"/>
+      <c r="M8" s="109"/>
+      <c r="N8" s="109"/>
+      <c r="O8" s="109"/>
+      <c r="P8" s="109"/>
+      <c r="Q8" s="109"/>
+      <c r="R8" s="109"/>
+      <c r="S8" s="109"/>
+      <c r="T8" s="109"/>
+      <c r="U8" s="109"/>
+      <c r="V8" s="109"/>
+      <c r="W8" s="109"/>
+      <c r="X8" s="109"/>
+      <c r="Y8" s="110"/>
     </row>
     <row r="10" spans="1:55" ht="20">
       <c r="A10" s="41" t="s">
@@ -6552,12 +6579,12 @@
       <c r="X12" s="20"/>
       <c r="Y12" s="20"/>
       <c r="Z12" s="21"/>
-      <c r="AA12" s="76"/>
-      <c r="AB12" s="77"/>
-      <c r="AC12" s="76"/>
-      <c r="AD12" s="77"/>
-      <c r="AE12" s="76"/>
-      <c r="AF12" s="77"/>
+      <c r="AA12" s="111"/>
+      <c r="AB12" s="112"/>
+      <c r="AC12" s="111"/>
+      <c r="AD12" s="112"/>
+      <c r="AE12" s="111"/>
+      <c r="AF12" s="112"/>
       <c r="AG12" s="19"/>
       <c r="AH12" s="20"/>
       <c r="AI12" s="20"/>
@@ -6608,12 +6635,12 @@
       <c r="X13" s="20"/>
       <c r="Y13" s="20"/>
       <c r="Z13" s="21"/>
-      <c r="AA13" s="76"/>
-      <c r="AB13" s="77"/>
-      <c r="AC13" s="76"/>
-      <c r="AD13" s="77"/>
-      <c r="AE13" s="76"/>
-      <c r="AF13" s="77"/>
+      <c r="AA13" s="111"/>
+      <c r="AB13" s="112"/>
+      <c r="AC13" s="111"/>
+      <c r="AD13" s="112"/>
+      <c r="AE13" s="111"/>
+      <c r="AF13" s="112"/>
       <c r="AG13" s="19"/>
       <c r="AH13" s="20"/>
       <c r="AI13" s="20"/>
@@ -6664,12 +6691,12 @@
       <c r="X14" s="20"/>
       <c r="Y14" s="20"/>
       <c r="Z14" s="21"/>
-      <c r="AA14" s="76"/>
-      <c r="AB14" s="77"/>
-      <c r="AC14" s="76"/>
-      <c r="AD14" s="77"/>
-      <c r="AE14" s="76"/>
-      <c r="AF14" s="77"/>
+      <c r="AA14" s="111"/>
+      <c r="AB14" s="112"/>
+      <c r="AC14" s="111"/>
+      <c r="AD14" s="112"/>
+      <c r="AE14" s="111"/>
+      <c r="AF14" s="112"/>
       <c r="AG14" s="19"/>
       <c r="AH14" s="20"/>
       <c r="AI14" s="20"/>
@@ -6720,12 +6747,12 @@
       <c r="X15" s="20"/>
       <c r="Y15" s="20"/>
       <c r="Z15" s="21"/>
-      <c r="AA15" s="76"/>
-      <c r="AB15" s="77"/>
-      <c r="AC15" s="76"/>
-      <c r="AD15" s="77"/>
-      <c r="AE15" s="76"/>
-      <c r="AF15" s="77"/>
+      <c r="AA15" s="111"/>
+      <c r="AB15" s="112"/>
+      <c r="AC15" s="111"/>
+      <c r="AD15" s="112"/>
+      <c r="AE15" s="111"/>
+      <c r="AF15" s="112"/>
       <c r="AG15" s="19"/>
       <c r="AH15" s="20"/>
       <c r="AI15" s="20"/>
@@ -6776,12 +6803,12 @@
       <c r="X16" s="20"/>
       <c r="Y16" s="20"/>
       <c r="Z16" s="21"/>
-      <c r="AA16" s="76"/>
-      <c r="AB16" s="77"/>
-      <c r="AC16" s="76"/>
-      <c r="AD16" s="77"/>
-      <c r="AE16" s="76"/>
-      <c r="AF16" s="77"/>
+      <c r="AA16" s="111"/>
+      <c r="AB16" s="112"/>
+      <c r="AC16" s="111"/>
+      <c r="AD16" s="112"/>
+      <c r="AE16" s="111"/>
+      <c r="AF16" s="112"/>
       <c r="AG16" s="19"/>
       <c r="AH16" s="20"/>
       <c r="AI16" s="20"/>
@@ -6832,12 +6859,12 @@
       <c r="X17" s="20"/>
       <c r="Y17" s="20"/>
       <c r="Z17" s="21"/>
-      <c r="AA17" s="76"/>
-      <c r="AB17" s="77"/>
-      <c r="AC17" s="76"/>
-      <c r="AD17" s="77"/>
-      <c r="AE17" s="76"/>
-      <c r="AF17" s="77"/>
+      <c r="AA17" s="111"/>
+      <c r="AB17" s="112"/>
+      <c r="AC17" s="111"/>
+      <c r="AD17" s="112"/>
+      <c r="AE17" s="111"/>
+      <c r="AF17" s="112"/>
       <c r="AG17" s="19"/>
       <c r="AH17" s="20"/>
       <c r="AI17" s="20"/>
@@ -6888,12 +6915,12 @@
       <c r="X18" s="20"/>
       <c r="Y18" s="20"/>
       <c r="Z18" s="21"/>
-      <c r="AA18" s="76"/>
-      <c r="AB18" s="77"/>
-      <c r="AC18" s="76"/>
-      <c r="AD18" s="77"/>
-      <c r="AE18" s="76"/>
-      <c r="AF18" s="77"/>
+      <c r="AA18" s="111"/>
+      <c r="AB18" s="112"/>
+      <c r="AC18" s="111"/>
+      <c r="AD18" s="112"/>
+      <c r="AE18" s="111"/>
+      <c r="AF18" s="112"/>
       <c r="AG18" s="19"/>
       <c r="AH18" s="20"/>
       <c r="AI18" s="20"/>
@@ -6944,12 +6971,12 @@
       <c r="X19" s="20"/>
       <c r="Y19" s="20"/>
       <c r="Z19" s="21"/>
-      <c r="AA19" s="76"/>
-      <c r="AB19" s="77"/>
-      <c r="AC19" s="76"/>
-      <c r="AD19" s="77"/>
-      <c r="AE19" s="76"/>
-      <c r="AF19" s="77"/>
+      <c r="AA19" s="111"/>
+      <c r="AB19" s="112"/>
+      <c r="AC19" s="111"/>
+      <c r="AD19" s="112"/>
+      <c r="AE19" s="111"/>
+      <c r="AF19" s="112"/>
       <c r="AG19" s="19"/>
       <c r="AH19" s="20"/>
       <c r="AI19" s="20"/>
@@ -7000,12 +7027,12 @@
       <c r="X20" s="20"/>
       <c r="Y20" s="20"/>
       <c r="Z20" s="21"/>
-      <c r="AA20" s="76"/>
-      <c r="AB20" s="77"/>
-      <c r="AC20" s="76"/>
-      <c r="AD20" s="77"/>
-      <c r="AE20" s="76"/>
-      <c r="AF20" s="77"/>
+      <c r="AA20" s="111"/>
+      <c r="AB20" s="112"/>
+      <c r="AC20" s="111"/>
+      <c r="AD20" s="112"/>
+      <c r="AE20" s="111"/>
+      <c r="AF20" s="112"/>
       <c r="AG20" s="19"/>
       <c r="AH20" s="20"/>
       <c r="AI20" s="20"/>
@@ -7056,12 +7083,12 @@
       <c r="X21" s="20"/>
       <c r="Y21" s="20"/>
       <c r="Z21" s="21"/>
-      <c r="AA21" s="76"/>
-      <c r="AB21" s="77"/>
-      <c r="AC21" s="76"/>
-      <c r="AD21" s="77"/>
-      <c r="AE21" s="76"/>
-      <c r="AF21" s="77"/>
+      <c r="AA21" s="111"/>
+      <c r="AB21" s="112"/>
+      <c r="AC21" s="111"/>
+      <c r="AD21" s="112"/>
+      <c r="AE21" s="111"/>
+      <c r="AF21" s="112"/>
       <c r="AG21" s="19"/>
       <c r="AH21" s="20"/>
       <c r="AI21" s="20"/>
@@ -7112,12 +7139,12 @@
       <c r="X22" s="20"/>
       <c r="Y22" s="20"/>
       <c r="Z22" s="21"/>
-      <c r="AA22" s="76"/>
-      <c r="AB22" s="77"/>
-      <c r="AC22" s="76"/>
-      <c r="AD22" s="77"/>
-      <c r="AE22" s="76"/>
-      <c r="AF22" s="77"/>
+      <c r="AA22" s="111"/>
+      <c r="AB22" s="112"/>
+      <c r="AC22" s="111"/>
+      <c r="AD22" s="112"/>
+      <c r="AE22" s="111"/>
+      <c r="AF22" s="112"/>
       <c r="AG22" s="19"/>
       <c r="AH22" s="20"/>
       <c r="AI22" s="20"/>
@@ -7168,12 +7195,12 @@
       <c r="X23" s="20"/>
       <c r="Y23" s="20"/>
       <c r="Z23" s="21"/>
-      <c r="AA23" s="76"/>
-      <c r="AB23" s="77"/>
-      <c r="AC23" s="76"/>
-      <c r="AD23" s="77"/>
-      <c r="AE23" s="76"/>
-      <c r="AF23" s="77"/>
+      <c r="AA23" s="111"/>
+      <c r="AB23" s="112"/>
+      <c r="AC23" s="111"/>
+      <c r="AD23" s="112"/>
+      <c r="AE23" s="111"/>
+      <c r="AF23" s="112"/>
       <c r="AG23" s="19"/>
       <c r="AH23" s="20"/>
       <c r="AI23" s="20"/>
@@ -7224,12 +7251,12 @@
       <c r="X24" s="20"/>
       <c r="Y24" s="20"/>
       <c r="Z24" s="21"/>
-      <c r="AA24" s="76"/>
-      <c r="AB24" s="77"/>
-      <c r="AC24" s="76"/>
-      <c r="AD24" s="77"/>
-      <c r="AE24" s="76"/>
-      <c r="AF24" s="77"/>
+      <c r="AA24" s="111"/>
+      <c r="AB24" s="112"/>
+      <c r="AC24" s="111"/>
+      <c r="AD24" s="112"/>
+      <c r="AE24" s="111"/>
+      <c r="AF24" s="112"/>
       <c r="AG24" s="19"/>
       <c r="AH24" s="20"/>
       <c r="AI24" s="20"/>
@@ -7310,10 +7337,10 @@
     </row>
     <row r="28" spans="1:55">
       <c r="B28" s="39" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C28" s="19" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D28" s="20"/>
       <c r="E28" s="20"/>
@@ -7324,7 +7351,7 @@
       <c r="J28" s="20"/>
       <c r="K28" s="21"/>
       <c r="L28" s="19" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="M28" s="20"/>
       <c r="N28" s="20"/>
@@ -7335,7 +7362,7 @@
       <c r="S28" s="20"/>
       <c r="T28" s="21"/>
       <c r="U28" s="19" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="V28" s="20"/>
       <c r="W28" s="20"/>
@@ -7346,7 +7373,7 @@
       <c r="AB28" s="20"/>
       <c r="AC28" s="21"/>
       <c r="AD28" s="19" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AE28" s="20"/>
       <c r="AF28" s="20"/>

--- a/2024年_スキル検索モデル（仮）/04.テーブル設計/テーブル定義.xlsx
+++ b/2024年_スキル検索モデル（仮）/04.テーブル設計/テーブル定義.xlsx
@@ -8,18 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/beaming-boy/growth/プロジェクト/ドキュメント共有フォルダ/2024年_スキル検索モデル（仮）/04.テーブル設計/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8999FCCA-5DD2-6F4E-BCCC-B039DDC947C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8197DA60-CFCD-0D45-B945-1743425F089C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-72000" yWindow="500" windowWidth="38400" windowHeight="21100" activeTab="3" xr2:uid="{3C8D862C-6145-E842-B259-880AA5F992AF}"/>
+    <workbookView xWindow="-33600" yWindow="0" windowWidth="33600" windowHeight="21000" firstSheet="2" activeTab="2" xr2:uid="{3C8D862C-6145-E842-B259-880AA5F992AF}"/>
   </bookViews>
   <sheets>
     <sheet name="改訂履歴" sheetId="3" r:id="rId1"/>
     <sheet name="ヘッダー" sheetId="2" r:id="rId2"/>
     <sheet name="テーブル一覧" sheetId="5" r:id="rId3"/>
     <sheet name=" No1_engineer(技術者情報マスタ) " sheetId="8" r:id="rId4"/>
-    <sheet name=" 一覧のNo_ 物理テーブル名 ( 論理テーブル名 )" sheetId="7" r:id="rId5"/>
+    <sheet name=" No２_utilData(汎用マスタ)" sheetId="9" r:id="rId5"/>
+    <sheet name=" 一覧のNo_ 物理テーブル名 ( 論理テーブル名 )" sheetId="7" r:id="rId6"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">' No1_engineer(技術者情報マスタ) '!$A$11:$BC$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">テーブル一覧!#REF!</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">テーブル一覧!$A$1:$AZ$27</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">ヘッダー!$A$1:$AZ$6</definedName>
@@ -43,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="851" uniqueCount="216">
   <si>
     <t>No.</t>
     <phoneticPr fontId="1"/>
@@ -395,13 +397,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>技術者ナンバー</t>
-    <rPh sb="0" eb="3">
-      <t>ギジュｔウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>年齢</t>
     <rPh sb="0" eb="2">
       <t>ネンレイ</t>
@@ -515,7 +510,559 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>engineer_id</t>
+    <t>技術者ID</t>
+    <rPh sb="0" eb="3">
+      <t>ギジュｔウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>utilData</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>汎用マスタ</t>
+    <rPh sb="0" eb="2">
+      <t>ハンヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>汎用データを保持。プルダウンなどの値に使用</t>
+    <rPh sb="0" eb="1">
+      <t>ハンヨウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ホｚイ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>アタイ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>シヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>sortNo</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>type</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>val</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>String</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>分類</t>
+    <rPh sb="0" eb="2">
+      <t>ブンルイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>値</t>
+    <rPh sb="0" eb="1">
+      <t>アタイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>並び順</t>
+    <rPh sb="0" eb="1">
+      <t>ナラｂイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>id</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>設定内容</t>
+    <rPh sb="0" eb="4">
+      <t>セッテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>0:未経験など値の意味合いを定義する項目</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>settingDetails</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アクティブフラグ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>activeFlg</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>有効なら1、無効なら0</t>
+    <rPh sb="0" eb="2">
+      <t>ユウコウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>👉</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>作成日</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>作成者</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>更新日</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>更新者</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>createDate</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>createUser</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>updateDate</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>updateUser</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Timestamp</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>windows</t>
+  </si>
+  <si>
+    <t>windows</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>mac</t>
+  </si>
+  <si>
+    <t>mac</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>android</t>
+  </si>
+  <si>
+    <t>android</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ios</t>
+  </si>
+  <si>
+    <t>ios</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>DB1</t>
+  </si>
+  <si>
+    <t>DB2</t>
+  </si>
+  <si>
+    <t>DB3</t>
+  </si>
+  <si>
+    <t>DB4</t>
+  </si>
+  <si>
+    <t>DB5</t>
+  </si>
+  <si>
+    <t>Git</t>
+  </si>
+  <si>
+    <t>svn</t>
+  </si>
+  <si>
+    <t>Backlog</t>
+  </si>
+  <si>
+    <t>Docker</t>
+  </si>
+  <si>
+    <t>Jenkins</t>
+  </si>
+  <si>
+    <t>Ansible</t>
+  </si>
+  <si>
+    <t>androidStadio</t>
+  </si>
+  <si>
+    <t>Eclipse</t>
+  </si>
+  <si>
+    <t>IntelliJ IDEA</t>
+  </si>
+  <si>
+    <t>Xcode</t>
+  </si>
+  <si>
+    <t>基本設計</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>詳細設計</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>コーデング</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>単体</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>結合</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>保守</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>PM経験</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>PM補佐経験</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>リーダ経験</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>技術支援経験</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>コンサル経験</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Linux </t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>クラウド1</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>クラウド1経験</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>クラウド2</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>クラウド2経験</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>クラウド3</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>クラウド3経験</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>クラウド4</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>クラウド4経験</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>クラウド5</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>クラウド5経験</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>言語1</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>言語1経験</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>言語2</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>言語2経験</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>言語3</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>言語3経験</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>言語4</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>言語4経験</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>言語5</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>言語5経験</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>DB1</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>DB1経験</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>DB2</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>DB2経験</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>DB3</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>DB3経験</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>DB4</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>DB4経験</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>DB5</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>DB5経験</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Git</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>svn</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Backlog</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Docker</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Jenkins</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Ansible</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>androidStadio</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Visual Studio Code</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Eclipse</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>IntelliJ IDEA</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Xcode</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Coding</t>
+  </si>
+  <si>
+    <t>Unit</t>
+  </si>
+  <si>
+    <t>Combination</t>
+  </si>
+  <si>
+    <t>Maintenance</t>
+  </si>
+  <si>
+    <t>Linux</t>
+  </si>
+  <si>
+    <t>BasicDesign</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>DetailedDesign</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>PMExperience</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>PMAssistantExperience</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>LeaderExperience</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>TechnicalSupportExperience</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ConsultingExperience</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Cloud1</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Cloud1experience</t>
+  </si>
+  <si>
+    <t>Cloud2</t>
+  </si>
+  <si>
+    <t>Cloud2experience</t>
+  </si>
+  <si>
+    <t>Cloud3</t>
+  </si>
+  <si>
+    <t>Cloud3experience</t>
+  </si>
+  <si>
+    <t>Cloud4</t>
+  </si>
+  <si>
+    <t>Cloud4experience</t>
+  </si>
+  <si>
+    <t>Cloud5</t>
+  </si>
+  <si>
+    <t>Cloud5experience</t>
+  </si>
+  <si>
+    <t>Language1</t>
+  </si>
+  <si>
+    <t>Language1experience</t>
+  </si>
+  <si>
+    <t>Language2</t>
+  </si>
+  <si>
+    <t>Language2experience</t>
+  </si>
+  <si>
+    <t>Language3</t>
+  </si>
+  <si>
+    <t>Language3experience</t>
+  </si>
+  <si>
+    <t>Language4</t>
+  </si>
+  <si>
+    <t>Language4experience</t>
+  </si>
+  <si>
+    <t>Language5</t>
+  </si>
+  <si>
+    <t>Language5experience</t>
+  </si>
+  <si>
+    <t>DB1experience</t>
+  </si>
+  <si>
+    <t>DB2experience</t>
+  </si>
+  <si>
+    <t>DB3experience</t>
+  </si>
+  <si>
+    <t>DB4experience</t>
+  </si>
+  <si>
+    <t>DB5experience</t>
+  </si>
+  <si>
+    <t>VisualStudioCode</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -523,7 +1070,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="16">
+  <fonts count="19">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -626,6 +1173,25 @@
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
+      <name val="MeiryoUI"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Courier New"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="MeiryoUI"/>
+      <family val="2"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
       <name val="MeiryoUI"/>
       <charset val="128"/>
     </font>
@@ -812,7 +1378,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="115">
+  <cellXfs count="125">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -941,6 +1507,12 @@
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1158,6 +1730,30 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -1211,7 +1807,7 @@
               <a:picLocks noChangeAspect="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="ヘッダー!A1:AY3" spid="_x0000_s3372"/>
+                  <a14:cameraTool cellRange="ヘッダー!A1:AY3" spid="_x0000_s3484"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -1270,7 +1866,7 @@
               <a:picLocks noChangeAspect="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="ヘッダー!A1:AY3" spid="_x0000_s7377"/>
+                  <a14:cameraTool cellRange="ヘッダー!A1:AY3" spid="_x0000_s7489"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -1688,13 +2284,13 @@
       <c r="D8" s="4"/>
       <c r="E8" s="4"/>
       <c r="F8" s="5"/>
-      <c r="G8" s="43">
+      <c r="G8" s="45">
         <v>45459</v>
       </c>
-      <c r="H8" s="44"/>
-      <c r="I8" s="44"/>
-      <c r="J8" s="44"/>
-      <c r="K8" s="45"/>
+      <c r="H8" s="46"/>
+      <c r="I8" s="46"/>
+      <c r="J8" s="46"/>
+      <c r="K8" s="47"/>
       <c r="L8" s="11" t="s">
         <v>45</v>
       </c>
@@ -1727,7 +2323,7 @@
       <c r="AK8" s="4"/>
       <c r="AL8" s="5"/>
       <c r="AM8" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AN8" s="4"/>
       <c r="AO8" s="4"/>
@@ -3303,187 +3899,187 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="3.33203125" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:54" ht="15" customHeight="1">
-      <c r="A1" s="61" t="s">
+      <c r="A1" s="63" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="62"/>
-      <c r="C1" s="62"/>
-      <c r="D1" s="62"/>
-      <c r="E1" s="63"/>
-      <c r="F1" s="46" t="s">
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="65"/>
+      <c r="F1" s="48" t="s">
         <v>17</v>
       </c>
-      <c r="G1" s="47"/>
-      <c r="H1" s="47"/>
-      <c r="I1" s="47"/>
-      <c r="J1" s="48"/>
-      <c r="K1" s="46" t="s">
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
+      <c r="I1" s="49"/>
+      <c r="J1" s="50"/>
+      <c r="K1" s="48" t="s">
         <v>2</v>
       </c>
-      <c r="L1" s="47"/>
-      <c r="M1" s="47"/>
-      <c r="N1" s="47"/>
-      <c r="O1" s="47"/>
-      <c r="P1" s="47"/>
-      <c r="Q1" s="47"/>
-      <c r="R1" s="47"/>
-      <c r="S1" s="47"/>
-      <c r="T1" s="47"/>
-      <c r="U1" s="47"/>
-      <c r="V1" s="47"/>
-      <c r="W1" s="47"/>
-      <c r="X1" s="47"/>
-      <c r="Y1" s="47"/>
-      <c r="Z1" s="47"/>
-      <c r="AA1" s="47"/>
-      <c r="AB1" s="47"/>
-      <c r="AC1" s="47"/>
-      <c r="AD1" s="47"/>
-      <c r="AE1" s="48"/>
-      <c r="AF1" s="46" t="s">
+      <c r="L1" s="49"/>
+      <c r="M1" s="49"/>
+      <c r="N1" s="49"/>
+      <c r="O1" s="49"/>
+      <c r="P1" s="49"/>
+      <c r="Q1" s="49"/>
+      <c r="R1" s="49"/>
+      <c r="S1" s="49"/>
+      <c r="T1" s="49"/>
+      <c r="U1" s="49"/>
+      <c r="V1" s="49"/>
+      <c r="W1" s="49"/>
+      <c r="X1" s="49"/>
+      <c r="Y1" s="49"/>
+      <c r="Z1" s="49"/>
+      <c r="AA1" s="49"/>
+      <c r="AB1" s="49"/>
+      <c r="AC1" s="49"/>
+      <c r="AD1" s="49"/>
+      <c r="AE1" s="50"/>
+      <c r="AF1" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="AG1" s="47"/>
-      <c r="AH1" s="47"/>
-      <c r="AI1" s="47"/>
-      <c r="AJ1" s="48"/>
-      <c r="AK1" s="46" t="s">
+      <c r="AG1" s="49"/>
+      <c r="AH1" s="49"/>
+      <c r="AI1" s="49"/>
+      <c r="AJ1" s="50"/>
+      <c r="AK1" s="48" t="s">
         <v>4</v>
       </c>
-      <c r="AL1" s="47"/>
-      <c r="AM1" s="47"/>
-      <c r="AN1" s="47"/>
-      <c r="AO1" s="48"/>
-      <c r="AP1" s="46" t="s">
+      <c r="AL1" s="49"/>
+      <c r="AM1" s="49"/>
+      <c r="AN1" s="49"/>
+      <c r="AO1" s="50"/>
+      <c r="AP1" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="AQ1" s="47"/>
-      <c r="AR1" s="47"/>
-      <c r="AS1" s="47"/>
-      <c r="AT1" s="48"/>
-      <c r="AU1" s="46" t="s">
+      <c r="AQ1" s="49"/>
+      <c r="AR1" s="49"/>
+      <c r="AS1" s="49"/>
+      <c r="AT1" s="50"/>
+      <c r="AU1" s="48" t="s">
         <v>6</v>
       </c>
-      <c r="AV1" s="47"/>
-      <c r="AW1" s="47"/>
-      <c r="AX1" s="47"/>
-      <c r="AY1" s="48"/>
+      <c r="AV1" s="49"/>
+      <c r="AW1" s="49"/>
+      <c r="AX1" s="49"/>
+      <c r="AY1" s="50"/>
       <c r="BB1" s="2"/>
     </row>
     <row r="2" spans="1:54" ht="15" customHeight="1">
-      <c r="A2" s="64"/>
-      <c r="B2" s="65"/>
-      <c r="C2" s="65"/>
-      <c r="D2" s="65"/>
-      <c r="E2" s="66"/>
-      <c r="F2" s="70" t="s">
+      <c r="A2" s="66"/>
+      <c r="B2" s="67"/>
+      <c r="C2" s="67"/>
+      <c r="D2" s="67"/>
+      <c r="E2" s="68"/>
+      <c r="F2" s="72" t="s">
         <v>44</v>
       </c>
-      <c r="G2" s="71"/>
-      <c r="H2" s="71"/>
-      <c r="I2" s="71"/>
-      <c r="J2" s="72"/>
-      <c r="K2" s="49" t="s">
+      <c r="G2" s="73"/>
+      <c r="H2" s="73"/>
+      <c r="I2" s="73"/>
+      <c r="J2" s="74"/>
+      <c r="K2" s="51" t="s">
         <v>18</v>
       </c>
-      <c r="L2" s="50"/>
-      <c r="M2" s="50"/>
-      <c r="N2" s="50"/>
-      <c r="O2" s="50"/>
-      <c r="P2" s="50"/>
-      <c r="Q2" s="50"/>
-      <c r="R2" s="50"/>
-      <c r="S2" s="50"/>
-      <c r="T2" s="50"/>
-      <c r="U2" s="50"/>
-      <c r="V2" s="50"/>
-      <c r="W2" s="50"/>
-      <c r="X2" s="50"/>
-      <c r="Y2" s="50"/>
-      <c r="Z2" s="50"/>
-      <c r="AA2" s="50"/>
-      <c r="AB2" s="50"/>
-      <c r="AC2" s="50"/>
-      <c r="AD2" s="50"/>
-      <c r="AE2" s="51"/>
-      <c r="AF2" s="55">
+      <c r="L2" s="52"/>
+      <c r="M2" s="52"/>
+      <c r="N2" s="52"/>
+      <c r="O2" s="52"/>
+      <c r="P2" s="52"/>
+      <c r="Q2" s="52"/>
+      <c r="R2" s="52"/>
+      <c r="S2" s="52"/>
+      <c r="T2" s="52"/>
+      <c r="U2" s="52"/>
+      <c r="V2" s="52"/>
+      <c r="W2" s="52"/>
+      <c r="X2" s="52"/>
+      <c r="Y2" s="52"/>
+      <c r="Z2" s="52"/>
+      <c r="AA2" s="52"/>
+      <c r="AB2" s="52"/>
+      <c r="AC2" s="52"/>
+      <c r="AD2" s="52"/>
+      <c r="AE2" s="53"/>
+      <c r="AF2" s="57">
         <v>45459</v>
       </c>
-      <c r="AG2" s="56"/>
-      <c r="AH2" s="56"/>
-      <c r="AI2" s="56"/>
-      <c r="AJ2" s="57"/>
-      <c r="AK2" s="49" t="s">
+      <c r="AG2" s="58"/>
+      <c r="AH2" s="58"/>
+      <c r="AI2" s="58"/>
+      <c r="AJ2" s="59"/>
+      <c r="AK2" s="51" t="s">
         <v>45</v>
       </c>
-      <c r="AL2" s="50"/>
-      <c r="AM2" s="50"/>
-      <c r="AN2" s="50"/>
-      <c r="AO2" s="51"/>
-      <c r="AP2" s="55"/>
-      <c r="AQ2" s="56"/>
-      <c r="AR2" s="56"/>
-      <c r="AS2" s="56"/>
-      <c r="AT2" s="57"/>
-      <c r="AU2" s="49"/>
-      <c r="AV2" s="50"/>
-      <c r="AW2" s="50"/>
-      <c r="AX2" s="50"/>
-      <c r="AY2" s="51"/>
+      <c r="AL2" s="52"/>
+      <c r="AM2" s="52"/>
+      <c r="AN2" s="52"/>
+      <c r="AO2" s="53"/>
+      <c r="AP2" s="57"/>
+      <c r="AQ2" s="58"/>
+      <c r="AR2" s="58"/>
+      <c r="AS2" s="58"/>
+      <c r="AT2" s="59"/>
+      <c r="AU2" s="51"/>
+      <c r="AV2" s="52"/>
+      <c r="AW2" s="52"/>
+      <c r="AX2" s="52"/>
+      <c r="AY2" s="53"/>
       <c r="BB2" s="2"/>
     </row>
     <row r="3" spans="1:54" ht="15" customHeight="1">
-      <c r="A3" s="67"/>
-      <c r="B3" s="68"/>
-      <c r="C3" s="68"/>
-      <c r="D3" s="68"/>
-      <c r="E3" s="69"/>
-      <c r="F3" s="73"/>
-      <c r="G3" s="74"/>
-      <c r="H3" s="74"/>
-      <c r="I3" s="74"/>
-      <c r="J3" s="75"/>
-      <c r="K3" s="52"/>
-      <c r="L3" s="53"/>
-      <c r="M3" s="53"/>
-      <c r="N3" s="53"/>
-      <c r="O3" s="53"/>
-      <c r="P3" s="53"/>
-      <c r="Q3" s="53"/>
-      <c r="R3" s="53"/>
-      <c r="S3" s="53"/>
-      <c r="T3" s="53"/>
-      <c r="U3" s="53"/>
-      <c r="V3" s="53"/>
-      <c r="W3" s="53"/>
-      <c r="X3" s="53"/>
-      <c r="Y3" s="53"/>
-      <c r="Z3" s="53"/>
-      <c r="AA3" s="53"/>
-      <c r="AB3" s="53"/>
-      <c r="AC3" s="53"/>
-      <c r="AD3" s="53"/>
-      <c r="AE3" s="54"/>
-      <c r="AF3" s="58"/>
-      <c r="AG3" s="59"/>
-      <c r="AH3" s="59"/>
-      <c r="AI3" s="59"/>
-      <c r="AJ3" s="60"/>
-      <c r="AK3" s="52"/>
-      <c r="AL3" s="53"/>
-      <c r="AM3" s="53"/>
-      <c r="AN3" s="53"/>
-      <c r="AO3" s="54"/>
-      <c r="AP3" s="58"/>
-      <c r="AQ3" s="59"/>
-      <c r="AR3" s="59"/>
-      <c r="AS3" s="59"/>
-      <c r="AT3" s="60"/>
-      <c r="AU3" s="52"/>
-      <c r="AV3" s="53"/>
-      <c r="AW3" s="53"/>
-      <c r="AX3" s="53"/>
-      <c r="AY3" s="54"/>
+      <c r="A3" s="69"/>
+      <c r="B3" s="70"/>
+      <c r="C3" s="70"/>
+      <c r="D3" s="70"/>
+      <c r="E3" s="71"/>
+      <c r="F3" s="75"/>
+      <c r="G3" s="76"/>
+      <c r="H3" s="76"/>
+      <c r="I3" s="76"/>
+      <c r="J3" s="77"/>
+      <c r="K3" s="54"/>
+      <c r="L3" s="55"/>
+      <c r="M3" s="55"/>
+      <c r="N3" s="55"/>
+      <c r="O3" s="55"/>
+      <c r="P3" s="55"/>
+      <c r="Q3" s="55"/>
+      <c r="R3" s="55"/>
+      <c r="S3" s="55"/>
+      <c r="T3" s="55"/>
+      <c r="U3" s="55"/>
+      <c r="V3" s="55"/>
+      <c r="W3" s="55"/>
+      <c r="X3" s="55"/>
+      <c r="Y3" s="55"/>
+      <c r="Z3" s="55"/>
+      <c r="AA3" s="55"/>
+      <c r="AB3" s="55"/>
+      <c r="AC3" s="55"/>
+      <c r="AD3" s="55"/>
+      <c r="AE3" s="56"/>
+      <c r="AF3" s="60"/>
+      <c r="AG3" s="61"/>
+      <c r="AH3" s="61"/>
+      <c r="AI3" s="61"/>
+      <c r="AJ3" s="62"/>
+      <c r="AK3" s="54"/>
+      <c r="AL3" s="55"/>
+      <c r="AM3" s="55"/>
+      <c r="AN3" s="55"/>
+      <c r="AO3" s="56"/>
+      <c r="AP3" s="60"/>
+      <c r="AQ3" s="61"/>
+      <c r="AR3" s="61"/>
+      <c r="AS3" s="61"/>
+      <c r="AT3" s="62"/>
+      <c r="AU3" s="54"/>
+      <c r="AV3" s="55"/>
+      <c r="AW3" s="55"/>
+      <c r="AX3" s="55"/>
+      <c r="AY3" s="56"/>
       <c r="BB3" s="2"/>
     </row>
     <row r="4" spans="1:54" ht="15" customHeight="1">
@@ -3595,92 +4191,92 @@
       <c r="A6" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="76" t="s">
+      <c r="B6" s="78" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="83" t="s">
+      <c r="C6" s="85" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="83" t="s">
+      <c r="D6" s="85" t="s">
         <v>15</v>
       </c>
-      <c r="E6" s="83" t="s">
+      <c r="E6" s="85" t="s">
         <v>15</v>
       </c>
-      <c r="F6" s="83" t="s">
+      <c r="F6" s="85" t="s">
         <v>15</v>
       </c>
-      <c r="G6" s="83" t="s">
+      <c r="G6" s="85" t="s">
         <v>15</v>
       </c>
-      <c r="H6" s="77" t="s">
+      <c r="H6" s="79" t="s">
         <v>15</v>
       </c>
-      <c r="I6" s="84" t="s">
+      <c r="I6" s="86" t="s">
         <v>21</v>
       </c>
-      <c r="J6" s="85" t="s">
+      <c r="J6" s="87" t="s">
         <v>16</v>
       </c>
-      <c r="K6" s="85" t="s">
+      <c r="K6" s="87" t="s">
         <v>16</v>
       </c>
-      <c r="L6" s="85" t="s">
+      <c r="L6" s="87" t="s">
         <v>16</v>
       </c>
-      <c r="M6" s="85" t="s">
+      <c r="M6" s="87" t="s">
         <v>16</v>
       </c>
-      <c r="N6" s="85" t="s">
+      <c r="N6" s="87" t="s">
         <v>16</v>
       </c>
-      <c r="O6" s="85" t="s">
+      <c r="O6" s="87" t="s">
         <v>16</v>
       </c>
-      <c r="P6" s="85" t="s">
+      <c r="P6" s="87" t="s">
         <v>16</v>
       </c>
-      <c r="Q6" s="76" t="s">
+      <c r="Q6" s="78" t="s">
         <v>22</v>
       </c>
-      <c r="R6" s="77"/>
-      <c r="S6" s="78" t="s">
+      <c r="R6" s="79"/>
+      <c r="S6" s="80" t="s">
         <v>24</v>
       </c>
-      <c r="T6" s="79"/>
-      <c r="U6" s="79"/>
-      <c r="V6" s="79"/>
-      <c r="W6" s="79"/>
-      <c r="X6" s="79"/>
-      <c r="Y6" s="79"/>
-      <c r="Z6" s="79"/>
-      <c r="AA6" s="79"/>
-      <c r="AB6" s="79"/>
-      <c r="AC6" s="79"/>
-      <c r="AD6" s="79"/>
-      <c r="AE6" s="79"/>
-      <c r="AF6" s="79"/>
-      <c r="AG6" s="79"/>
-      <c r="AH6" s="79"/>
-      <c r="AI6" s="79"/>
-      <c r="AJ6" s="79"/>
-      <c r="AK6" s="79"/>
-      <c r="AL6" s="79"/>
-      <c r="AM6" s="79"/>
-      <c r="AN6" s="79"/>
-      <c r="AO6" s="79"/>
-      <c r="AP6" s="80"/>
-      <c r="AQ6" s="76" t="s">
+      <c r="T6" s="81"/>
+      <c r="U6" s="81"/>
+      <c r="V6" s="81"/>
+      <c r="W6" s="81"/>
+      <c r="X6" s="81"/>
+      <c r="Y6" s="81"/>
+      <c r="Z6" s="81"/>
+      <c r="AA6" s="81"/>
+      <c r="AB6" s="81"/>
+      <c r="AC6" s="81"/>
+      <c r="AD6" s="81"/>
+      <c r="AE6" s="81"/>
+      <c r="AF6" s="81"/>
+      <c r="AG6" s="81"/>
+      <c r="AH6" s="81"/>
+      <c r="AI6" s="81"/>
+      <c r="AJ6" s="81"/>
+      <c r="AK6" s="81"/>
+      <c r="AL6" s="81"/>
+      <c r="AM6" s="81"/>
+      <c r="AN6" s="81"/>
+      <c r="AO6" s="81"/>
+      <c r="AP6" s="82"/>
+      <c r="AQ6" s="78" t="s">
         <v>14</v>
       </c>
-      <c r="AR6" s="83"/>
-      <c r="AS6" s="83"/>
-      <c r="AT6" s="83"/>
-      <c r="AU6" s="83"/>
-      <c r="AV6" s="83"/>
-      <c r="AW6" s="83"/>
-      <c r="AX6" s="83"/>
-      <c r="AY6" s="77"/>
+      <c r="AR6" s="85"/>
+      <c r="AS6" s="85"/>
+      <c r="AT6" s="85"/>
+      <c r="AU6" s="85"/>
+      <c r="AV6" s="85"/>
+      <c r="AW6" s="85"/>
+      <c r="AX6" s="85"/>
+      <c r="AY6" s="79"/>
     </row>
     <row r="7" spans="1:53" ht="17" customHeight="1">
       <c r="A7" s="34">
@@ -3706,10 +4302,10 @@
       <c r="N7" s="35"/>
       <c r="O7" s="35"/>
       <c r="P7" s="36"/>
-      <c r="Q7" s="81" t="s">
+      <c r="Q7" s="83" t="s">
         <v>47</v>
       </c>
-      <c r="R7" s="82"/>
+      <c r="R7" s="84"/>
       <c r="S7" s="35" t="s">
         <v>48</v>
       </c>
@@ -4723,7 +5319,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8357493-1BF8-4D4D-945D-8453AECFBF31}">
-  <dimension ref="A1:BC29"/>
+  <dimension ref="A1:BC96"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="4.33203125" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="16384" width="4.33203125" style="18"/>
@@ -4735,126 +5331,126 @@
       </c>
     </row>
     <row r="2" spans="1:55">
-      <c r="B2" s="76" t="s">
+      <c r="B2" s="78" t="s">
         <v>27</v>
       </c>
-      <c r="C2" s="83" t="s">
+      <c r="C2" s="85" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="83" t="s">
+      <c r="D2" s="85" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="83" t="s">
+      <c r="E2" s="85" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="83" t="s">
+      <c r="F2" s="85" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="77" t="s">
+      <c r="G2" s="79" t="s">
         <v>15</v>
       </c>
-      <c r="H2" s="86">
+      <c r="H2" s="88">
         <v>45459</v>
       </c>
-      <c r="I2" s="87"/>
-      <c r="J2" s="87"/>
-      <c r="K2" s="87"/>
-      <c r="L2" s="87"/>
-      <c r="M2" s="88"/>
-      <c r="N2" s="76" t="s">
+      <c r="I2" s="89"/>
+      <c r="J2" s="89"/>
+      <c r="K2" s="89"/>
+      <c r="L2" s="89"/>
+      <c r="M2" s="90"/>
+      <c r="N2" s="78" t="s">
         <v>26</v>
       </c>
-      <c r="O2" s="83" t="s">
+      <c r="O2" s="85" t="s">
         <v>15</v>
       </c>
-      <c r="P2" s="83" t="s">
+      <c r="P2" s="85" t="s">
         <v>15</v>
       </c>
-      <c r="Q2" s="83" t="s">
+      <c r="Q2" s="85" t="s">
         <v>15</v>
       </c>
-      <c r="R2" s="83" t="s">
+      <c r="R2" s="85" t="s">
         <v>15</v>
       </c>
-      <c r="S2" s="77" t="s">
+      <c r="S2" s="79" t="s">
         <v>15</v>
       </c>
-      <c r="T2" s="89" t="s">
+      <c r="T2" s="91" t="s">
         <v>45</v>
       </c>
-      <c r="U2" s="87"/>
-      <c r="V2" s="87"/>
-      <c r="W2" s="87"/>
-      <c r="X2" s="87"/>
-      <c r="Y2" s="88"/>
+      <c r="U2" s="89"/>
+      <c r="V2" s="89"/>
+      <c r="W2" s="89"/>
+      <c r="X2" s="89"/>
+      <c r="Y2" s="90"/>
     </row>
     <row r="3" spans="1:55">
-      <c r="B3" s="84" t="s">
+      <c r="B3" s="86" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="85" t="s">
+      <c r="C3" s="87" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="85" t="s">
+      <c r="D3" s="87" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="85" t="s">
+      <c r="E3" s="87" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="85" t="s">
+      <c r="F3" s="87" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="85" t="s">
+      <c r="G3" s="87" t="s">
         <v>16</v>
       </c>
-      <c r="H3" s="90"/>
-      <c r="I3" s="91"/>
-      <c r="J3" s="91"/>
-      <c r="K3" s="91"/>
-      <c r="L3" s="91"/>
-      <c r="M3" s="91"/>
-      <c r="N3" s="84" t="s">
+      <c r="H3" s="92"/>
+      <c r="I3" s="93"/>
+      <c r="J3" s="93"/>
+      <c r="K3" s="93"/>
+      <c r="L3" s="93"/>
+      <c r="M3" s="93"/>
+      <c r="N3" s="86" t="s">
         <v>29</v>
       </c>
-      <c r="O3" s="85" t="s">
+      <c r="O3" s="87" t="s">
         <v>16</v>
       </c>
-      <c r="P3" s="85" t="s">
+      <c r="P3" s="87" t="s">
         <v>16</v>
       </c>
-      <c r="Q3" s="85" t="s">
+      <c r="Q3" s="87" t="s">
         <v>16</v>
       </c>
-      <c r="R3" s="85" t="s">
+      <c r="R3" s="87" t="s">
         <v>16</v>
       </c>
-      <c r="S3" s="85" t="s">
+      <c r="S3" s="87" t="s">
         <v>16</v>
       </c>
-      <c r="T3" s="90"/>
-      <c r="U3" s="91"/>
-      <c r="V3" s="91"/>
-      <c r="W3" s="91"/>
-      <c r="X3" s="91"/>
-      <c r="Y3" s="92"/>
+      <c r="T3" s="92"/>
+      <c r="U3" s="93"/>
+      <c r="V3" s="93"/>
+      <c r="W3" s="93"/>
+      <c r="X3" s="93"/>
+      <c r="Y3" s="94"/>
     </row>
     <row r="4" spans="1:55">
-      <c r="B4" s="93" t="s">
+      <c r="B4" s="95" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="94" t="s">
+      <c r="C4" s="96" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="94" t="s">
+      <c r="D4" s="96" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="94" t="s">
+      <c r="E4" s="96" t="s">
         <v>15</v>
       </c>
-      <c r="F4" s="94" t="s">
+      <c r="F4" s="96" t="s">
         <v>15</v>
       </c>
-      <c r="G4" s="95" t="s">
+      <c r="G4" s="97" t="s">
         <v>15</v>
       </c>
       <c r="H4" s="19" t="str">
@@ -4880,22 +5476,22 @@
       <c r="Y4" s="21"/>
     </row>
     <row r="5" spans="1:55">
-      <c r="B5" s="84" t="s">
+      <c r="B5" s="86" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="85" t="s">
+      <c r="C5" s="87" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="85" t="s">
+      <c r="D5" s="87" t="s">
         <v>16</v>
       </c>
-      <c r="E5" s="85" t="s">
+      <c r="E5" s="87" t="s">
         <v>16</v>
       </c>
-      <c r="F5" s="85" t="s">
+      <c r="F5" s="87" t="s">
         <v>16</v>
       </c>
-      <c r="G5" s="85" t="s">
+      <c r="G5" s="87" t="s">
         <v>16</v>
       </c>
       <c r="H5" s="22" t="str">
@@ -4921,86 +5517,86 @@
       <c r="Y5" s="24"/>
     </row>
     <row r="6" spans="1:55">
-      <c r="B6" s="76" t="s">
+      <c r="B6" s="78" t="s">
         <v>30</v>
       </c>
-      <c r="C6" s="83"/>
-      <c r="D6" s="83"/>
-      <c r="E6" s="83"/>
-      <c r="F6" s="83"/>
-      <c r="G6" s="77"/>
-      <c r="H6" s="102" t="s">
+      <c r="C6" s="85"/>
+      <c r="D6" s="85"/>
+      <c r="E6" s="85"/>
+      <c r="F6" s="85"/>
+      <c r="G6" s="79"/>
+      <c r="H6" s="104" t="s">
         <v>50</v>
       </c>
-      <c r="I6" s="103"/>
-      <c r="J6" s="103"/>
-      <c r="K6" s="103"/>
-      <c r="L6" s="103"/>
-      <c r="M6" s="103"/>
-      <c r="N6" s="103"/>
-      <c r="O6" s="103"/>
-      <c r="P6" s="103"/>
-      <c r="Q6" s="103"/>
-      <c r="R6" s="103"/>
-      <c r="S6" s="103"/>
-      <c r="T6" s="103"/>
-      <c r="U6" s="103"/>
-      <c r="V6" s="103"/>
-      <c r="W6" s="103"/>
-      <c r="X6" s="103"/>
-      <c r="Y6" s="104"/>
+      <c r="I6" s="105"/>
+      <c r="J6" s="105"/>
+      <c r="K6" s="105"/>
+      <c r="L6" s="105"/>
+      <c r="M6" s="105"/>
+      <c r="N6" s="105"/>
+      <c r="O6" s="105"/>
+      <c r="P6" s="105"/>
+      <c r="Q6" s="105"/>
+      <c r="R6" s="105"/>
+      <c r="S6" s="105"/>
+      <c r="T6" s="105"/>
+      <c r="U6" s="105"/>
+      <c r="V6" s="105"/>
+      <c r="W6" s="105"/>
+      <c r="X6" s="105"/>
+      <c r="Y6" s="106"/>
     </row>
     <row r="7" spans="1:55">
-      <c r="B7" s="96"/>
-      <c r="C7" s="97"/>
-      <c r="D7" s="97"/>
-      <c r="E7" s="97"/>
-      <c r="F7" s="97"/>
-      <c r="G7" s="98"/>
-      <c r="H7" s="105"/>
-      <c r="I7" s="106"/>
-      <c r="J7" s="106"/>
-      <c r="K7" s="106"/>
-      <c r="L7" s="106"/>
-      <c r="M7" s="106"/>
-      <c r="N7" s="106"/>
-      <c r="O7" s="106"/>
-      <c r="P7" s="106"/>
-      <c r="Q7" s="106"/>
-      <c r="R7" s="106"/>
-      <c r="S7" s="106"/>
-      <c r="T7" s="106"/>
-      <c r="U7" s="106"/>
-      <c r="V7" s="106"/>
-      <c r="W7" s="106"/>
-      <c r="X7" s="106"/>
-      <c r="Y7" s="107"/>
+      <c r="B7" s="98"/>
+      <c r="C7" s="99"/>
+      <c r="D7" s="99"/>
+      <c r="E7" s="99"/>
+      <c r="F7" s="99"/>
+      <c r="G7" s="100"/>
+      <c r="H7" s="107"/>
+      <c r="I7" s="108"/>
+      <c r="J7" s="108"/>
+      <c r="K7" s="108"/>
+      <c r="L7" s="108"/>
+      <c r="M7" s="108"/>
+      <c r="N7" s="108"/>
+      <c r="O7" s="108"/>
+      <c r="P7" s="108"/>
+      <c r="Q7" s="108"/>
+      <c r="R7" s="108"/>
+      <c r="S7" s="108"/>
+      <c r="T7" s="108"/>
+      <c r="U7" s="108"/>
+      <c r="V7" s="108"/>
+      <c r="W7" s="108"/>
+      <c r="X7" s="108"/>
+      <c r="Y7" s="109"/>
     </row>
     <row r="8" spans="1:55">
-      <c r="B8" s="99"/>
-      <c r="C8" s="100"/>
-      <c r="D8" s="100"/>
-      <c r="E8" s="100"/>
-      <c r="F8" s="100"/>
-      <c r="G8" s="101"/>
-      <c r="H8" s="108"/>
-      <c r="I8" s="109"/>
-      <c r="J8" s="109"/>
-      <c r="K8" s="109"/>
-      <c r="L8" s="109"/>
-      <c r="M8" s="109"/>
-      <c r="N8" s="109"/>
-      <c r="O8" s="109"/>
-      <c r="P8" s="109"/>
-      <c r="Q8" s="109"/>
-      <c r="R8" s="109"/>
-      <c r="S8" s="109"/>
-      <c r="T8" s="109"/>
-      <c r="U8" s="109"/>
-      <c r="V8" s="109"/>
-      <c r="W8" s="109"/>
-      <c r="X8" s="109"/>
-      <c r="Y8" s="110"/>
+      <c r="B8" s="101"/>
+      <c r="C8" s="102"/>
+      <c r="D8" s="102"/>
+      <c r="E8" s="102"/>
+      <c r="F8" s="102"/>
+      <c r="G8" s="103"/>
+      <c r="H8" s="110"/>
+      <c r="I8" s="111"/>
+      <c r="J8" s="111"/>
+      <c r="K8" s="111"/>
+      <c r="L8" s="111"/>
+      <c r="M8" s="111"/>
+      <c r="N8" s="111"/>
+      <c r="O8" s="111"/>
+      <c r="P8" s="111"/>
+      <c r="Q8" s="111"/>
+      <c r="R8" s="111"/>
+      <c r="S8" s="111"/>
+      <c r="T8" s="111"/>
+      <c r="U8" s="111"/>
+      <c r="V8" s="111"/>
+      <c r="W8" s="111"/>
+      <c r="X8" s="111"/>
+      <c r="Y8" s="112"/>
     </row>
     <row r="10" spans="1:55" ht="20">
       <c r="A10" s="41" t="s">
@@ -5083,7 +5679,7 @@
     </row>
     <row r="12" spans="1:55">
       <c r="B12" s="39">
-        <f>ROW()-11</f>
+        <f t="shared" ref="B12:B92" si="0">ROW()-11</f>
         <v>1</v>
       </c>
       <c r="C12" s="19" t="s">
@@ -5097,8 +5693,8 @@
       <c r="I12" s="20"/>
       <c r="J12" s="20"/>
       <c r="K12" s="21"/>
-      <c r="L12" s="19" t="s">
-        <v>75</v>
+      <c r="L12" s="118" t="s">
+        <v>51</v>
       </c>
       <c r="M12" s="20"/>
       <c r="N12" s="20"/>
@@ -5109,34 +5705,34 @@
       <c r="S12" s="20"/>
       <c r="T12" s="21"/>
       <c r="U12" s="19" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="V12" s="20"/>
       <c r="W12" s="20"/>
       <c r="X12" s="20"/>
       <c r="Y12" s="20"/>
       <c r="Z12" s="21"/>
-      <c r="AA12" s="111" t="s">
-        <v>69</v>
-      </c>
-      <c r="AB12" s="112"/>
-      <c r="AC12" s="111" t="s">
-        <v>69</v>
-      </c>
-      <c r="AD12" s="112"/>
-      <c r="AE12" s="111" t="s">
-        <v>69</v>
-      </c>
-      <c r="AF12" s="112"/>
+      <c r="AA12" s="113" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB12" s="114"/>
+      <c r="AC12" s="113" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD12" s="114"/>
+      <c r="AE12" s="113" t="s">
+        <v>68</v>
+      </c>
+      <c r="AF12" s="114"/>
       <c r="AG12" s="19" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AH12" s="20"/>
       <c r="AI12" s="20"/>
       <c r="AJ12" s="20"/>
       <c r="AK12" s="21"/>
-      <c r="AL12" s="19" t="s">
-        <v>71</v>
+      <c r="AL12" s="42" t="s">
+        <v>69</v>
       </c>
       <c r="AM12" s="20"/>
       <c r="AN12" s="20"/>
@@ -5158,11 +5754,11 @@
     </row>
     <row r="13" spans="1:55">
       <c r="B13" s="39">
-        <f t="shared" ref="B13:B25" si="0">ROW()-11</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="D13" s="20"/>
       <c r="E13" s="20"/>
@@ -5173,7 +5769,7 @@
       <c r="J13" s="20"/>
       <c r="K13" s="21"/>
       <c r="L13" s="19" t="s">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="M13" s="20"/>
       <c r="N13" s="20"/>
@@ -5184,34 +5780,34 @@
       <c r="S13" s="20"/>
       <c r="T13" s="21"/>
       <c r="U13" s="19" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="V13" s="20"/>
       <c r="W13" s="20"/>
       <c r="X13" s="20"/>
       <c r="Y13" s="20"/>
       <c r="Z13" s="21"/>
-      <c r="AA13" s="111" t="s">
-        <v>70</v>
-      </c>
-      <c r="AB13" s="112"/>
-      <c r="AC13" s="111" t="s">
-        <v>70</v>
-      </c>
-      <c r="AD13" s="112"/>
-      <c r="AE13" s="111" t="s">
-        <v>69</v>
-      </c>
-      <c r="AF13" s="112"/>
+      <c r="AA13" s="113" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB13" s="114"/>
+      <c r="AC13" s="113" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD13" s="114"/>
+      <c r="AE13" s="115" t="s">
+        <v>69</v>
+      </c>
+      <c r="AF13" s="116"/>
       <c r="AG13" s="19" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AH13" s="20"/>
       <c r="AI13" s="20"/>
       <c r="AJ13" s="20"/>
       <c r="AK13" s="21"/>
       <c r="AL13" s="42" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AM13" s="20"/>
       <c r="AN13" s="20"/>
@@ -5237,7 +5833,7 @@
         <v>3</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D14" s="20"/>
       <c r="E14" s="20"/>
@@ -5248,7 +5844,7 @@
       <c r="J14" s="20"/>
       <c r="K14" s="21"/>
       <c r="L14" s="19" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="M14" s="20"/>
       <c r="N14" s="20"/>
@@ -5259,34 +5855,34 @@
       <c r="S14" s="20"/>
       <c r="T14" s="21"/>
       <c r="U14" s="19" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="V14" s="20"/>
       <c r="W14" s="20"/>
       <c r="X14" s="20"/>
       <c r="Y14" s="20"/>
       <c r="Z14" s="21"/>
-      <c r="AA14" s="111" t="s">
-        <v>70</v>
-      </c>
-      <c r="AB14" s="112"/>
-      <c r="AC14" s="111" t="s">
-        <v>70</v>
-      </c>
-      <c r="AD14" s="112"/>
-      <c r="AE14" s="111" t="s">
-        <v>69</v>
-      </c>
-      <c r="AF14" s="112"/>
+      <c r="AA14" s="113" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB14" s="114"/>
+      <c r="AC14" s="113" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD14" s="114"/>
+      <c r="AE14" s="113" t="s">
+        <v>68</v>
+      </c>
+      <c r="AF14" s="114"/>
       <c r="AG14" s="19" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AH14" s="20"/>
       <c r="AI14" s="20"/>
       <c r="AJ14" s="20"/>
       <c r="AK14" s="21"/>
       <c r="AL14" s="42" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AM14" s="20"/>
       <c r="AN14" s="20"/>
@@ -5308,11 +5904,11 @@
     </row>
     <row r="15" spans="1:55">
       <c r="B15" s="39">
-        <f t="shared" si="0"/>
+        <f>ROW()-11</f>
         <v>4</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="D15" s="20"/>
       <c r="E15" s="20"/>
@@ -5323,7 +5919,7 @@
       <c r="J15" s="20"/>
       <c r="K15" s="21"/>
       <c r="L15" s="19" t="s">
-        <v>51</v>
+        <v>86</v>
       </c>
       <c r="M15" s="20"/>
       <c r="N15" s="20"/>
@@ -5334,33 +5930,33 @@
       <c r="S15" s="20"/>
       <c r="T15" s="21"/>
       <c r="U15" s="19" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="V15" s="20"/>
       <c r="W15" s="20"/>
       <c r="X15" s="20"/>
       <c r="Y15" s="20"/>
       <c r="Z15" s="21"/>
-      <c r="AA15" s="111" t="s">
-        <v>70</v>
-      </c>
-      <c r="AB15" s="112"/>
-      <c r="AC15" s="111" t="s">
-        <v>70</v>
-      </c>
-      <c r="AD15" s="112"/>
-      <c r="AE15" s="111" t="s">
-        <v>69</v>
-      </c>
-      <c r="AF15" s="112"/>
+      <c r="AA15" s="113" t="s">
+        <v>68</v>
+      </c>
+      <c r="AB15" s="114"/>
+      <c r="AC15" s="113" t="s">
+        <v>68</v>
+      </c>
+      <c r="AD15" s="114"/>
+      <c r="AE15" s="113" t="s">
+        <v>68</v>
+      </c>
+      <c r="AF15" s="114"/>
       <c r="AG15" s="19" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AH15" s="20"/>
       <c r="AI15" s="20"/>
       <c r="AJ15" s="20"/>
       <c r="AK15" s="21"/>
-      <c r="AL15" s="42" t="s">
+      <c r="AL15" s="19" t="s">
         <v>70</v>
       </c>
       <c r="AM15" s="20"/>
@@ -5387,7 +5983,7 @@
         <v>5</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D16" s="20"/>
       <c r="E16" s="20"/>
@@ -5398,7 +5994,7 @@
       <c r="J16" s="20"/>
       <c r="K16" s="21"/>
       <c r="L16" s="19" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M16" s="20"/>
       <c r="N16" s="20"/>
@@ -5409,34 +6005,34 @@
       <c r="S16" s="20"/>
       <c r="T16" s="21"/>
       <c r="U16" s="19" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="V16" s="20"/>
       <c r="W16" s="20"/>
       <c r="X16" s="20"/>
       <c r="Y16" s="20"/>
       <c r="Z16" s="21"/>
-      <c r="AA16" s="111" t="s">
-        <v>70</v>
-      </c>
-      <c r="AB16" s="112"/>
-      <c r="AC16" s="111" t="s">
-        <v>70</v>
-      </c>
-      <c r="AD16" s="112"/>
-      <c r="AE16" s="111" t="s">
-        <v>70</v>
-      </c>
-      <c r="AF16" s="112"/>
+      <c r="AA16" s="113" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB16" s="114"/>
+      <c r="AC16" s="113" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD16" s="114"/>
+      <c r="AE16" s="113" t="s">
+        <v>68</v>
+      </c>
+      <c r="AF16" s="114"/>
       <c r="AG16" s="19" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AH16" s="20"/>
       <c r="AI16" s="20"/>
       <c r="AJ16" s="20"/>
       <c r="AK16" s="21"/>
       <c r="AL16" s="42" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AM16" s="20"/>
       <c r="AN16" s="20"/>
@@ -5456,13 +6052,13 @@
       <c r="BB16" s="20"/>
       <c r="BC16" s="21"/>
     </row>
-    <row r="17" spans="1:55">
+    <row r="17" spans="2:55">
       <c r="B17" s="39">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="C17" s="19" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D17" s="20"/>
       <c r="E17" s="20"/>
@@ -5473,7 +6069,7 @@
       <c r="J17" s="20"/>
       <c r="K17" s="21"/>
       <c r="L17" s="19" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="M17" s="20"/>
       <c r="N17" s="20"/>
@@ -5484,34 +6080,34 @@
       <c r="S17" s="20"/>
       <c r="T17" s="21"/>
       <c r="U17" s="19" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="V17" s="20"/>
       <c r="W17" s="20"/>
       <c r="X17" s="20"/>
       <c r="Y17" s="20"/>
       <c r="Z17" s="21"/>
-      <c r="AA17" s="111" t="s">
-        <v>70</v>
-      </c>
-      <c r="AB17" s="112"/>
-      <c r="AC17" s="111" t="s">
-        <v>70</v>
-      </c>
-      <c r="AD17" s="112"/>
-      <c r="AE17" s="113" t="s">
-        <v>70</v>
-      </c>
-      <c r="AF17" s="114"/>
+      <c r="AA17" s="113" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB17" s="114"/>
+      <c r="AC17" s="113" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD17" s="114"/>
+      <c r="AE17" s="115" t="s">
+        <v>69</v>
+      </c>
+      <c r="AF17" s="116"/>
       <c r="AG17" s="19" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AH17" s="20"/>
       <c r="AI17" s="20"/>
       <c r="AJ17" s="20"/>
       <c r="AK17" s="21"/>
       <c r="AL17" s="42" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AM17" s="20"/>
       <c r="AN17" s="20"/>
@@ -5531,13 +6127,13 @@
       <c r="BB17" s="20"/>
       <c r="BC17" s="21"/>
     </row>
-    <row r="18" spans="1:55">
+    <row r="18" spans="2:55">
       <c r="B18" s="39">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D18" s="20"/>
       <c r="E18" s="20"/>
@@ -5548,7 +6144,7 @@
       <c r="J18" s="20"/>
       <c r="K18" s="21"/>
       <c r="L18" s="19" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="M18" s="20"/>
       <c r="N18" s="20"/>
@@ -5559,34 +6155,34 @@
       <c r="S18" s="20"/>
       <c r="T18" s="21"/>
       <c r="U18" s="19" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="V18" s="20"/>
       <c r="W18" s="20"/>
       <c r="X18" s="20"/>
       <c r="Y18" s="20"/>
       <c r="Z18" s="21"/>
-      <c r="AA18" s="111" t="s">
-        <v>70</v>
-      </c>
-      <c r="AB18" s="112"/>
-      <c r="AC18" s="111" t="s">
-        <v>70</v>
-      </c>
-      <c r="AD18" s="112"/>
-      <c r="AE18" s="113" t="s">
-        <v>70</v>
-      </c>
-      <c r="AF18" s="114"/>
+      <c r="AA18" s="113" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB18" s="114"/>
+      <c r="AC18" s="113" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD18" s="114"/>
+      <c r="AE18" s="115" t="s">
+        <v>69</v>
+      </c>
+      <c r="AF18" s="116"/>
       <c r="AG18" s="19" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AH18" s="20"/>
       <c r="AI18" s="20"/>
       <c r="AJ18" s="20"/>
       <c r="AK18" s="21"/>
       <c r="AL18" s="42" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AM18" s="20"/>
       <c r="AN18" s="20"/>
@@ -5606,13 +6202,13 @@
       <c r="BB18" s="20"/>
       <c r="BC18" s="21"/>
     </row>
-    <row r="19" spans="1:55">
+    <row r="19" spans="2:55">
       <c r="B19" s="39">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>73</v>
+        <v>56</v>
       </c>
       <c r="D19" s="20"/>
       <c r="E19" s="20"/>
@@ -5623,7 +6219,7 @@
       <c r="J19" s="20"/>
       <c r="K19" s="21"/>
       <c r="L19" s="19" t="s">
-        <v>74</v>
+        <v>52</v>
       </c>
       <c r="M19" s="20"/>
       <c r="N19" s="20"/>
@@ -5634,34 +6230,34 @@
       <c r="S19" s="20"/>
       <c r="T19" s="21"/>
       <c r="U19" s="19" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="V19" s="20"/>
       <c r="W19" s="20"/>
       <c r="X19" s="20"/>
       <c r="Y19" s="20"/>
       <c r="Z19" s="21"/>
-      <c r="AA19" s="111" t="s">
-        <v>70</v>
-      </c>
-      <c r="AB19" s="112"/>
-      <c r="AC19" s="111" t="s">
-        <v>70</v>
-      </c>
-      <c r="AD19" s="112"/>
+      <c r="AA19" s="113" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB19" s="114"/>
+      <c r="AC19" s="113" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD19" s="114"/>
       <c r="AE19" s="113" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AF19" s="114"/>
       <c r="AG19" s="19" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AH19" s="20"/>
       <c r="AI19" s="20"/>
       <c r="AJ19" s="20"/>
       <c r="AK19" s="21"/>
       <c r="AL19" s="42" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AM19" s="20"/>
       <c r="AN19" s="20"/>
@@ -5681,12 +6277,14 @@
       <c r="BB19" s="20"/>
       <c r="BC19" s="21"/>
     </row>
-    <row r="20" spans="1:55">
+    <row r="20" spans="2:55">
       <c r="B20" s="39">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="C20" s="19"/>
+      <c r="C20" s="119" t="s">
+        <v>107</v>
+      </c>
       <c r="D20" s="20"/>
       <c r="E20" s="20"/>
       <c r="F20" s="20"/>
@@ -5695,7 +6293,9 @@
       <c r="I20" s="20"/>
       <c r="J20" s="20"/>
       <c r="K20" s="21"/>
-      <c r="L20" s="19"/>
+      <c r="L20" s="119" t="s">
+        <v>106</v>
+      </c>
       <c r="M20" s="20"/>
       <c r="N20" s="20"/>
       <c r="O20" s="20"/>
@@ -5704,18 +6304,6636 @@
       <c r="R20" s="20"/>
       <c r="S20" s="20"/>
       <c r="T20" s="21"/>
-      <c r="U20" s="19"/>
-      <c r="V20" s="20"/>
-      <c r="W20" s="20"/>
-      <c r="X20" s="20"/>
-      <c r="Y20" s="20"/>
-      <c r="Z20" s="21"/>
-      <c r="AA20" s="111"/>
-      <c r="AB20" s="112"/>
-      <c r="AC20" s="111"/>
-      <c r="AD20" s="112"/>
-      <c r="AE20" s="111"/>
-      <c r="AF20" s="112"/>
+      <c r="U20" s="120" t="s">
+        <v>82</v>
+      </c>
+      <c r="V20" s="121"/>
+      <c r="W20" s="121"/>
+      <c r="X20" s="121"/>
+      <c r="Y20" s="121"/>
+      <c r="Z20" s="122"/>
+      <c r="AA20" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB20" s="124"/>
+      <c r="AC20" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD20" s="124"/>
+      <c r="AE20" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AF20" s="124"/>
+      <c r="AG20" s="120" t="s">
+        <v>71</v>
+      </c>
+      <c r="AH20" s="121"/>
+      <c r="AI20" s="121"/>
+      <c r="AJ20" s="121"/>
+      <c r="AK20" s="122"/>
+      <c r="AL20" s="120" t="s">
+        <v>69</v>
+      </c>
+      <c r="AM20" s="20"/>
+      <c r="AN20" s="20"/>
+      <c r="AO20" s="20"/>
+      <c r="AP20" s="20"/>
+      <c r="AQ20" s="20"/>
+      <c r="AR20" s="20"/>
+      <c r="AS20" s="20"/>
+      <c r="AT20" s="20"/>
+      <c r="AU20" s="20"/>
+      <c r="AV20" s="20"/>
+      <c r="AW20" s="20"/>
+      <c r="AX20" s="20"/>
+      <c r="AY20" s="20"/>
+      <c r="AZ20" s="20"/>
+      <c r="BA20" s="20"/>
+      <c r="BB20" s="20"/>
+      <c r="BC20" s="21"/>
+    </row>
+    <row r="21" spans="2:55">
+      <c r="B21" s="39">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="C21" s="119" t="s">
+        <v>125</v>
+      </c>
+      <c r="D21" s="20"/>
+      <c r="E21" s="20"/>
+      <c r="F21" s="20"/>
+      <c r="G21" s="20"/>
+      <c r="H21" s="20"/>
+      <c r="I21" s="20"/>
+      <c r="J21" s="20"/>
+      <c r="K21" s="21"/>
+      <c r="L21" s="119" t="s">
+        <v>183</v>
+      </c>
+      <c r="M21" s="20"/>
+      <c r="N21" s="20"/>
+      <c r="O21" s="20"/>
+      <c r="P21" s="20"/>
+      <c r="Q21" s="20"/>
+      <c r="R21" s="20"/>
+      <c r="S21" s="20"/>
+      <c r="T21" s="21"/>
+      <c r="U21" s="120" t="s">
+        <v>82</v>
+      </c>
+      <c r="V21" s="121"/>
+      <c r="W21" s="121"/>
+      <c r="X21" s="121"/>
+      <c r="Y21" s="121"/>
+      <c r="Z21" s="122"/>
+      <c r="AA21" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB21" s="124"/>
+      <c r="AC21" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD21" s="124"/>
+      <c r="AE21" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AF21" s="124"/>
+      <c r="AG21" s="120" t="s">
+        <v>71</v>
+      </c>
+      <c r="AH21" s="121"/>
+      <c r="AI21" s="121"/>
+      <c r="AJ21" s="121"/>
+      <c r="AK21" s="122"/>
+      <c r="AL21" s="120" t="s">
+        <v>69</v>
+      </c>
+      <c r="AM21" s="20"/>
+      <c r="AN21" s="20"/>
+      <c r="AO21" s="20"/>
+      <c r="AP21" s="20"/>
+      <c r="AQ21" s="20"/>
+      <c r="AR21" s="20"/>
+      <c r="AS21" s="20"/>
+      <c r="AT21" s="20"/>
+      <c r="AU21" s="20"/>
+      <c r="AV21" s="20"/>
+      <c r="AW21" s="20"/>
+      <c r="AX21" s="20"/>
+      <c r="AY21" s="20"/>
+      <c r="AZ21" s="20"/>
+      <c r="BA21" s="20"/>
+      <c r="BB21" s="20"/>
+      <c r="BC21" s="21"/>
+    </row>
+    <row r="22" spans="2:55">
+      <c r="B22" s="39">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="C22" s="119" t="s">
+        <v>126</v>
+      </c>
+      <c r="D22" s="20"/>
+      <c r="E22" s="20"/>
+      <c r="F22" s="20"/>
+      <c r="G22" s="20"/>
+      <c r="H22" s="20"/>
+      <c r="I22" s="20"/>
+      <c r="J22" s="20"/>
+      <c r="K22" s="21"/>
+      <c r="L22" s="119" t="s">
+        <v>184</v>
+      </c>
+      <c r="M22" s="20"/>
+      <c r="N22" s="20"/>
+      <c r="O22" s="20"/>
+      <c r="P22" s="20"/>
+      <c r="Q22" s="20"/>
+      <c r="R22" s="20"/>
+      <c r="S22" s="20"/>
+      <c r="T22" s="21"/>
+      <c r="U22" s="120" t="s">
+        <v>82</v>
+      </c>
+      <c r="V22" s="121"/>
+      <c r="W22" s="121"/>
+      <c r="X22" s="121"/>
+      <c r="Y22" s="121"/>
+      <c r="Z22" s="122"/>
+      <c r="AA22" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB22" s="124"/>
+      <c r="AC22" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD22" s="124"/>
+      <c r="AE22" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AF22" s="124"/>
+      <c r="AG22" s="120" t="s">
+        <v>71</v>
+      </c>
+      <c r="AH22" s="121"/>
+      <c r="AI22" s="121"/>
+      <c r="AJ22" s="121"/>
+      <c r="AK22" s="122"/>
+      <c r="AL22" s="120" t="s">
+        <v>69</v>
+      </c>
+      <c r="AM22" s="20"/>
+      <c r="AN22" s="20"/>
+      <c r="AO22" s="20"/>
+      <c r="AP22" s="20"/>
+      <c r="AQ22" s="20"/>
+      <c r="AR22" s="20"/>
+      <c r="AS22" s="20"/>
+      <c r="AT22" s="20"/>
+      <c r="AU22" s="20"/>
+      <c r="AV22" s="20"/>
+      <c r="AW22" s="20"/>
+      <c r="AX22" s="20"/>
+      <c r="AY22" s="20"/>
+      <c r="AZ22" s="20"/>
+      <c r="BA22" s="20"/>
+      <c r="BB22" s="20"/>
+      <c r="BC22" s="21"/>
+    </row>
+    <row r="23" spans="2:55">
+      <c r="B23" s="39">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="C23" s="119" t="s">
+        <v>127</v>
+      </c>
+      <c r="D23" s="20"/>
+      <c r="E23" s="20"/>
+      <c r="F23" s="20"/>
+      <c r="G23" s="20"/>
+      <c r="H23" s="20"/>
+      <c r="I23" s="20"/>
+      <c r="J23" s="20"/>
+      <c r="K23" s="21"/>
+      <c r="L23" s="119" t="s">
+        <v>178</v>
+      </c>
+      <c r="M23" s="20"/>
+      <c r="N23" s="20"/>
+      <c r="O23" s="20"/>
+      <c r="P23" s="20"/>
+      <c r="Q23" s="20"/>
+      <c r="R23" s="20"/>
+      <c r="S23" s="20"/>
+      <c r="T23" s="21"/>
+      <c r="U23" s="120" t="s">
+        <v>82</v>
+      </c>
+      <c r="V23" s="121"/>
+      <c r="W23" s="121"/>
+      <c r="X23" s="121"/>
+      <c r="Y23" s="121"/>
+      <c r="Z23" s="122"/>
+      <c r="AA23" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB23" s="124"/>
+      <c r="AC23" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD23" s="124"/>
+      <c r="AE23" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AF23" s="124"/>
+      <c r="AG23" s="120" t="s">
+        <v>71</v>
+      </c>
+      <c r="AH23" s="121"/>
+      <c r="AI23" s="121"/>
+      <c r="AJ23" s="121"/>
+      <c r="AK23" s="122"/>
+      <c r="AL23" s="120" t="s">
+        <v>69</v>
+      </c>
+      <c r="AM23" s="20"/>
+      <c r="AN23" s="20"/>
+      <c r="AO23" s="20"/>
+      <c r="AP23" s="20"/>
+      <c r="AQ23" s="20"/>
+      <c r="AR23" s="20"/>
+      <c r="AS23" s="20"/>
+      <c r="AT23" s="20"/>
+      <c r="AU23" s="20"/>
+      <c r="AV23" s="20"/>
+      <c r="AW23" s="20"/>
+      <c r="AX23" s="20"/>
+      <c r="AY23" s="20"/>
+      <c r="AZ23" s="20"/>
+      <c r="BA23" s="20"/>
+      <c r="BB23" s="20"/>
+      <c r="BC23" s="21"/>
+    </row>
+    <row r="24" spans="2:55">
+      <c r="B24" s="39">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="C24" s="119" t="s">
+        <v>128</v>
+      </c>
+      <c r="D24" s="20"/>
+      <c r="E24" s="20"/>
+      <c r="F24" s="20"/>
+      <c r="G24" s="20"/>
+      <c r="H24" s="20"/>
+      <c r="I24" s="20"/>
+      <c r="J24" s="20"/>
+      <c r="K24" s="21"/>
+      <c r="L24" s="119" t="s">
+        <v>179</v>
+      </c>
+      <c r="M24" s="20"/>
+      <c r="N24" s="20"/>
+      <c r="O24" s="20"/>
+      <c r="P24" s="20"/>
+      <c r="Q24" s="20"/>
+      <c r="R24" s="20"/>
+      <c r="S24" s="20"/>
+      <c r="T24" s="21"/>
+      <c r="U24" s="120" t="s">
+        <v>82</v>
+      </c>
+      <c r="V24" s="121"/>
+      <c r="W24" s="121"/>
+      <c r="X24" s="121"/>
+      <c r="Y24" s="121"/>
+      <c r="Z24" s="122"/>
+      <c r="AA24" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB24" s="124"/>
+      <c r="AC24" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD24" s="124"/>
+      <c r="AE24" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AF24" s="124"/>
+      <c r="AG24" s="120" t="s">
+        <v>71</v>
+      </c>
+      <c r="AH24" s="121"/>
+      <c r="AI24" s="121"/>
+      <c r="AJ24" s="121"/>
+      <c r="AK24" s="122"/>
+      <c r="AL24" s="120" t="s">
+        <v>69</v>
+      </c>
+      <c r="AM24" s="20"/>
+      <c r="AN24" s="20"/>
+      <c r="AO24" s="20"/>
+      <c r="AP24" s="20"/>
+      <c r="AQ24" s="20"/>
+      <c r="AR24" s="20"/>
+      <c r="AS24" s="20"/>
+      <c r="AT24" s="20"/>
+      <c r="AU24" s="20"/>
+      <c r="AV24" s="20"/>
+      <c r="AW24" s="20"/>
+      <c r="AX24" s="20"/>
+      <c r="AY24" s="20"/>
+      <c r="AZ24" s="20"/>
+      <c r="BA24" s="20"/>
+      <c r="BB24" s="20"/>
+      <c r="BC24" s="21"/>
+    </row>
+    <row r="25" spans="2:55">
+      <c r="B25" s="39">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="C25" s="119" t="s">
+        <v>129</v>
+      </c>
+      <c r="D25" s="20"/>
+      <c r="E25" s="20"/>
+      <c r="F25" s="20"/>
+      <c r="G25" s="20"/>
+      <c r="H25" s="20"/>
+      <c r="I25" s="20"/>
+      <c r="J25" s="20"/>
+      <c r="K25" s="21"/>
+      <c r="L25" s="119" t="s">
+        <v>180</v>
+      </c>
+      <c r="M25" s="20"/>
+      <c r="N25" s="20"/>
+      <c r="O25" s="20"/>
+      <c r="P25" s="20"/>
+      <c r="Q25" s="20"/>
+      <c r="R25" s="20"/>
+      <c r="S25" s="20"/>
+      <c r="T25" s="21"/>
+      <c r="U25" s="120" t="s">
+        <v>82</v>
+      </c>
+      <c r="V25" s="121"/>
+      <c r="W25" s="121"/>
+      <c r="X25" s="121"/>
+      <c r="Y25" s="121"/>
+      <c r="Z25" s="122"/>
+      <c r="AA25" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB25" s="124"/>
+      <c r="AC25" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD25" s="124"/>
+      <c r="AE25" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AF25" s="124"/>
+      <c r="AG25" s="120" t="s">
+        <v>71</v>
+      </c>
+      <c r="AH25" s="121"/>
+      <c r="AI25" s="121"/>
+      <c r="AJ25" s="121"/>
+      <c r="AK25" s="122"/>
+      <c r="AL25" s="120" t="s">
+        <v>69</v>
+      </c>
+      <c r="AM25" s="20"/>
+      <c r="AN25" s="20"/>
+      <c r="AO25" s="20"/>
+      <c r="AP25" s="20"/>
+      <c r="AQ25" s="20"/>
+      <c r="AR25" s="20"/>
+      <c r="AS25" s="20"/>
+      <c r="AT25" s="20"/>
+      <c r="AU25" s="20"/>
+      <c r="AV25" s="20"/>
+      <c r="AW25" s="20"/>
+      <c r="AX25" s="20"/>
+      <c r="AY25" s="20"/>
+      <c r="AZ25" s="20"/>
+      <c r="BA25" s="20"/>
+      <c r="BB25" s="20"/>
+      <c r="BC25" s="21"/>
+    </row>
+    <row r="26" spans="2:55">
+      <c r="B26" s="39">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="C26" s="119" t="s">
+        <v>130</v>
+      </c>
+      <c r="D26" s="20"/>
+      <c r="E26" s="20"/>
+      <c r="F26" s="20"/>
+      <c r="G26" s="20"/>
+      <c r="H26" s="20"/>
+      <c r="I26" s="20"/>
+      <c r="J26" s="20"/>
+      <c r="K26" s="21"/>
+      <c r="L26" s="119" t="s">
+        <v>181</v>
+      </c>
+      <c r="M26" s="20"/>
+      <c r="N26" s="20"/>
+      <c r="O26" s="20"/>
+      <c r="P26" s="20"/>
+      <c r="Q26" s="20"/>
+      <c r="R26" s="20"/>
+      <c r="S26" s="20"/>
+      <c r="T26" s="21"/>
+      <c r="U26" s="120" t="s">
+        <v>82</v>
+      </c>
+      <c r="V26" s="121"/>
+      <c r="W26" s="121"/>
+      <c r="X26" s="121"/>
+      <c r="Y26" s="121"/>
+      <c r="Z26" s="122"/>
+      <c r="AA26" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB26" s="124"/>
+      <c r="AC26" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD26" s="124"/>
+      <c r="AE26" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AF26" s="124"/>
+      <c r="AG26" s="120" t="s">
+        <v>71</v>
+      </c>
+      <c r="AH26" s="121"/>
+      <c r="AI26" s="121"/>
+      <c r="AJ26" s="121"/>
+      <c r="AK26" s="122"/>
+      <c r="AL26" s="120" t="s">
+        <v>69</v>
+      </c>
+      <c r="AM26" s="20"/>
+      <c r="AN26" s="20"/>
+      <c r="AO26" s="20"/>
+      <c r="AP26" s="20"/>
+      <c r="AQ26" s="20"/>
+      <c r="AR26" s="20"/>
+      <c r="AS26" s="20"/>
+      <c r="AT26" s="20"/>
+      <c r="AU26" s="20"/>
+      <c r="AV26" s="20"/>
+      <c r="AW26" s="20"/>
+      <c r="AX26" s="20"/>
+      <c r="AY26" s="20"/>
+      <c r="AZ26" s="20"/>
+      <c r="BA26" s="20"/>
+      <c r="BB26" s="20"/>
+      <c r="BC26" s="21"/>
+    </row>
+    <row r="27" spans="2:55">
+      <c r="B27" s="39">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="C27" s="119" t="s">
+        <v>131</v>
+      </c>
+      <c r="D27" s="20"/>
+      <c r="E27" s="20"/>
+      <c r="F27" s="20"/>
+      <c r="G27" s="20"/>
+      <c r="H27" s="20"/>
+      <c r="I27" s="20"/>
+      <c r="J27" s="20"/>
+      <c r="K27" s="21"/>
+      <c r="L27" s="119" t="s">
+        <v>185</v>
+      </c>
+      <c r="M27" s="20"/>
+      <c r="N27" s="20"/>
+      <c r="O27" s="20"/>
+      <c r="P27" s="20"/>
+      <c r="Q27" s="20"/>
+      <c r="R27" s="20"/>
+      <c r="S27" s="20"/>
+      <c r="T27" s="21"/>
+      <c r="U27" s="120" t="s">
+        <v>82</v>
+      </c>
+      <c r="V27" s="121"/>
+      <c r="W27" s="121"/>
+      <c r="X27" s="121"/>
+      <c r="Y27" s="121"/>
+      <c r="Z27" s="122"/>
+      <c r="AA27" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB27" s="124"/>
+      <c r="AC27" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD27" s="124"/>
+      <c r="AE27" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AF27" s="124"/>
+      <c r="AG27" s="120" t="s">
+        <v>71</v>
+      </c>
+      <c r="AH27" s="121"/>
+      <c r="AI27" s="121"/>
+      <c r="AJ27" s="121"/>
+      <c r="AK27" s="122"/>
+      <c r="AL27" s="120" t="s">
+        <v>69</v>
+      </c>
+      <c r="AM27" s="20"/>
+      <c r="AN27" s="20"/>
+      <c r="AO27" s="20"/>
+      <c r="AP27" s="20"/>
+      <c r="AQ27" s="20"/>
+      <c r="AR27" s="20"/>
+      <c r="AS27" s="20"/>
+      <c r="AT27" s="20"/>
+      <c r="AU27" s="20"/>
+      <c r="AV27" s="20"/>
+      <c r="AW27" s="20"/>
+      <c r="AX27" s="20"/>
+      <c r="AY27" s="20"/>
+      <c r="AZ27" s="20"/>
+      <c r="BA27" s="20"/>
+      <c r="BB27" s="20"/>
+      <c r="BC27" s="21"/>
+    </row>
+    <row r="28" spans="2:55">
+      <c r="B28" s="39">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="C28" s="119" t="s">
+        <v>132</v>
+      </c>
+      <c r="D28" s="20"/>
+      <c r="E28" s="20"/>
+      <c r="F28" s="20"/>
+      <c r="G28" s="20"/>
+      <c r="H28" s="20"/>
+      <c r="I28" s="20"/>
+      <c r="J28" s="20"/>
+      <c r="K28" s="21"/>
+      <c r="L28" s="119" t="s">
+        <v>186</v>
+      </c>
+      <c r="M28" s="20"/>
+      <c r="N28" s="20"/>
+      <c r="O28" s="20"/>
+      <c r="P28" s="20"/>
+      <c r="Q28" s="20"/>
+      <c r="R28" s="20"/>
+      <c r="S28" s="20"/>
+      <c r="T28" s="21"/>
+      <c r="U28" s="120" t="s">
+        <v>82</v>
+      </c>
+      <c r="V28" s="121"/>
+      <c r="W28" s="121"/>
+      <c r="X28" s="121"/>
+      <c r="Y28" s="121"/>
+      <c r="Z28" s="122"/>
+      <c r="AA28" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB28" s="124"/>
+      <c r="AC28" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD28" s="124"/>
+      <c r="AE28" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AF28" s="124"/>
+      <c r="AG28" s="120" t="s">
+        <v>71</v>
+      </c>
+      <c r="AH28" s="121"/>
+      <c r="AI28" s="121"/>
+      <c r="AJ28" s="121"/>
+      <c r="AK28" s="122"/>
+      <c r="AL28" s="120" t="s">
+        <v>69</v>
+      </c>
+      <c r="AM28" s="20"/>
+      <c r="AN28" s="20"/>
+      <c r="AO28" s="20"/>
+      <c r="AP28" s="20"/>
+      <c r="AQ28" s="20"/>
+      <c r="AR28" s="20"/>
+      <c r="AS28" s="20"/>
+      <c r="AT28" s="20"/>
+      <c r="AU28" s="20"/>
+      <c r="AV28" s="20"/>
+      <c r="AW28" s="20"/>
+      <c r="AX28" s="20"/>
+      <c r="AY28" s="20"/>
+      <c r="AZ28" s="20"/>
+      <c r="BA28" s="20"/>
+      <c r="BB28" s="20"/>
+      <c r="BC28" s="21"/>
+    </row>
+    <row r="29" spans="2:55">
+      <c r="B29" s="39">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="C29" s="119" t="s">
+        <v>133</v>
+      </c>
+      <c r="D29" s="20"/>
+      <c r="E29" s="20"/>
+      <c r="F29" s="20"/>
+      <c r="G29" s="20"/>
+      <c r="H29" s="20"/>
+      <c r="I29" s="20"/>
+      <c r="J29" s="20"/>
+      <c r="K29" s="21"/>
+      <c r="L29" s="119" t="s">
+        <v>187</v>
+      </c>
+      <c r="M29" s="20"/>
+      <c r="N29" s="20"/>
+      <c r="O29" s="20"/>
+      <c r="P29" s="20"/>
+      <c r="Q29" s="20"/>
+      <c r="R29" s="20"/>
+      <c r="S29" s="20"/>
+      <c r="T29" s="21"/>
+      <c r="U29" s="120" t="s">
+        <v>82</v>
+      </c>
+      <c r="V29" s="121"/>
+      <c r="W29" s="121"/>
+      <c r="X29" s="121"/>
+      <c r="Y29" s="121"/>
+      <c r="Z29" s="122"/>
+      <c r="AA29" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB29" s="124"/>
+      <c r="AC29" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD29" s="124"/>
+      <c r="AE29" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AF29" s="124"/>
+      <c r="AG29" s="120" t="s">
+        <v>71</v>
+      </c>
+      <c r="AH29" s="121"/>
+      <c r="AI29" s="121"/>
+      <c r="AJ29" s="121"/>
+      <c r="AK29" s="122"/>
+      <c r="AL29" s="120" t="s">
+        <v>69</v>
+      </c>
+      <c r="AM29" s="20"/>
+      <c r="AN29" s="20"/>
+      <c r="AO29" s="20"/>
+      <c r="AP29" s="20"/>
+      <c r="AQ29" s="20"/>
+      <c r="AR29" s="20"/>
+      <c r="AS29" s="20"/>
+      <c r="AT29" s="20"/>
+      <c r="AU29" s="20"/>
+      <c r="AV29" s="20"/>
+      <c r="AW29" s="20"/>
+      <c r="AX29" s="20"/>
+      <c r="AY29" s="20"/>
+      <c r="AZ29" s="20"/>
+      <c r="BA29" s="20"/>
+      <c r="BB29" s="20"/>
+      <c r="BC29" s="21"/>
+    </row>
+    <row r="30" spans="2:55">
+      <c r="B30" s="39">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="C30" s="119" t="s">
+        <v>134</v>
+      </c>
+      <c r="D30" s="20"/>
+      <c r="E30" s="20"/>
+      <c r="F30" s="20"/>
+      <c r="G30" s="20"/>
+      <c r="H30" s="20"/>
+      <c r="I30" s="20"/>
+      <c r="J30" s="20"/>
+      <c r="K30" s="21"/>
+      <c r="L30" s="119" t="s">
+        <v>188</v>
+      </c>
+      <c r="M30" s="20"/>
+      <c r="N30" s="20"/>
+      <c r="O30" s="20"/>
+      <c r="P30" s="20"/>
+      <c r="Q30" s="20"/>
+      <c r="R30" s="20"/>
+      <c r="S30" s="20"/>
+      <c r="T30" s="21"/>
+      <c r="U30" s="120" t="s">
+        <v>82</v>
+      </c>
+      <c r="V30" s="121"/>
+      <c r="W30" s="121"/>
+      <c r="X30" s="121"/>
+      <c r="Y30" s="121"/>
+      <c r="Z30" s="122"/>
+      <c r="AA30" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB30" s="124"/>
+      <c r="AC30" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD30" s="124"/>
+      <c r="AE30" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AF30" s="124"/>
+      <c r="AG30" s="120" t="s">
+        <v>71</v>
+      </c>
+      <c r="AH30" s="121"/>
+      <c r="AI30" s="121"/>
+      <c r="AJ30" s="121"/>
+      <c r="AK30" s="122"/>
+      <c r="AL30" s="120" t="s">
+        <v>69</v>
+      </c>
+      <c r="AM30" s="20"/>
+      <c r="AN30" s="20"/>
+      <c r="AO30" s="20"/>
+      <c r="AP30" s="20"/>
+      <c r="AQ30" s="20"/>
+      <c r="AR30" s="20"/>
+      <c r="AS30" s="20"/>
+      <c r="AT30" s="20"/>
+      <c r="AU30" s="20"/>
+      <c r="AV30" s="20"/>
+      <c r="AW30" s="20"/>
+      <c r="AX30" s="20"/>
+      <c r="AY30" s="20"/>
+      <c r="AZ30" s="20"/>
+      <c r="BA30" s="20"/>
+      <c r="BB30" s="20"/>
+      <c r="BC30" s="21"/>
+    </row>
+    <row r="31" spans="2:55">
+      <c r="B31" s="39">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="C31" s="119" t="s">
+        <v>135</v>
+      </c>
+      <c r="D31" s="20"/>
+      <c r="E31" s="20"/>
+      <c r="F31" s="20"/>
+      <c r="G31" s="20"/>
+      <c r="H31" s="20"/>
+      <c r="I31" s="20"/>
+      <c r="J31" s="20"/>
+      <c r="K31" s="21"/>
+      <c r="L31" s="119" t="s">
+        <v>189</v>
+      </c>
+      <c r="M31" s="20"/>
+      <c r="N31" s="20"/>
+      <c r="O31" s="20"/>
+      <c r="P31" s="20"/>
+      <c r="Q31" s="20"/>
+      <c r="R31" s="20"/>
+      <c r="S31" s="20"/>
+      <c r="T31" s="21"/>
+      <c r="U31" s="120" t="s">
+        <v>82</v>
+      </c>
+      <c r="V31" s="121"/>
+      <c r="W31" s="121"/>
+      <c r="X31" s="121"/>
+      <c r="Y31" s="121"/>
+      <c r="Z31" s="122"/>
+      <c r="AA31" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB31" s="124"/>
+      <c r="AC31" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD31" s="124"/>
+      <c r="AE31" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AF31" s="124"/>
+      <c r="AG31" s="120" t="s">
+        <v>71</v>
+      </c>
+      <c r="AH31" s="121"/>
+      <c r="AI31" s="121"/>
+      <c r="AJ31" s="121"/>
+      <c r="AK31" s="122"/>
+      <c r="AL31" s="120" t="s">
+        <v>69</v>
+      </c>
+      <c r="AM31" s="20"/>
+      <c r="AN31" s="20"/>
+      <c r="AO31" s="20"/>
+      <c r="AP31" s="20"/>
+      <c r="AQ31" s="20"/>
+      <c r="AR31" s="20"/>
+      <c r="AS31" s="20"/>
+      <c r="AT31" s="20"/>
+      <c r="AU31" s="20"/>
+      <c r="AV31" s="20"/>
+      <c r="AW31" s="20"/>
+      <c r="AX31" s="20"/>
+      <c r="AY31" s="20"/>
+      <c r="AZ31" s="20"/>
+      <c r="BA31" s="20"/>
+      <c r="BB31" s="20"/>
+      <c r="BC31" s="21"/>
+    </row>
+    <row r="32" spans="2:55">
+      <c r="B32" s="39">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="C32" s="119" t="s">
+        <v>103</v>
+      </c>
+      <c r="D32" s="20"/>
+      <c r="E32" s="20"/>
+      <c r="F32" s="20"/>
+      <c r="G32" s="20"/>
+      <c r="H32" s="20"/>
+      <c r="I32" s="20"/>
+      <c r="J32" s="20"/>
+      <c r="K32" s="21"/>
+      <c r="L32" s="119" t="s">
+        <v>102</v>
+      </c>
+      <c r="M32" s="20"/>
+      <c r="N32" s="20"/>
+      <c r="O32" s="20"/>
+      <c r="P32" s="20"/>
+      <c r="Q32" s="20"/>
+      <c r="R32" s="20"/>
+      <c r="S32" s="20"/>
+      <c r="T32" s="21"/>
+      <c r="U32" s="120" t="s">
+        <v>82</v>
+      </c>
+      <c r="V32" s="121"/>
+      <c r="W32" s="121"/>
+      <c r="X32" s="121"/>
+      <c r="Y32" s="121"/>
+      <c r="Z32" s="122"/>
+      <c r="AA32" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB32" s="124"/>
+      <c r="AC32" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD32" s="124"/>
+      <c r="AE32" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AF32" s="124"/>
+      <c r="AG32" s="120" t="s">
+        <v>71</v>
+      </c>
+      <c r="AH32" s="121"/>
+      <c r="AI32" s="121"/>
+      <c r="AJ32" s="121"/>
+      <c r="AK32" s="122"/>
+      <c r="AL32" s="120" t="s">
+        <v>69</v>
+      </c>
+      <c r="AM32" s="20"/>
+      <c r="AN32" s="20"/>
+      <c r="AO32" s="20"/>
+      <c r="AP32" s="20"/>
+      <c r="AQ32" s="20"/>
+      <c r="AR32" s="20"/>
+      <c r="AS32" s="20"/>
+      <c r="AT32" s="20"/>
+      <c r="AU32" s="20"/>
+      <c r="AV32" s="20"/>
+      <c r="AW32" s="20"/>
+      <c r="AX32" s="20"/>
+      <c r="AY32" s="20"/>
+      <c r="AZ32" s="20"/>
+      <c r="BA32" s="20"/>
+      <c r="BB32" s="20"/>
+      <c r="BC32" s="21"/>
+    </row>
+    <row r="33" spans="2:55">
+      <c r="B33" s="39">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="C33" s="119" t="s">
+        <v>105</v>
+      </c>
+      <c r="D33" s="20"/>
+      <c r="E33" s="20"/>
+      <c r="F33" s="20"/>
+      <c r="G33" s="20"/>
+      <c r="H33" s="20"/>
+      <c r="I33" s="20"/>
+      <c r="J33" s="20"/>
+      <c r="K33" s="21"/>
+      <c r="L33" s="119" t="s">
+        <v>104</v>
+      </c>
+      <c r="M33" s="20"/>
+      <c r="N33" s="20"/>
+      <c r="O33" s="20"/>
+      <c r="P33" s="20"/>
+      <c r="Q33" s="20"/>
+      <c r="R33" s="20"/>
+      <c r="S33" s="20"/>
+      <c r="T33" s="21"/>
+      <c r="U33" s="120" t="s">
+        <v>82</v>
+      </c>
+      <c r="V33" s="121"/>
+      <c r="W33" s="121"/>
+      <c r="X33" s="121"/>
+      <c r="Y33" s="121"/>
+      <c r="Z33" s="122"/>
+      <c r="AA33" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB33" s="124"/>
+      <c r="AC33" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD33" s="124"/>
+      <c r="AE33" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AF33" s="124"/>
+      <c r="AG33" s="120" t="s">
+        <v>71</v>
+      </c>
+      <c r="AH33" s="121"/>
+      <c r="AI33" s="121"/>
+      <c r="AJ33" s="121"/>
+      <c r="AK33" s="122"/>
+      <c r="AL33" s="120" t="s">
+        <v>69</v>
+      </c>
+      <c r="AM33" s="20"/>
+      <c r="AN33" s="20"/>
+      <c r="AO33" s="20"/>
+      <c r="AP33" s="20"/>
+      <c r="AQ33" s="20"/>
+      <c r="AR33" s="20"/>
+      <c r="AS33" s="20"/>
+      <c r="AT33" s="20"/>
+      <c r="AU33" s="20"/>
+      <c r="AV33" s="20"/>
+      <c r="AW33" s="20"/>
+      <c r="AX33" s="20"/>
+      <c r="AY33" s="20"/>
+      <c r="AZ33" s="20"/>
+      <c r="BA33" s="20"/>
+      <c r="BB33" s="20"/>
+      <c r="BC33" s="21"/>
+    </row>
+    <row r="34" spans="2:55">
+      <c r="B34" s="39">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="C34" s="119" t="s">
+        <v>107</v>
+      </c>
+      <c r="D34" s="20"/>
+      <c r="E34" s="20"/>
+      <c r="F34" s="20"/>
+      <c r="G34" s="20"/>
+      <c r="H34" s="20"/>
+      <c r="I34" s="20"/>
+      <c r="J34" s="20"/>
+      <c r="K34" s="21"/>
+      <c r="L34" s="119" t="s">
+        <v>106</v>
+      </c>
+      <c r="M34" s="20"/>
+      <c r="N34" s="20"/>
+      <c r="O34" s="20"/>
+      <c r="P34" s="20"/>
+      <c r="Q34" s="20"/>
+      <c r="R34" s="20"/>
+      <c r="S34" s="20"/>
+      <c r="T34" s="21"/>
+      <c r="U34" s="120" t="s">
+        <v>82</v>
+      </c>
+      <c r="V34" s="121"/>
+      <c r="W34" s="121"/>
+      <c r="X34" s="121"/>
+      <c r="Y34" s="121"/>
+      <c r="Z34" s="122"/>
+      <c r="AA34" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB34" s="124"/>
+      <c r="AC34" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD34" s="124"/>
+      <c r="AE34" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AF34" s="124"/>
+      <c r="AG34" s="120" t="s">
+        <v>71</v>
+      </c>
+      <c r="AH34" s="121"/>
+      <c r="AI34" s="121"/>
+      <c r="AJ34" s="121"/>
+      <c r="AK34" s="122"/>
+      <c r="AL34" s="120" t="s">
+        <v>69</v>
+      </c>
+      <c r="AM34" s="20"/>
+      <c r="AN34" s="20"/>
+      <c r="AO34" s="20"/>
+      <c r="AP34" s="20"/>
+      <c r="AQ34" s="20"/>
+      <c r="AR34" s="20"/>
+      <c r="AS34" s="20"/>
+      <c r="AT34" s="20"/>
+      <c r="AU34" s="20"/>
+      <c r="AV34" s="20"/>
+      <c r="AW34" s="20"/>
+      <c r="AX34" s="20"/>
+      <c r="AY34" s="20"/>
+      <c r="AZ34" s="20"/>
+      <c r="BA34" s="20"/>
+      <c r="BB34" s="20"/>
+      <c r="BC34" s="21"/>
+    </row>
+    <row r="35" spans="2:55">
+      <c r="B35" s="39">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="C35" s="119" t="s">
+        <v>109</v>
+      </c>
+      <c r="D35" s="20"/>
+      <c r="E35" s="20"/>
+      <c r="F35" s="20"/>
+      <c r="G35" s="20"/>
+      <c r="H35" s="20"/>
+      <c r="I35" s="20"/>
+      <c r="J35" s="20"/>
+      <c r="K35" s="21"/>
+      <c r="L35" s="119" t="s">
+        <v>108</v>
+      </c>
+      <c r="M35" s="20"/>
+      <c r="N35" s="20"/>
+      <c r="O35" s="20"/>
+      <c r="P35" s="20"/>
+      <c r="Q35" s="20"/>
+      <c r="R35" s="20"/>
+      <c r="S35" s="20"/>
+      <c r="T35" s="21"/>
+      <c r="U35" s="120" t="s">
+        <v>82</v>
+      </c>
+      <c r="V35" s="121"/>
+      <c r="W35" s="121"/>
+      <c r="X35" s="121"/>
+      <c r="Y35" s="121"/>
+      <c r="Z35" s="122"/>
+      <c r="AA35" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB35" s="124"/>
+      <c r="AC35" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD35" s="124"/>
+      <c r="AE35" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AF35" s="124"/>
+      <c r="AG35" s="120" t="s">
+        <v>71</v>
+      </c>
+      <c r="AH35" s="121"/>
+      <c r="AI35" s="121"/>
+      <c r="AJ35" s="121"/>
+      <c r="AK35" s="122"/>
+      <c r="AL35" s="120" t="s">
+        <v>69</v>
+      </c>
+      <c r="AM35" s="20"/>
+      <c r="AN35" s="20"/>
+      <c r="AO35" s="20"/>
+      <c r="AP35" s="20"/>
+      <c r="AQ35" s="20"/>
+      <c r="AR35" s="20"/>
+      <c r="AS35" s="20"/>
+      <c r="AT35" s="20"/>
+      <c r="AU35" s="20"/>
+      <c r="AV35" s="20"/>
+      <c r="AW35" s="20"/>
+      <c r="AX35" s="20"/>
+      <c r="AY35" s="20"/>
+      <c r="AZ35" s="20"/>
+      <c r="BA35" s="20"/>
+      <c r="BB35" s="20"/>
+      <c r="BC35" s="21"/>
+    </row>
+    <row r="36" spans="2:55">
+      <c r="B36" s="39">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="C36" s="119" t="s">
+        <v>136</v>
+      </c>
+      <c r="D36" s="20"/>
+      <c r="E36" s="20"/>
+      <c r="F36" s="20"/>
+      <c r="G36" s="20"/>
+      <c r="H36" s="20"/>
+      <c r="I36" s="20"/>
+      <c r="J36" s="20"/>
+      <c r="K36" s="21"/>
+      <c r="L36" s="119" t="s">
+        <v>182</v>
+      </c>
+      <c r="M36" s="20"/>
+      <c r="N36" s="20"/>
+      <c r="O36" s="20"/>
+      <c r="P36" s="20"/>
+      <c r="Q36" s="20"/>
+      <c r="R36" s="20"/>
+      <c r="S36" s="20"/>
+      <c r="T36" s="21"/>
+      <c r="U36" s="120" t="s">
+        <v>82</v>
+      </c>
+      <c r="V36" s="121"/>
+      <c r="W36" s="121"/>
+      <c r="X36" s="121"/>
+      <c r="Y36" s="121"/>
+      <c r="Z36" s="122"/>
+      <c r="AA36" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB36" s="124"/>
+      <c r="AC36" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD36" s="124"/>
+      <c r="AE36" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AF36" s="124"/>
+      <c r="AG36" s="120" t="s">
+        <v>71</v>
+      </c>
+      <c r="AH36" s="121"/>
+      <c r="AI36" s="121"/>
+      <c r="AJ36" s="121"/>
+      <c r="AK36" s="122"/>
+      <c r="AL36" s="120" t="s">
+        <v>69</v>
+      </c>
+      <c r="AM36" s="20"/>
+      <c r="AN36" s="20"/>
+      <c r="AO36" s="20"/>
+      <c r="AP36" s="20"/>
+      <c r="AQ36" s="20"/>
+      <c r="AR36" s="20"/>
+      <c r="AS36" s="20"/>
+      <c r="AT36" s="20"/>
+      <c r="AU36" s="20"/>
+      <c r="AV36" s="20"/>
+      <c r="AW36" s="20"/>
+      <c r="AX36" s="20"/>
+      <c r="AY36" s="20"/>
+      <c r="AZ36" s="20"/>
+      <c r="BA36" s="20"/>
+      <c r="BB36" s="20"/>
+      <c r="BC36" s="21"/>
+    </row>
+    <row r="37" spans="2:55">
+      <c r="B37" s="39">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="C37" s="119" t="s">
+        <v>137</v>
+      </c>
+      <c r="D37" s="20"/>
+      <c r="E37" s="20"/>
+      <c r="F37" s="20"/>
+      <c r="G37" s="20"/>
+      <c r="H37" s="20"/>
+      <c r="I37" s="20"/>
+      <c r="J37" s="20"/>
+      <c r="K37" s="21"/>
+      <c r="L37" s="119" t="s">
+        <v>190</v>
+      </c>
+      <c r="M37" s="20"/>
+      <c r="N37" s="20"/>
+      <c r="O37" s="20"/>
+      <c r="P37" s="20"/>
+      <c r="Q37" s="20"/>
+      <c r="R37" s="20"/>
+      <c r="S37" s="20"/>
+      <c r="T37" s="21"/>
+      <c r="U37" s="120" t="s">
+        <v>82</v>
+      </c>
+      <c r="V37" s="121"/>
+      <c r="W37" s="121"/>
+      <c r="X37" s="121"/>
+      <c r="Y37" s="121"/>
+      <c r="Z37" s="122"/>
+      <c r="AA37" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB37" s="124"/>
+      <c r="AC37" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD37" s="124"/>
+      <c r="AE37" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AF37" s="124"/>
+      <c r="AG37" s="120" t="s">
+        <v>71</v>
+      </c>
+      <c r="AH37" s="121"/>
+      <c r="AI37" s="121"/>
+      <c r="AJ37" s="121"/>
+      <c r="AK37" s="122"/>
+      <c r="AL37" s="120" t="s">
+        <v>69</v>
+      </c>
+      <c r="AM37" s="20"/>
+      <c r="AN37" s="20"/>
+      <c r="AO37" s="20"/>
+      <c r="AP37" s="20"/>
+      <c r="AQ37" s="20"/>
+      <c r="AR37" s="20"/>
+      <c r="AS37" s="20"/>
+      <c r="AT37" s="20"/>
+      <c r="AU37" s="20"/>
+      <c r="AV37" s="20"/>
+      <c r="AW37" s="20"/>
+      <c r="AX37" s="20"/>
+      <c r="AY37" s="20"/>
+      <c r="AZ37" s="20"/>
+      <c r="BA37" s="20"/>
+      <c r="BB37" s="20"/>
+      <c r="BC37" s="21"/>
+    </row>
+    <row r="38" spans="2:55">
+      <c r="B38" s="39">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="C38" s="119" t="s">
+        <v>138</v>
+      </c>
+      <c r="D38" s="20"/>
+      <c r="E38" s="20"/>
+      <c r="F38" s="20"/>
+      <c r="G38" s="20"/>
+      <c r="H38" s="20"/>
+      <c r="I38" s="20"/>
+      <c r="J38" s="20"/>
+      <c r="K38" s="21"/>
+      <c r="L38" s="119" t="s">
+        <v>191</v>
+      </c>
+      <c r="M38" s="20"/>
+      <c r="N38" s="20"/>
+      <c r="O38" s="20"/>
+      <c r="P38" s="20"/>
+      <c r="Q38" s="20"/>
+      <c r="R38" s="20"/>
+      <c r="S38" s="20"/>
+      <c r="T38" s="21"/>
+      <c r="U38" s="120" t="s">
+        <v>82</v>
+      </c>
+      <c r="V38" s="121"/>
+      <c r="W38" s="121"/>
+      <c r="X38" s="121"/>
+      <c r="Y38" s="121"/>
+      <c r="Z38" s="122"/>
+      <c r="AA38" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB38" s="124"/>
+      <c r="AC38" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD38" s="124"/>
+      <c r="AE38" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AF38" s="124"/>
+      <c r="AG38" s="120" t="s">
+        <v>71</v>
+      </c>
+      <c r="AH38" s="121"/>
+      <c r="AI38" s="121"/>
+      <c r="AJ38" s="121"/>
+      <c r="AK38" s="122"/>
+      <c r="AL38" s="120" t="s">
+        <v>69</v>
+      </c>
+      <c r="AM38" s="20"/>
+      <c r="AN38" s="20"/>
+      <c r="AO38" s="20"/>
+      <c r="AP38" s="20"/>
+      <c r="AQ38" s="20"/>
+      <c r="AR38" s="20"/>
+      <c r="AS38" s="20"/>
+      <c r="AT38" s="20"/>
+      <c r="AU38" s="20"/>
+      <c r="AV38" s="20"/>
+      <c r="AW38" s="20"/>
+      <c r="AX38" s="20"/>
+      <c r="AY38" s="20"/>
+      <c r="AZ38" s="20"/>
+      <c r="BA38" s="20"/>
+      <c r="BB38" s="20"/>
+      <c r="BC38" s="21"/>
+    </row>
+    <row r="39" spans="2:55">
+      <c r="B39" s="39">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="C39" s="119" t="s">
+        <v>139</v>
+      </c>
+      <c r="D39" s="20"/>
+      <c r="E39" s="20"/>
+      <c r="F39" s="20"/>
+      <c r="G39" s="20"/>
+      <c r="H39" s="20"/>
+      <c r="I39" s="20"/>
+      <c r="J39" s="20"/>
+      <c r="K39" s="21"/>
+      <c r="L39" s="119" t="s">
+        <v>192</v>
+      </c>
+      <c r="M39" s="20"/>
+      <c r="N39" s="20"/>
+      <c r="O39" s="20"/>
+      <c r="P39" s="20"/>
+      <c r="Q39" s="20"/>
+      <c r="R39" s="20"/>
+      <c r="S39" s="20"/>
+      <c r="T39" s="21"/>
+      <c r="U39" s="120" t="s">
+        <v>82</v>
+      </c>
+      <c r="V39" s="121"/>
+      <c r="W39" s="121"/>
+      <c r="X39" s="121"/>
+      <c r="Y39" s="121"/>
+      <c r="Z39" s="122"/>
+      <c r="AA39" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB39" s="124"/>
+      <c r="AC39" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD39" s="124"/>
+      <c r="AE39" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AF39" s="124"/>
+      <c r="AG39" s="120" t="s">
+        <v>71</v>
+      </c>
+      <c r="AH39" s="121"/>
+      <c r="AI39" s="121"/>
+      <c r="AJ39" s="121"/>
+      <c r="AK39" s="122"/>
+      <c r="AL39" s="120" t="s">
+        <v>69</v>
+      </c>
+      <c r="AM39" s="20"/>
+      <c r="AN39" s="20"/>
+      <c r="AO39" s="20"/>
+      <c r="AP39" s="20"/>
+      <c r="AQ39" s="20"/>
+      <c r="AR39" s="20"/>
+      <c r="AS39" s="20"/>
+      <c r="AT39" s="20"/>
+      <c r="AU39" s="20"/>
+      <c r="AV39" s="20"/>
+      <c r="AW39" s="20"/>
+      <c r="AX39" s="20"/>
+      <c r="AY39" s="20"/>
+      <c r="AZ39" s="20"/>
+      <c r="BA39" s="20"/>
+      <c r="BB39" s="20"/>
+      <c r="BC39" s="21"/>
+    </row>
+    <row r="40" spans="2:55">
+      <c r="B40" s="39">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="C40" s="119" t="s">
+        <v>140</v>
+      </c>
+      <c r="D40" s="20"/>
+      <c r="E40" s="20"/>
+      <c r="F40" s="20"/>
+      <c r="G40" s="20"/>
+      <c r="H40" s="20"/>
+      <c r="I40" s="20"/>
+      <c r="J40" s="20"/>
+      <c r="K40" s="21"/>
+      <c r="L40" s="119" t="s">
+        <v>193</v>
+      </c>
+      <c r="M40" s="20"/>
+      <c r="N40" s="20"/>
+      <c r="O40" s="20"/>
+      <c r="P40" s="20"/>
+      <c r="Q40" s="20"/>
+      <c r="R40" s="20"/>
+      <c r="S40" s="20"/>
+      <c r="T40" s="21"/>
+      <c r="U40" s="120" t="s">
+        <v>82</v>
+      </c>
+      <c r="V40" s="121"/>
+      <c r="W40" s="121"/>
+      <c r="X40" s="121"/>
+      <c r="Y40" s="121"/>
+      <c r="Z40" s="122"/>
+      <c r="AA40" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB40" s="124"/>
+      <c r="AC40" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD40" s="124"/>
+      <c r="AE40" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AF40" s="124"/>
+      <c r="AG40" s="120" t="s">
+        <v>71</v>
+      </c>
+      <c r="AH40" s="121"/>
+      <c r="AI40" s="121"/>
+      <c r="AJ40" s="121"/>
+      <c r="AK40" s="122"/>
+      <c r="AL40" s="120" t="s">
+        <v>69</v>
+      </c>
+      <c r="AM40" s="20"/>
+      <c r="AN40" s="20"/>
+      <c r="AO40" s="20"/>
+      <c r="AP40" s="20"/>
+      <c r="AQ40" s="20"/>
+      <c r="AR40" s="20"/>
+      <c r="AS40" s="20"/>
+      <c r="AT40" s="20"/>
+      <c r="AU40" s="20"/>
+      <c r="AV40" s="20"/>
+      <c r="AW40" s="20"/>
+      <c r="AX40" s="20"/>
+      <c r="AY40" s="20"/>
+      <c r="AZ40" s="20"/>
+      <c r="BA40" s="20"/>
+      <c r="BB40" s="20"/>
+      <c r="BC40" s="21"/>
+    </row>
+    <row r="41" spans="2:55">
+      <c r="B41" s="39">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="C41" s="119" t="s">
+        <v>141</v>
+      </c>
+      <c r="D41" s="20"/>
+      <c r="E41" s="20"/>
+      <c r="F41" s="20"/>
+      <c r="G41" s="20"/>
+      <c r="H41" s="20"/>
+      <c r="I41" s="20"/>
+      <c r="J41" s="20"/>
+      <c r="K41" s="21"/>
+      <c r="L41" s="119" t="s">
+        <v>194</v>
+      </c>
+      <c r="M41" s="20"/>
+      <c r="N41" s="20"/>
+      <c r="O41" s="20"/>
+      <c r="P41" s="20"/>
+      <c r="Q41" s="20"/>
+      <c r="R41" s="20"/>
+      <c r="S41" s="20"/>
+      <c r="T41" s="21"/>
+      <c r="U41" s="120" t="s">
+        <v>82</v>
+      </c>
+      <c r="V41" s="121"/>
+      <c r="W41" s="121"/>
+      <c r="X41" s="121"/>
+      <c r="Y41" s="121"/>
+      <c r="Z41" s="122"/>
+      <c r="AA41" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB41" s="124"/>
+      <c r="AC41" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD41" s="124"/>
+      <c r="AE41" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AF41" s="124"/>
+      <c r="AG41" s="120" t="s">
+        <v>71</v>
+      </c>
+      <c r="AH41" s="121"/>
+      <c r="AI41" s="121"/>
+      <c r="AJ41" s="121"/>
+      <c r="AK41" s="122"/>
+      <c r="AL41" s="120" t="s">
+        <v>69</v>
+      </c>
+      <c r="AM41" s="20"/>
+      <c r="AN41" s="20"/>
+      <c r="AO41" s="20"/>
+      <c r="AP41" s="20"/>
+      <c r="AQ41" s="20"/>
+      <c r="AR41" s="20"/>
+      <c r="AS41" s="20"/>
+      <c r="AT41" s="20"/>
+      <c r="AU41" s="20"/>
+      <c r="AV41" s="20"/>
+      <c r="AW41" s="20"/>
+      <c r="AX41" s="20"/>
+      <c r="AY41" s="20"/>
+      <c r="AZ41" s="20"/>
+      <c r="BA41" s="20"/>
+      <c r="BB41" s="20"/>
+      <c r="BC41" s="21"/>
+    </row>
+    <row r="42" spans="2:55">
+      <c r="B42" s="39">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="C42" s="119" t="s">
+        <v>142</v>
+      </c>
+      <c r="D42" s="20"/>
+      <c r="E42" s="20"/>
+      <c r="F42" s="20"/>
+      <c r="G42" s="20"/>
+      <c r="H42" s="20"/>
+      <c r="I42" s="20"/>
+      <c r="J42" s="20"/>
+      <c r="K42" s="21"/>
+      <c r="L42" s="119" t="s">
+        <v>195</v>
+      </c>
+      <c r="M42" s="20"/>
+      <c r="N42" s="20"/>
+      <c r="O42" s="20"/>
+      <c r="P42" s="20"/>
+      <c r="Q42" s="20"/>
+      <c r="R42" s="20"/>
+      <c r="S42" s="20"/>
+      <c r="T42" s="21"/>
+      <c r="U42" s="120" t="s">
+        <v>82</v>
+      </c>
+      <c r="V42" s="121"/>
+      <c r="W42" s="121"/>
+      <c r="X42" s="121"/>
+      <c r="Y42" s="121"/>
+      <c r="Z42" s="122"/>
+      <c r="AA42" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB42" s="124"/>
+      <c r="AC42" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD42" s="124"/>
+      <c r="AE42" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AF42" s="124"/>
+      <c r="AG42" s="120" t="s">
+        <v>71</v>
+      </c>
+      <c r="AH42" s="121"/>
+      <c r="AI42" s="121"/>
+      <c r="AJ42" s="121"/>
+      <c r="AK42" s="122"/>
+      <c r="AL42" s="120" t="s">
+        <v>69</v>
+      </c>
+      <c r="AM42" s="20"/>
+      <c r="AN42" s="20"/>
+      <c r="AO42" s="20"/>
+      <c r="AP42" s="20"/>
+      <c r="AQ42" s="20"/>
+      <c r="AR42" s="20"/>
+      <c r="AS42" s="20"/>
+      <c r="AT42" s="20"/>
+      <c r="AU42" s="20"/>
+      <c r="AV42" s="20"/>
+      <c r="AW42" s="20"/>
+      <c r="AX42" s="20"/>
+      <c r="AY42" s="20"/>
+      <c r="AZ42" s="20"/>
+      <c r="BA42" s="20"/>
+      <c r="BB42" s="20"/>
+      <c r="BC42" s="21"/>
+    </row>
+    <row r="43" spans="2:55">
+      <c r="B43" s="39">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="C43" s="119" t="s">
+        <v>143</v>
+      </c>
+      <c r="D43" s="20"/>
+      <c r="E43" s="20"/>
+      <c r="F43" s="20"/>
+      <c r="G43" s="20"/>
+      <c r="H43" s="20"/>
+      <c r="I43" s="20"/>
+      <c r="J43" s="20"/>
+      <c r="K43" s="21"/>
+      <c r="L43" s="119" t="s">
+        <v>196</v>
+      </c>
+      <c r="M43" s="20"/>
+      <c r="N43" s="20"/>
+      <c r="O43" s="20"/>
+      <c r="P43" s="20"/>
+      <c r="Q43" s="20"/>
+      <c r="R43" s="20"/>
+      <c r="S43" s="20"/>
+      <c r="T43" s="21"/>
+      <c r="U43" s="120" t="s">
+        <v>82</v>
+      </c>
+      <c r="V43" s="121"/>
+      <c r="W43" s="121"/>
+      <c r="X43" s="121"/>
+      <c r="Y43" s="121"/>
+      <c r="Z43" s="122"/>
+      <c r="AA43" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB43" s="124"/>
+      <c r="AC43" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD43" s="124"/>
+      <c r="AE43" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AF43" s="124"/>
+      <c r="AG43" s="120" t="s">
+        <v>71</v>
+      </c>
+      <c r="AH43" s="121"/>
+      <c r="AI43" s="121"/>
+      <c r="AJ43" s="121"/>
+      <c r="AK43" s="122"/>
+      <c r="AL43" s="120" t="s">
+        <v>69</v>
+      </c>
+      <c r="AM43" s="20"/>
+      <c r="AN43" s="20"/>
+      <c r="AO43" s="20"/>
+      <c r="AP43" s="20"/>
+      <c r="AQ43" s="20"/>
+      <c r="AR43" s="20"/>
+      <c r="AS43" s="20"/>
+      <c r="AT43" s="20"/>
+      <c r="AU43" s="20"/>
+      <c r="AV43" s="20"/>
+      <c r="AW43" s="20"/>
+      <c r="AX43" s="20"/>
+      <c r="AY43" s="20"/>
+      <c r="AZ43" s="20"/>
+      <c r="BA43" s="20"/>
+      <c r="BB43" s="20"/>
+      <c r="BC43" s="21"/>
+    </row>
+    <row r="44" spans="2:55">
+      <c r="B44" s="39">
+        <f t="shared" si="0"/>
+        <v>33</v>
+      </c>
+      <c r="C44" s="119" t="s">
+        <v>144</v>
+      </c>
+      <c r="D44" s="20"/>
+      <c r="E44" s="20"/>
+      <c r="F44" s="20"/>
+      <c r="G44" s="20"/>
+      <c r="H44" s="20"/>
+      <c r="I44" s="20"/>
+      <c r="J44" s="20"/>
+      <c r="K44" s="21"/>
+      <c r="L44" s="119" t="s">
+        <v>197</v>
+      </c>
+      <c r="M44" s="20"/>
+      <c r="N44" s="20"/>
+      <c r="O44" s="20"/>
+      <c r="P44" s="20"/>
+      <c r="Q44" s="20"/>
+      <c r="R44" s="20"/>
+      <c r="S44" s="20"/>
+      <c r="T44" s="21"/>
+      <c r="U44" s="120" t="s">
+        <v>82</v>
+      </c>
+      <c r="V44" s="121"/>
+      <c r="W44" s="121"/>
+      <c r="X44" s="121"/>
+      <c r="Y44" s="121"/>
+      <c r="Z44" s="122"/>
+      <c r="AA44" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB44" s="124"/>
+      <c r="AC44" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD44" s="124"/>
+      <c r="AE44" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AF44" s="124"/>
+      <c r="AG44" s="120" t="s">
+        <v>71</v>
+      </c>
+      <c r="AH44" s="121"/>
+      <c r="AI44" s="121"/>
+      <c r="AJ44" s="121"/>
+      <c r="AK44" s="122"/>
+      <c r="AL44" s="120" t="s">
+        <v>69</v>
+      </c>
+      <c r="AM44" s="20"/>
+      <c r="AN44" s="20"/>
+      <c r="AO44" s="20"/>
+      <c r="AP44" s="20"/>
+      <c r="AQ44" s="20"/>
+      <c r="AR44" s="20"/>
+      <c r="AS44" s="20"/>
+      <c r="AT44" s="20"/>
+      <c r="AU44" s="20"/>
+      <c r="AV44" s="20"/>
+      <c r="AW44" s="20"/>
+      <c r="AX44" s="20"/>
+      <c r="AY44" s="20"/>
+      <c r="AZ44" s="20"/>
+      <c r="BA44" s="20"/>
+      <c r="BB44" s="20"/>
+      <c r="BC44" s="21"/>
+    </row>
+    <row r="45" spans="2:55">
+      <c r="B45" s="39">
+        <f t="shared" si="0"/>
+        <v>34</v>
+      </c>
+      <c r="C45" s="119" t="s">
+        <v>145</v>
+      </c>
+      <c r="D45" s="20"/>
+      <c r="E45" s="20"/>
+      <c r="F45" s="20"/>
+      <c r="G45" s="20"/>
+      <c r="H45" s="20"/>
+      <c r="I45" s="20"/>
+      <c r="J45" s="20"/>
+      <c r="K45" s="21"/>
+      <c r="L45" s="119" t="s">
+        <v>198</v>
+      </c>
+      <c r="M45" s="20"/>
+      <c r="N45" s="20"/>
+      <c r="O45" s="20"/>
+      <c r="P45" s="20"/>
+      <c r="Q45" s="20"/>
+      <c r="R45" s="20"/>
+      <c r="S45" s="20"/>
+      <c r="T45" s="21"/>
+      <c r="U45" s="120" t="s">
+        <v>82</v>
+      </c>
+      <c r="V45" s="121"/>
+      <c r="W45" s="121"/>
+      <c r="X45" s="121"/>
+      <c r="Y45" s="121"/>
+      <c r="Z45" s="122"/>
+      <c r="AA45" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB45" s="124"/>
+      <c r="AC45" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD45" s="124"/>
+      <c r="AE45" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AF45" s="124"/>
+      <c r="AG45" s="120" t="s">
+        <v>71</v>
+      </c>
+      <c r="AH45" s="121"/>
+      <c r="AI45" s="121"/>
+      <c r="AJ45" s="121"/>
+      <c r="AK45" s="122"/>
+      <c r="AL45" s="120" t="s">
+        <v>69</v>
+      </c>
+      <c r="AM45" s="20"/>
+      <c r="AN45" s="20"/>
+      <c r="AO45" s="20"/>
+      <c r="AP45" s="20"/>
+      <c r="AQ45" s="20"/>
+      <c r="AR45" s="20"/>
+      <c r="AS45" s="20"/>
+      <c r="AT45" s="20"/>
+      <c r="AU45" s="20"/>
+      <c r="AV45" s="20"/>
+      <c r="AW45" s="20"/>
+      <c r="AX45" s="20"/>
+      <c r="AY45" s="20"/>
+      <c r="AZ45" s="20"/>
+      <c r="BA45" s="20"/>
+      <c r="BB45" s="20"/>
+      <c r="BC45" s="21"/>
+    </row>
+    <row r="46" spans="2:55">
+      <c r="B46" s="39">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
+      <c r="C46" s="119" t="s">
+        <v>146</v>
+      </c>
+      <c r="D46" s="20"/>
+      <c r="E46" s="20"/>
+      <c r="F46" s="20"/>
+      <c r="G46" s="20"/>
+      <c r="H46" s="20"/>
+      <c r="I46" s="20"/>
+      <c r="J46" s="20"/>
+      <c r="K46" s="21"/>
+      <c r="L46" s="119" t="s">
+        <v>199</v>
+      </c>
+      <c r="M46" s="20"/>
+      <c r="N46" s="20"/>
+      <c r="O46" s="20"/>
+      <c r="P46" s="20"/>
+      <c r="Q46" s="20"/>
+      <c r="R46" s="20"/>
+      <c r="S46" s="20"/>
+      <c r="T46" s="21"/>
+      <c r="U46" s="120" t="s">
+        <v>82</v>
+      </c>
+      <c r="V46" s="121"/>
+      <c r="W46" s="121"/>
+      <c r="X46" s="121"/>
+      <c r="Y46" s="121"/>
+      <c r="Z46" s="122"/>
+      <c r="AA46" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB46" s="124"/>
+      <c r="AC46" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD46" s="124"/>
+      <c r="AE46" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AF46" s="124"/>
+      <c r="AG46" s="120" t="s">
+        <v>71</v>
+      </c>
+      <c r="AH46" s="121"/>
+      <c r="AI46" s="121"/>
+      <c r="AJ46" s="121"/>
+      <c r="AK46" s="122"/>
+      <c r="AL46" s="120" t="s">
+        <v>69</v>
+      </c>
+      <c r="AM46" s="20"/>
+      <c r="AN46" s="20"/>
+      <c r="AO46" s="20"/>
+      <c r="AP46" s="20"/>
+      <c r="AQ46" s="20"/>
+      <c r="AR46" s="20"/>
+      <c r="AS46" s="20"/>
+      <c r="AT46" s="20"/>
+      <c r="AU46" s="20"/>
+      <c r="AV46" s="20"/>
+      <c r="AW46" s="20"/>
+      <c r="AX46" s="20"/>
+      <c r="AY46" s="20"/>
+      <c r="AZ46" s="20"/>
+      <c r="BA46" s="20"/>
+      <c r="BB46" s="20"/>
+      <c r="BC46" s="21"/>
+    </row>
+    <row r="47" spans="2:55">
+      <c r="B47" s="39">
+        <f t="shared" si="0"/>
+        <v>36</v>
+      </c>
+      <c r="C47" s="119" t="s">
+        <v>147</v>
+      </c>
+      <c r="D47" s="20"/>
+      <c r="E47" s="20"/>
+      <c r="F47" s="20"/>
+      <c r="G47" s="20"/>
+      <c r="H47" s="20"/>
+      <c r="I47" s="20"/>
+      <c r="J47" s="20"/>
+      <c r="K47" s="21"/>
+      <c r="L47" s="119" t="s">
+        <v>200</v>
+      </c>
+      <c r="M47" s="20"/>
+      <c r="N47" s="20"/>
+      <c r="O47" s="20"/>
+      <c r="P47" s="20"/>
+      <c r="Q47" s="20"/>
+      <c r="R47" s="20"/>
+      <c r="S47" s="20"/>
+      <c r="T47" s="21"/>
+      <c r="U47" s="120" t="s">
+        <v>82</v>
+      </c>
+      <c r="V47" s="121"/>
+      <c r="W47" s="121"/>
+      <c r="X47" s="121"/>
+      <c r="Y47" s="121"/>
+      <c r="Z47" s="122"/>
+      <c r="AA47" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB47" s="124"/>
+      <c r="AC47" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD47" s="124"/>
+      <c r="AE47" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AF47" s="124"/>
+      <c r="AG47" s="120" t="s">
+        <v>71</v>
+      </c>
+      <c r="AH47" s="121"/>
+      <c r="AI47" s="121"/>
+      <c r="AJ47" s="121"/>
+      <c r="AK47" s="122"/>
+      <c r="AL47" s="120" t="s">
+        <v>69</v>
+      </c>
+      <c r="AM47" s="20"/>
+      <c r="AN47" s="20"/>
+      <c r="AO47" s="20"/>
+      <c r="AP47" s="20"/>
+      <c r="AQ47" s="20"/>
+      <c r="AR47" s="20"/>
+      <c r="AS47" s="20"/>
+      <c r="AT47" s="20"/>
+      <c r="AU47" s="20"/>
+      <c r="AV47" s="20"/>
+      <c r="AW47" s="20"/>
+      <c r="AX47" s="20"/>
+      <c r="AY47" s="20"/>
+      <c r="AZ47" s="20"/>
+      <c r="BA47" s="20"/>
+      <c r="BB47" s="20"/>
+      <c r="BC47" s="21"/>
+    </row>
+    <row r="48" spans="2:55">
+      <c r="B48" s="39">
+        <f t="shared" si="0"/>
+        <v>37</v>
+      </c>
+      <c r="C48" s="119" t="s">
+        <v>148</v>
+      </c>
+      <c r="D48" s="20"/>
+      <c r="E48" s="20"/>
+      <c r="F48" s="20"/>
+      <c r="G48" s="20"/>
+      <c r="H48" s="20"/>
+      <c r="I48" s="20"/>
+      <c r="J48" s="20"/>
+      <c r="K48" s="21"/>
+      <c r="L48" s="119" t="s">
+        <v>201</v>
+      </c>
+      <c r="M48" s="20"/>
+      <c r="N48" s="20"/>
+      <c r="O48" s="20"/>
+      <c r="P48" s="20"/>
+      <c r="Q48" s="20"/>
+      <c r="R48" s="20"/>
+      <c r="S48" s="20"/>
+      <c r="T48" s="21"/>
+      <c r="U48" s="120" t="s">
+        <v>82</v>
+      </c>
+      <c r="V48" s="121"/>
+      <c r="W48" s="121"/>
+      <c r="X48" s="121"/>
+      <c r="Y48" s="121"/>
+      <c r="Z48" s="122"/>
+      <c r="AA48" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB48" s="124"/>
+      <c r="AC48" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD48" s="124"/>
+      <c r="AE48" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AF48" s="124"/>
+      <c r="AG48" s="120" t="s">
+        <v>71</v>
+      </c>
+      <c r="AH48" s="121"/>
+      <c r="AI48" s="121"/>
+      <c r="AJ48" s="121"/>
+      <c r="AK48" s="122"/>
+      <c r="AL48" s="120" t="s">
+        <v>69</v>
+      </c>
+      <c r="AM48" s="20"/>
+      <c r="AN48" s="20"/>
+      <c r="AO48" s="20"/>
+      <c r="AP48" s="20"/>
+      <c r="AQ48" s="20"/>
+      <c r="AR48" s="20"/>
+      <c r="AS48" s="20"/>
+      <c r="AT48" s="20"/>
+      <c r="AU48" s="20"/>
+      <c r="AV48" s="20"/>
+      <c r="AW48" s="20"/>
+      <c r="AX48" s="20"/>
+      <c r="AY48" s="20"/>
+      <c r="AZ48" s="20"/>
+      <c r="BA48" s="20"/>
+      <c r="BB48" s="20"/>
+      <c r="BC48" s="21"/>
+    </row>
+    <row r="49" spans="2:55">
+      <c r="B49" s="39">
+        <f t="shared" si="0"/>
+        <v>38</v>
+      </c>
+      <c r="C49" s="119" t="s">
+        <v>149</v>
+      </c>
+      <c r="D49" s="20"/>
+      <c r="E49" s="20"/>
+      <c r="F49" s="20"/>
+      <c r="G49" s="20"/>
+      <c r="H49" s="20"/>
+      <c r="I49" s="20"/>
+      <c r="J49" s="20"/>
+      <c r="K49" s="21"/>
+      <c r="L49" s="119" t="s">
+        <v>202</v>
+      </c>
+      <c r="M49" s="20"/>
+      <c r="N49" s="20"/>
+      <c r="O49" s="20"/>
+      <c r="P49" s="20"/>
+      <c r="Q49" s="20"/>
+      <c r="R49" s="20"/>
+      <c r="S49" s="20"/>
+      <c r="T49" s="21"/>
+      <c r="U49" s="120" t="s">
+        <v>82</v>
+      </c>
+      <c r="V49" s="121"/>
+      <c r="W49" s="121"/>
+      <c r="X49" s="121"/>
+      <c r="Y49" s="121"/>
+      <c r="Z49" s="122"/>
+      <c r="AA49" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB49" s="124"/>
+      <c r="AC49" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD49" s="124"/>
+      <c r="AE49" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AF49" s="124"/>
+      <c r="AG49" s="120" t="s">
+        <v>71</v>
+      </c>
+      <c r="AH49" s="121"/>
+      <c r="AI49" s="121"/>
+      <c r="AJ49" s="121"/>
+      <c r="AK49" s="122"/>
+      <c r="AL49" s="120" t="s">
+        <v>69</v>
+      </c>
+      <c r="AM49" s="20"/>
+      <c r="AN49" s="20"/>
+      <c r="AO49" s="20"/>
+      <c r="AP49" s="20"/>
+      <c r="AQ49" s="20"/>
+      <c r="AR49" s="20"/>
+      <c r="AS49" s="20"/>
+      <c r="AT49" s="20"/>
+      <c r="AU49" s="20"/>
+      <c r="AV49" s="20"/>
+      <c r="AW49" s="20"/>
+      <c r="AX49" s="20"/>
+      <c r="AY49" s="20"/>
+      <c r="AZ49" s="20"/>
+      <c r="BA49" s="20"/>
+      <c r="BB49" s="20"/>
+      <c r="BC49" s="21"/>
+    </row>
+    <row r="50" spans="2:55">
+      <c r="B50" s="39">
+        <f t="shared" si="0"/>
+        <v>39</v>
+      </c>
+      <c r="C50" s="119" t="s">
+        <v>150</v>
+      </c>
+      <c r="D50" s="20"/>
+      <c r="E50" s="20"/>
+      <c r="F50" s="20"/>
+      <c r="G50" s="20"/>
+      <c r="H50" s="20"/>
+      <c r="I50" s="20"/>
+      <c r="J50" s="20"/>
+      <c r="K50" s="21"/>
+      <c r="L50" s="119" t="s">
+        <v>203</v>
+      </c>
+      <c r="M50" s="20"/>
+      <c r="N50" s="20"/>
+      <c r="O50" s="20"/>
+      <c r="P50" s="20"/>
+      <c r="Q50" s="20"/>
+      <c r="R50" s="20"/>
+      <c r="S50" s="20"/>
+      <c r="T50" s="21"/>
+      <c r="U50" s="120" t="s">
+        <v>82</v>
+      </c>
+      <c r="V50" s="121"/>
+      <c r="W50" s="121"/>
+      <c r="X50" s="121"/>
+      <c r="Y50" s="121"/>
+      <c r="Z50" s="122"/>
+      <c r="AA50" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB50" s="124"/>
+      <c r="AC50" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD50" s="124"/>
+      <c r="AE50" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AF50" s="124"/>
+      <c r="AG50" s="120" t="s">
+        <v>71</v>
+      </c>
+      <c r="AH50" s="121"/>
+      <c r="AI50" s="121"/>
+      <c r="AJ50" s="121"/>
+      <c r="AK50" s="122"/>
+      <c r="AL50" s="120" t="s">
+        <v>69</v>
+      </c>
+      <c r="AM50" s="20"/>
+      <c r="AN50" s="20"/>
+      <c r="AO50" s="20"/>
+      <c r="AP50" s="20"/>
+      <c r="AQ50" s="20"/>
+      <c r="AR50" s="20"/>
+      <c r="AS50" s="20"/>
+      <c r="AT50" s="20"/>
+      <c r="AU50" s="20"/>
+      <c r="AV50" s="20"/>
+      <c r="AW50" s="20"/>
+      <c r="AX50" s="20"/>
+      <c r="AY50" s="20"/>
+      <c r="AZ50" s="20"/>
+      <c r="BA50" s="20"/>
+      <c r="BB50" s="20"/>
+      <c r="BC50" s="21"/>
+    </row>
+    <row r="51" spans="2:55">
+      <c r="B51" s="39">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="C51" s="119" t="s">
+        <v>151</v>
+      </c>
+      <c r="D51" s="20"/>
+      <c r="E51" s="20"/>
+      <c r="F51" s="20"/>
+      <c r="G51" s="20"/>
+      <c r="H51" s="20"/>
+      <c r="I51" s="20"/>
+      <c r="J51" s="20"/>
+      <c r="K51" s="21"/>
+      <c r="L51" s="119" t="s">
+        <v>204</v>
+      </c>
+      <c r="M51" s="20"/>
+      <c r="N51" s="20"/>
+      <c r="O51" s="20"/>
+      <c r="P51" s="20"/>
+      <c r="Q51" s="20"/>
+      <c r="R51" s="20"/>
+      <c r="S51" s="20"/>
+      <c r="T51" s="21"/>
+      <c r="U51" s="120" t="s">
+        <v>82</v>
+      </c>
+      <c r="V51" s="121"/>
+      <c r="W51" s="121"/>
+      <c r="X51" s="121"/>
+      <c r="Y51" s="121"/>
+      <c r="Z51" s="122"/>
+      <c r="AA51" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB51" s="124"/>
+      <c r="AC51" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD51" s="124"/>
+      <c r="AE51" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AF51" s="124"/>
+      <c r="AG51" s="120" t="s">
+        <v>71</v>
+      </c>
+      <c r="AH51" s="121"/>
+      <c r="AI51" s="121"/>
+      <c r="AJ51" s="121"/>
+      <c r="AK51" s="122"/>
+      <c r="AL51" s="120" t="s">
+        <v>69</v>
+      </c>
+      <c r="AM51" s="20"/>
+      <c r="AN51" s="20"/>
+      <c r="AO51" s="20"/>
+      <c r="AP51" s="20"/>
+      <c r="AQ51" s="20"/>
+      <c r="AR51" s="20"/>
+      <c r="AS51" s="20"/>
+      <c r="AT51" s="20"/>
+      <c r="AU51" s="20"/>
+      <c r="AV51" s="20"/>
+      <c r="AW51" s="20"/>
+      <c r="AX51" s="20"/>
+      <c r="AY51" s="20"/>
+      <c r="AZ51" s="20"/>
+      <c r="BA51" s="20"/>
+      <c r="BB51" s="20"/>
+      <c r="BC51" s="21"/>
+    </row>
+    <row r="52" spans="2:55">
+      <c r="B52" s="39">
+        <f t="shared" si="0"/>
+        <v>41</v>
+      </c>
+      <c r="C52" s="119" t="s">
+        <v>152</v>
+      </c>
+      <c r="D52" s="20"/>
+      <c r="E52" s="20"/>
+      <c r="F52" s="20"/>
+      <c r="G52" s="20"/>
+      <c r="H52" s="20"/>
+      <c r="I52" s="20"/>
+      <c r="J52" s="20"/>
+      <c r="K52" s="21"/>
+      <c r="L52" s="119" t="s">
+        <v>205</v>
+      </c>
+      <c r="M52" s="20"/>
+      <c r="N52" s="20"/>
+      <c r="O52" s="20"/>
+      <c r="P52" s="20"/>
+      <c r="Q52" s="20"/>
+      <c r="R52" s="20"/>
+      <c r="S52" s="20"/>
+      <c r="T52" s="21"/>
+      <c r="U52" s="120" t="s">
+        <v>82</v>
+      </c>
+      <c r="V52" s="121"/>
+      <c r="W52" s="121"/>
+      <c r="X52" s="121"/>
+      <c r="Y52" s="121"/>
+      <c r="Z52" s="122"/>
+      <c r="AA52" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB52" s="124"/>
+      <c r="AC52" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD52" s="124"/>
+      <c r="AE52" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AF52" s="124"/>
+      <c r="AG52" s="120" t="s">
+        <v>71</v>
+      </c>
+      <c r="AH52" s="121"/>
+      <c r="AI52" s="121"/>
+      <c r="AJ52" s="121"/>
+      <c r="AK52" s="122"/>
+      <c r="AL52" s="120" t="s">
+        <v>69</v>
+      </c>
+      <c r="AM52" s="20"/>
+      <c r="AN52" s="20"/>
+      <c r="AO52" s="20"/>
+      <c r="AP52" s="20"/>
+      <c r="AQ52" s="20"/>
+      <c r="AR52" s="20"/>
+      <c r="AS52" s="20"/>
+      <c r="AT52" s="20"/>
+      <c r="AU52" s="20"/>
+      <c r="AV52" s="20"/>
+      <c r="AW52" s="20"/>
+      <c r="AX52" s="20"/>
+      <c r="AY52" s="20"/>
+      <c r="AZ52" s="20"/>
+      <c r="BA52" s="20"/>
+      <c r="BB52" s="20"/>
+      <c r="BC52" s="21"/>
+    </row>
+    <row r="53" spans="2:55">
+      <c r="B53" s="39">
+        <f t="shared" si="0"/>
+        <v>42</v>
+      </c>
+      <c r="C53" s="119" t="s">
+        <v>153</v>
+      </c>
+      <c r="D53" s="20"/>
+      <c r="E53" s="20"/>
+      <c r="F53" s="20"/>
+      <c r="G53" s="20"/>
+      <c r="H53" s="20"/>
+      <c r="I53" s="20"/>
+      <c r="J53" s="20"/>
+      <c r="K53" s="21"/>
+      <c r="L53" s="119" t="s">
+        <v>206</v>
+      </c>
+      <c r="M53" s="20"/>
+      <c r="N53" s="20"/>
+      <c r="O53" s="20"/>
+      <c r="P53" s="20"/>
+      <c r="Q53" s="20"/>
+      <c r="R53" s="20"/>
+      <c r="S53" s="20"/>
+      <c r="T53" s="21"/>
+      <c r="U53" s="120" t="s">
+        <v>82</v>
+      </c>
+      <c r="V53" s="121"/>
+      <c r="W53" s="121"/>
+      <c r="X53" s="121"/>
+      <c r="Y53" s="121"/>
+      <c r="Z53" s="122"/>
+      <c r="AA53" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB53" s="124"/>
+      <c r="AC53" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD53" s="124"/>
+      <c r="AE53" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AF53" s="124"/>
+      <c r="AG53" s="120" t="s">
+        <v>71</v>
+      </c>
+      <c r="AH53" s="121"/>
+      <c r="AI53" s="121"/>
+      <c r="AJ53" s="121"/>
+      <c r="AK53" s="122"/>
+      <c r="AL53" s="120" t="s">
+        <v>69</v>
+      </c>
+      <c r="AM53" s="20"/>
+      <c r="AN53" s="20"/>
+      <c r="AO53" s="20"/>
+      <c r="AP53" s="20"/>
+      <c r="AQ53" s="20"/>
+      <c r="AR53" s="20"/>
+      <c r="AS53" s="20"/>
+      <c r="AT53" s="20"/>
+      <c r="AU53" s="20"/>
+      <c r="AV53" s="20"/>
+      <c r="AW53" s="20"/>
+      <c r="AX53" s="20"/>
+      <c r="AY53" s="20"/>
+      <c r="AZ53" s="20"/>
+      <c r="BA53" s="20"/>
+      <c r="BB53" s="20"/>
+      <c r="BC53" s="21"/>
+    </row>
+    <row r="54" spans="2:55">
+      <c r="B54" s="39">
+        <f t="shared" si="0"/>
+        <v>43</v>
+      </c>
+      <c r="C54" s="119" t="s">
+        <v>154</v>
+      </c>
+      <c r="D54" s="20"/>
+      <c r="E54" s="20"/>
+      <c r="F54" s="20"/>
+      <c r="G54" s="20"/>
+      <c r="H54" s="20"/>
+      <c r="I54" s="20"/>
+      <c r="J54" s="20"/>
+      <c r="K54" s="21"/>
+      <c r="L54" s="119" t="s">
+        <v>207</v>
+      </c>
+      <c r="M54" s="20"/>
+      <c r="N54" s="20"/>
+      <c r="O54" s="20"/>
+      <c r="P54" s="20"/>
+      <c r="Q54" s="20"/>
+      <c r="R54" s="20"/>
+      <c r="S54" s="20"/>
+      <c r="T54" s="21"/>
+      <c r="U54" s="120" t="s">
+        <v>82</v>
+      </c>
+      <c r="V54" s="121"/>
+      <c r="W54" s="121"/>
+      <c r="X54" s="121"/>
+      <c r="Y54" s="121"/>
+      <c r="Z54" s="122"/>
+      <c r="AA54" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB54" s="124"/>
+      <c r="AC54" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD54" s="124"/>
+      <c r="AE54" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AF54" s="124"/>
+      <c r="AG54" s="120" t="s">
+        <v>71</v>
+      </c>
+      <c r="AH54" s="121"/>
+      <c r="AI54" s="121"/>
+      <c r="AJ54" s="121"/>
+      <c r="AK54" s="122"/>
+      <c r="AL54" s="120" t="s">
+        <v>69</v>
+      </c>
+      <c r="AM54" s="20"/>
+      <c r="AN54" s="20"/>
+      <c r="AO54" s="20"/>
+      <c r="AP54" s="20"/>
+      <c r="AQ54" s="20"/>
+      <c r="AR54" s="20"/>
+      <c r="AS54" s="20"/>
+      <c r="AT54" s="20"/>
+      <c r="AU54" s="20"/>
+      <c r="AV54" s="20"/>
+      <c r="AW54" s="20"/>
+      <c r="AX54" s="20"/>
+      <c r="AY54" s="20"/>
+      <c r="AZ54" s="20"/>
+      <c r="BA54" s="20"/>
+      <c r="BB54" s="20"/>
+      <c r="BC54" s="21"/>
+    </row>
+    <row r="55" spans="2:55">
+      <c r="B55" s="39">
+        <f t="shared" si="0"/>
+        <v>44</v>
+      </c>
+      <c r="C55" s="119" t="s">
+        <v>155</v>
+      </c>
+      <c r="D55" s="20"/>
+      <c r="E55" s="20"/>
+      <c r="F55" s="20"/>
+      <c r="G55" s="20"/>
+      <c r="H55" s="20"/>
+      <c r="I55" s="20"/>
+      <c r="J55" s="20"/>
+      <c r="K55" s="21"/>
+      <c r="L55" s="119" t="s">
+        <v>208</v>
+      </c>
+      <c r="M55" s="20"/>
+      <c r="N55" s="20"/>
+      <c r="O55" s="20"/>
+      <c r="P55" s="20"/>
+      <c r="Q55" s="20"/>
+      <c r="R55" s="20"/>
+      <c r="S55" s="20"/>
+      <c r="T55" s="21"/>
+      <c r="U55" s="120" t="s">
+        <v>82</v>
+      </c>
+      <c r="V55" s="121"/>
+      <c r="W55" s="121"/>
+      <c r="X55" s="121"/>
+      <c r="Y55" s="121"/>
+      <c r="Z55" s="122"/>
+      <c r="AA55" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB55" s="124"/>
+      <c r="AC55" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD55" s="124"/>
+      <c r="AE55" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AF55" s="124"/>
+      <c r="AG55" s="120" t="s">
+        <v>71</v>
+      </c>
+      <c r="AH55" s="121"/>
+      <c r="AI55" s="121"/>
+      <c r="AJ55" s="121"/>
+      <c r="AK55" s="122"/>
+      <c r="AL55" s="120" t="s">
+        <v>69</v>
+      </c>
+      <c r="AM55" s="20"/>
+      <c r="AN55" s="20"/>
+      <c r="AO55" s="20"/>
+      <c r="AP55" s="20"/>
+      <c r="AQ55" s="20"/>
+      <c r="AR55" s="20"/>
+      <c r="AS55" s="20"/>
+      <c r="AT55" s="20"/>
+      <c r="AU55" s="20"/>
+      <c r="AV55" s="20"/>
+      <c r="AW55" s="20"/>
+      <c r="AX55" s="20"/>
+      <c r="AY55" s="20"/>
+      <c r="AZ55" s="20"/>
+      <c r="BA55" s="20"/>
+      <c r="BB55" s="20"/>
+      <c r="BC55" s="21"/>
+    </row>
+    <row r="56" spans="2:55">
+      <c r="B56" s="39">
+        <f t="shared" si="0"/>
+        <v>45</v>
+      </c>
+      <c r="C56" s="119" t="s">
+        <v>156</v>
+      </c>
+      <c r="D56" s="20"/>
+      <c r="E56" s="20"/>
+      <c r="F56" s="20"/>
+      <c r="G56" s="20"/>
+      <c r="H56" s="20"/>
+      <c r="I56" s="20"/>
+      <c r="J56" s="20"/>
+      <c r="K56" s="21"/>
+      <c r="L56" s="119" t="s">
+        <v>209</v>
+      </c>
+      <c r="M56" s="20"/>
+      <c r="N56" s="20"/>
+      <c r="O56" s="20"/>
+      <c r="P56" s="20"/>
+      <c r="Q56" s="20"/>
+      <c r="R56" s="20"/>
+      <c r="S56" s="20"/>
+      <c r="T56" s="21"/>
+      <c r="U56" s="120" t="s">
+        <v>82</v>
+      </c>
+      <c r="V56" s="121"/>
+      <c r="W56" s="121"/>
+      <c r="X56" s="121"/>
+      <c r="Y56" s="121"/>
+      <c r="Z56" s="122"/>
+      <c r="AA56" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB56" s="124"/>
+      <c r="AC56" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD56" s="124"/>
+      <c r="AE56" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AF56" s="124"/>
+      <c r="AG56" s="120" t="s">
+        <v>71</v>
+      </c>
+      <c r="AH56" s="121"/>
+      <c r="AI56" s="121"/>
+      <c r="AJ56" s="121"/>
+      <c r="AK56" s="122"/>
+      <c r="AL56" s="120" t="s">
+        <v>69</v>
+      </c>
+      <c r="AM56" s="20"/>
+      <c r="AN56" s="20"/>
+      <c r="AO56" s="20"/>
+      <c r="AP56" s="20"/>
+      <c r="AQ56" s="20"/>
+      <c r="AR56" s="20"/>
+      <c r="AS56" s="20"/>
+      <c r="AT56" s="20"/>
+      <c r="AU56" s="20"/>
+      <c r="AV56" s="20"/>
+      <c r="AW56" s="20"/>
+      <c r="AX56" s="20"/>
+      <c r="AY56" s="20"/>
+      <c r="AZ56" s="20"/>
+      <c r="BA56" s="20"/>
+      <c r="BB56" s="20"/>
+      <c r="BC56" s="21"/>
+    </row>
+    <row r="57" spans="2:55">
+      <c r="B57" s="39">
+        <f t="shared" si="0"/>
+        <v>46</v>
+      </c>
+      <c r="C57" s="119" t="s">
+        <v>157</v>
+      </c>
+      <c r="D57" s="20"/>
+      <c r="E57" s="20"/>
+      <c r="F57" s="20"/>
+      <c r="G57" s="20"/>
+      <c r="H57" s="20"/>
+      <c r="I57" s="20"/>
+      <c r="J57" s="20"/>
+      <c r="K57" s="21"/>
+      <c r="L57" s="119" t="s">
+        <v>110</v>
+      </c>
+      <c r="M57" s="20"/>
+      <c r="N57" s="20"/>
+      <c r="O57" s="20"/>
+      <c r="P57" s="20"/>
+      <c r="Q57" s="20"/>
+      <c r="R57" s="20"/>
+      <c r="S57" s="20"/>
+      <c r="T57" s="21"/>
+      <c r="U57" s="120" t="s">
+        <v>82</v>
+      </c>
+      <c r="V57" s="121"/>
+      <c r="W57" s="121"/>
+      <c r="X57" s="121"/>
+      <c r="Y57" s="121"/>
+      <c r="Z57" s="122"/>
+      <c r="AA57" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB57" s="124"/>
+      <c r="AC57" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD57" s="124"/>
+      <c r="AE57" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AF57" s="124"/>
+      <c r="AG57" s="120" t="s">
+        <v>71</v>
+      </c>
+      <c r="AH57" s="121"/>
+      <c r="AI57" s="121"/>
+      <c r="AJ57" s="121"/>
+      <c r="AK57" s="122"/>
+      <c r="AL57" s="120" t="s">
+        <v>69</v>
+      </c>
+      <c r="AM57" s="20"/>
+      <c r="AN57" s="20"/>
+      <c r="AO57" s="20"/>
+      <c r="AP57" s="20"/>
+      <c r="AQ57" s="20"/>
+      <c r="AR57" s="20"/>
+      <c r="AS57" s="20"/>
+      <c r="AT57" s="20"/>
+      <c r="AU57" s="20"/>
+      <c r="AV57" s="20"/>
+      <c r="AW57" s="20"/>
+      <c r="AX57" s="20"/>
+      <c r="AY57" s="20"/>
+      <c r="AZ57" s="20"/>
+      <c r="BA57" s="20"/>
+      <c r="BB57" s="20"/>
+      <c r="BC57" s="21"/>
+    </row>
+    <row r="58" spans="2:55">
+      <c r="B58" s="39">
+        <f t="shared" si="0"/>
+        <v>47</v>
+      </c>
+      <c r="C58" s="119" t="s">
+        <v>158</v>
+      </c>
+      <c r="D58" s="20"/>
+      <c r="E58" s="20"/>
+      <c r="F58" s="20"/>
+      <c r="G58" s="20"/>
+      <c r="H58" s="20"/>
+      <c r="I58" s="20"/>
+      <c r="J58" s="20"/>
+      <c r="K58" s="21"/>
+      <c r="L58" s="119" t="s">
+        <v>210</v>
+      </c>
+      <c r="M58" s="20"/>
+      <c r="N58" s="20"/>
+      <c r="O58" s="20"/>
+      <c r="P58" s="20"/>
+      <c r="Q58" s="20"/>
+      <c r="R58" s="20"/>
+      <c r="S58" s="20"/>
+      <c r="T58" s="21"/>
+      <c r="U58" s="120" t="s">
+        <v>82</v>
+      </c>
+      <c r="V58" s="121"/>
+      <c r="W58" s="121"/>
+      <c r="X58" s="121"/>
+      <c r="Y58" s="121"/>
+      <c r="Z58" s="122"/>
+      <c r="AA58" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB58" s="124"/>
+      <c r="AC58" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD58" s="124"/>
+      <c r="AE58" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AF58" s="124"/>
+      <c r="AG58" s="120" t="s">
+        <v>71</v>
+      </c>
+      <c r="AH58" s="121"/>
+      <c r="AI58" s="121"/>
+      <c r="AJ58" s="121"/>
+      <c r="AK58" s="122"/>
+      <c r="AL58" s="120" t="s">
+        <v>69</v>
+      </c>
+      <c r="AM58" s="20"/>
+      <c r="AN58" s="20"/>
+      <c r="AO58" s="20"/>
+      <c r="AP58" s="20"/>
+      <c r="AQ58" s="20"/>
+      <c r="AR58" s="20"/>
+      <c r="AS58" s="20"/>
+      <c r="AT58" s="20"/>
+      <c r="AU58" s="20"/>
+      <c r="AV58" s="20"/>
+      <c r="AW58" s="20"/>
+      <c r="AX58" s="20"/>
+      <c r="AY58" s="20"/>
+      <c r="AZ58" s="20"/>
+      <c r="BA58" s="20"/>
+      <c r="BB58" s="20"/>
+      <c r="BC58" s="21"/>
+    </row>
+    <row r="59" spans="2:55">
+      <c r="B59" s="39">
+        <f t="shared" si="0"/>
+        <v>48</v>
+      </c>
+      <c r="C59" s="119" t="s">
+        <v>159</v>
+      </c>
+      <c r="D59" s="20"/>
+      <c r="E59" s="20"/>
+      <c r="F59" s="20"/>
+      <c r="G59" s="20"/>
+      <c r="H59" s="20"/>
+      <c r="I59" s="20"/>
+      <c r="J59" s="20"/>
+      <c r="K59" s="21"/>
+      <c r="L59" s="119" t="s">
+        <v>111</v>
+      </c>
+      <c r="M59" s="20"/>
+      <c r="N59" s="20"/>
+      <c r="O59" s="20"/>
+      <c r="P59" s="20"/>
+      <c r="Q59" s="20"/>
+      <c r="R59" s="20"/>
+      <c r="S59" s="20"/>
+      <c r="T59" s="21"/>
+      <c r="U59" s="120" t="s">
+        <v>82</v>
+      </c>
+      <c r="V59" s="121"/>
+      <c r="W59" s="121"/>
+      <c r="X59" s="121"/>
+      <c r="Y59" s="121"/>
+      <c r="Z59" s="122"/>
+      <c r="AA59" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB59" s="124"/>
+      <c r="AC59" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD59" s="124"/>
+      <c r="AE59" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AF59" s="124"/>
+      <c r="AG59" s="120" t="s">
+        <v>71</v>
+      </c>
+      <c r="AH59" s="121"/>
+      <c r="AI59" s="121"/>
+      <c r="AJ59" s="121"/>
+      <c r="AK59" s="122"/>
+      <c r="AL59" s="120" t="s">
+        <v>69</v>
+      </c>
+      <c r="AM59" s="20"/>
+      <c r="AN59" s="20"/>
+      <c r="AO59" s="20"/>
+      <c r="AP59" s="20"/>
+      <c r="AQ59" s="20"/>
+      <c r="AR59" s="20"/>
+      <c r="AS59" s="20"/>
+      <c r="AT59" s="20"/>
+      <c r="AU59" s="20"/>
+      <c r="AV59" s="20"/>
+      <c r="AW59" s="20"/>
+      <c r="AX59" s="20"/>
+      <c r="AY59" s="20"/>
+      <c r="AZ59" s="20"/>
+      <c r="BA59" s="20"/>
+      <c r="BB59" s="20"/>
+      <c r="BC59" s="21"/>
+    </row>
+    <row r="60" spans="2:55">
+      <c r="B60" s="39">
+        <f t="shared" si="0"/>
+        <v>49</v>
+      </c>
+      <c r="C60" s="119" t="s">
+        <v>160</v>
+      </c>
+      <c r="D60" s="20"/>
+      <c r="E60" s="20"/>
+      <c r="F60" s="20"/>
+      <c r="G60" s="20"/>
+      <c r="H60" s="20"/>
+      <c r="I60" s="20"/>
+      <c r="J60" s="20"/>
+      <c r="K60" s="21"/>
+      <c r="L60" s="119" t="s">
+        <v>211</v>
+      </c>
+      <c r="M60" s="20"/>
+      <c r="N60" s="20"/>
+      <c r="O60" s="20"/>
+      <c r="P60" s="20"/>
+      <c r="Q60" s="20"/>
+      <c r="R60" s="20"/>
+      <c r="S60" s="20"/>
+      <c r="T60" s="21"/>
+      <c r="U60" s="120" t="s">
+        <v>82</v>
+      </c>
+      <c r="V60" s="121"/>
+      <c r="W60" s="121"/>
+      <c r="X60" s="121"/>
+      <c r="Y60" s="121"/>
+      <c r="Z60" s="122"/>
+      <c r="AA60" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB60" s="124"/>
+      <c r="AC60" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD60" s="124"/>
+      <c r="AE60" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AF60" s="124"/>
+      <c r="AG60" s="120" t="s">
+        <v>71</v>
+      </c>
+      <c r="AH60" s="121"/>
+      <c r="AI60" s="121"/>
+      <c r="AJ60" s="121"/>
+      <c r="AK60" s="122"/>
+      <c r="AL60" s="120" t="s">
+        <v>69</v>
+      </c>
+      <c r="AM60" s="20"/>
+      <c r="AN60" s="20"/>
+      <c r="AO60" s="20"/>
+      <c r="AP60" s="20"/>
+      <c r="AQ60" s="20"/>
+      <c r="AR60" s="20"/>
+      <c r="AS60" s="20"/>
+      <c r="AT60" s="20"/>
+      <c r="AU60" s="20"/>
+      <c r="AV60" s="20"/>
+      <c r="AW60" s="20"/>
+      <c r="AX60" s="20"/>
+      <c r="AY60" s="20"/>
+      <c r="AZ60" s="20"/>
+      <c r="BA60" s="20"/>
+      <c r="BB60" s="20"/>
+      <c r="BC60" s="21"/>
+    </row>
+    <row r="61" spans="2:55">
+      <c r="B61" s="39">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="C61" s="119" t="s">
+        <v>161</v>
+      </c>
+      <c r="D61" s="20"/>
+      <c r="E61" s="20"/>
+      <c r="F61" s="20"/>
+      <c r="G61" s="20"/>
+      <c r="H61" s="20"/>
+      <c r="I61" s="20"/>
+      <c r="J61" s="20"/>
+      <c r="K61" s="21"/>
+      <c r="L61" s="119" t="s">
+        <v>112</v>
+      </c>
+      <c r="M61" s="20"/>
+      <c r="N61" s="20"/>
+      <c r="O61" s="20"/>
+      <c r="P61" s="20"/>
+      <c r="Q61" s="20"/>
+      <c r="R61" s="20"/>
+      <c r="S61" s="20"/>
+      <c r="T61" s="21"/>
+      <c r="U61" s="120" t="s">
+        <v>82</v>
+      </c>
+      <c r="V61" s="121"/>
+      <c r="W61" s="121"/>
+      <c r="X61" s="121"/>
+      <c r="Y61" s="121"/>
+      <c r="Z61" s="122"/>
+      <c r="AA61" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB61" s="124"/>
+      <c r="AC61" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD61" s="124"/>
+      <c r="AE61" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AF61" s="124"/>
+      <c r="AG61" s="120" t="s">
+        <v>71</v>
+      </c>
+      <c r="AH61" s="121"/>
+      <c r="AI61" s="121"/>
+      <c r="AJ61" s="121"/>
+      <c r="AK61" s="122"/>
+      <c r="AL61" s="120" t="s">
+        <v>69</v>
+      </c>
+      <c r="AM61" s="20"/>
+      <c r="AN61" s="20"/>
+      <c r="AO61" s="20"/>
+      <c r="AP61" s="20"/>
+      <c r="AQ61" s="20"/>
+      <c r="AR61" s="20"/>
+      <c r="AS61" s="20"/>
+      <c r="AT61" s="20"/>
+      <c r="AU61" s="20"/>
+      <c r="AV61" s="20"/>
+      <c r="AW61" s="20"/>
+      <c r="AX61" s="20"/>
+      <c r="AY61" s="20"/>
+      <c r="AZ61" s="20"/>
+      <c r="BA61" s="20"/>
+      <c r="BB61" s="20"/>
+      <c r="BC61" s="21"/>
+    </row>
+    <row r="62" spans="2:55">
+      <c r="B62" s="39">
+        <f t="shared" si="0"/>
+        <v>51</v>
+      </c>
+      <c r="C62" s="119" t="s">
+        <v>162</v>
+      </c>
+      <c r="D62" s="20"/>
+      <c r="E62" s="20"/>
+      <c r="F62" s="20"/>
+      <c r="G62" s="20"/>
+      <c r="H62" s="20"/>
+      <c r="I62" s="20"/>
+      <c r="J62" s="20"/>
+      <c r="K62" s="21"/>
+      <c r="L62" s="119" t="s">
+        <v>212</v>
+      </c>
+      <c r="M62" s="20"/>
+      <c r="N62" s="20"/>
+      <c r="O62" s="20"/>
+      <c r="P62" s="20"/>
+      <c r="Q62" s="20"/>
+      <c r="R62" s="20"/>
+      <c r="S62" s="20"/>
+      <c r="T62" s="21"/>
+      <c r="U62" s="120" t="s">
+        <v>82</v>
+      </c>
+      <c r="V62" s="121"/>
+      <c r="W62" s="121"/>
+      <c r="X62" s="121"/>
+      <c r="Y62" s="121"/>
+      <c r="Z62" s="122"/>
+      <c r="AA62" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB62" s="124"/>
+      <c r="AC62" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD62" s="124"/>
+      <c r="AE62" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AF62" s="124"/>
+      <c r="AG62" s="120" t="s">
+        <v>71</v>
+      </c>
+      <c r="AH62" s="121"/>
+      <c r="AI62" s="121"/>
+      <c r="AJ62" s="121"/>
+      <c r="AK62" s="122"/>
+      <c r="AL62" s="120" t="s">
+        <v>69</v>
+      </c>
+      <c r="AM62" s="20"/>
+      <c r="AN62" s="20"/>
+      <c r="AO62" s="20"/>
+      <c r="AP62" s="20"/>
+      <c r="AQ62" s="20"/>
+      <c r="AR62" s="20"/>
+      <c r="AS62" s="20"/>
+      <c r="AT62" s="20"/>
+      <c r="AU62" s="20"/>
+      <c r="AV62" s="20"/>
+      <c r="AW62" s="20"/>
+      <c r="AX62" s="20"/>
+      <c r="AY62" s="20"/>
+      <c r="AZ62" s="20"/>
+      <c r="BA62" s="20"/>
+      <c r="BB62" s="20"/>
+      <c r="BC62" s="21"/>
+    </row>
+    <row r="63" spans="2:55">
+      <c r="B63" s="39">
+        <f t="shared" si="0"/>
+        <v>52</v>
+      </c>
+      <c r="C63" s="119" t="s">
+        <v>163</v>
+      </c>
+      <c r="D63" s="20"/>
+      <c r="E63" s="20"/>
+      <c r="F63" s="20"/>
+      <c r="G63" s="20"/>
+      <c r="H63" s="20"/>
+      <c r="I63" s="20"/>
+      <c r="J63" s="20"/>
+      <c r="K63" s="21"/>
+      <c r="L63" s="119" t="s">
+        <v>113</v>
+      </c>
+      <c r="M63" s="20"/>
+      <c r="N63" s="20"/>
+      <c r="O63" s="20"/>
+      <c r="P63" s="20"/>
+      <c r="Q63" s="20"/>
+      <c r="R63" s="20"/>
+      <c r="S63" s="20"/>
+      <c r="T63" s="21"/>
+      <c r="U63" s="120" t="s">
+        <v>82</v>
+      </c>
+      <c r="V63" s="121"/>
+      <c r="W63" s="121"/>
+      <c r="X63" s="121"/>
+      <c r="Y63" s="121"/>
+      <c r="Z63" s="122"/>
+      <c r="AA63" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB63" s="124"/>
+      <c r="AC63" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD63" s="124"/>
+      <c r="AE63" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AF63" s="124"/>
+      <c r="AG63" s="120" t="s">
+        <v>71</v>
+      </c>
+      <c r="AH63" s="121"/>
+      <c r="AI63" s="121"/>
+      <c r="AJ63" s="121"/>
+      <c r="AK63" s="122"/>
+      <c r="AL63" s="120" t="s">
+        <v>69</v>
+      </c>
+      <c r="AM63" s="20"/>
+      <c r="AN63" s="20"/>
+      <c r="AO63" s="20"/>
+      <c r="AP63" s="20"/>
+      <c r="AQ63" s="20"/>
+      <c r="AR63" s="20"/>
+      <c r="AS63" s="20"/>
+      <c r="AT63" s="20"/>
+      <c r="AU63" s="20"/>
+      <c r="AV63" s="20"/>
+      <c r="AW63" s="20"/>
+      <c r="AX63" s="20"/>
+      <c r="AY63" s="20"/>
+      <c r="AZ63" s="20"/>
+      <c r="BA63" s="20"/>
+      <c r="BB63" s="20"/>
+      <c r="BC63" s="21"/>
+    </row>
+    <row r="64" spans="2:55">
+      <c r="B64" s="39">
+        <f t="shared" si="0"/>
+        <v>53</v>
+      </c>
+      <c r="C64" s="119" t="s">
+        <v>164</v>
+      </c>
+      <c r="D64" s="20"/>
+      <c r="E64" s="20"/>
+      <c r="F64" s="20"/>
+      <c r="G64" s="20"/>
+      <c r="H64" s="20"/>
+      <c r="I64" s="20"/>
+      <c r="J64" s="20"/>
+      <c r="K64" s="21"/>
+      <c r="L64" s="119" t="s">
+        <v>213</v>
+      </c>
+      <c r="M64" s="20"/>
+      <c r="N64" s="20"/>
+      <c r="O64" s="20"/>
+      <c r="P64" s="20"/>
+      <c r="Q64" s="20"/>
+      <c r="R64" s="20"/>
+      <c r="S64" s="20"/>
+      <c r="T64" s="21"/>
+      <c r="U64" s="120" t="s">
+        <v>82</v>
+      </c>
+      <c r="V64" s="121"/>
+      <c r="W64" s="121"/>
+      <c r="X64" s="121"/>
+      <c r="Y64" s="121"/>
+      <c r="Z64" s="122"/>
+      <c r="AA64" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB64" s="124"/>
+      <c r="AC64" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD64" s="124"/>
+      <c r="AE64" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AF64" s="124"/>
+      <c r="AG64" s="120" t="s">
+        <v>71</v>
+      </c>
+      <c r="AH64" s="121"/>
+      <c r="AI64" s="121"/>
+      <c r="AJ64" s="121"/>
+      <c r="AK64" s="122"/>
+      <c r="AL64" s="120" t="s">
+        <v>69</v>
+      </c>
+      <c r="AM64" s="20"/>
+      <c r="AN64" s="20"/>
+      <c r="AO64" s="20"/>
+      <c r="AP64" s="20"/>
+      <c r="AQ64" s="20"/>
+      <c r="AR64" s="20"/>
+      <c r="AS64" s="20"/>
+      <c r="AT64" s="20"/>
+      <c r="AU64" s="20"/>
+      <c r="AV64" s="20"/>
+      <c r="AW64" s="20"/>
+      <c r="AX64" s="20"/>
+      <c r="AY64" s="20"/>
+      <c r="AZ64" s="20"/>
+      <c r="BA64" s="20"/>
+      <c r="BB64" s="20"/>
+      <c r="BC64" s="21"/>
+    </row>
+    <row r="65" spans="2:55">
+      <c r="B65" s="39">
+        <f t="shared" si="0"/>
+        <v>54</v>
+      </c>
+      <c r="C65" s="119" t="s">
+        <v>165</v>
+      </c>
+      <c r="D65" s="20"/>
+      <c r="E65" s="20"/>
+      <c r="F65" s="20"/>
+      <c r="G65" s="20"/>
+      <c r="H65" s="20"/>
+      <c r="I65" s="20"/>
+      <c r="J65" s="20"/>
+      <c r="K65" s="21"/>
+      <c r="L65" s="119" t="s">
+        <v>114</v>
+      </c>
+      <c r="M65" s="20"/>
+      <c r="N65" s="20"/>
+      <c r="O65" s="20"/>
+      <c r="P65" s="20"/>
+      <c r="Q65" s="20"/>
+      <c r="R65" s="20"/>
+      <c r="S65" s="20"/>
+      <c r="T65" s="21"/>
+      <c r="U65" s="120" t="s">
+        <v>82</v>
+      </c>
+      <c r="V65" s="121"/>
+      <c r="W65" s="121"/>
+      <c r="X65" s="121"/>
+      <c r="Y65" s="121"/>
+      <c r="Z65" s="122"/>
+      <c r="AA65" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB65" s="124"/>
+      <c r="AC65" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD65" s="124"/>
+      <c r="AE65" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AF65" s="124"/>
+      <c r="AG65" s="120" t="s">
+        <v>71</v>
+      </c>
+      <c r="AH65" s="121"/>
+      <c r="AI65" s="121"/>
+      <c r="AJ65" s="121"/>
+      <c r="AK65" s="122"/>
+      <c r="AL65" s="120" t="s">
+        <v>69</v>
+      </c>
+      <c r="AM65" s="20"/>
+      <c r="AN65" s="20"/>
+      <c r="AO65" s="20"/>
+      <c r="AP65" s="20"/>
+      <c r="AQ65" s="20"/>
+      <c r="AR65" s="20"/>
+      <c r="AS65" s="20"/>
+      <c r="AT65" s="20"/>
+      <c r="AU65" s="20"/>
+      <c r="AV65" s="20"/>
+      <c r="AW65" s="20"/>
+      <c r="AX65" s="20"/>
+      <c r="AY65" s="20"/>
+      <c r="AZ65" s="20"/>
+      <c r="BA65" s="20"/>
+      <c r="BB65" s="20"/>
+      <c r="BC65" s="21"/>
+    </row>
+    <row r="66" spans="2:55">
+      <c r="B66" s="39">
+        <f t="shared" si="0"/>
+        <v>55</v>
+      </c>
+      <c r="C66" s="119" t="s">
+        <v>166</v>
+      </c>
+      <c r="D66" s="20"/>
+      <c r="E66" s="20"/>
+      <c r="F66" s="20"/>
+      <c r="G66" s="20"/>
+      <c r="H66" s="20"/>
+      <c r="I66" s="20"/>
+      <c r="J66" s="20"/>
+      <c r="K66" s="21"/>
+      <c r="L66" s="119" t="s">
+        <v>214</v>
+      </c>
+      <c r="M66" s="20"/>
+      <c r="N66" s="20"/>
+      <c r="O66" s="20"/>
+      <c r="P66" s="20"/>
+      <c r="Q66" s="20"/>
+      <c r="R66" s="20"/>
+      <c r="S66" s="20"/>
+      <c r="T66" s="21"/>
+      <c r="U66" s="120" t="s">
+        <v>82</v>
+      </c>
+      <c r="V66" s="121"/>
+      <c r="W66" s="121"/>
+      <c r="X66" s="121"/>
+      <c r="Y66" s="121"/>
+      <c r="Z66" s="122"/>
+      <c r="AA66" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB66" s="124"/>
+      <c r="AC66" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD66" s="124"/>
+      <c r="AE66" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AF66" s="124"/>
+      <c r="AG66" s="120" t="s">
+        <v>71</v>
+      </c>
+      <c r="AH66" s="121"/>
+      <c r="AI66" s="121"/>
+      <c r="AJ66" s="121"/>
+      <c r="AK66" s="122"/>
+      <c r="AL66" s="120" t="s">
+        <v>69</v>
+      </c>
+      <c r="AM66" s="20"/>
+      <c r="AN66" s="20"/>
+      <c r="AO66" s="20"/>
+      <c r="AP66" s="20"/>
+      <c r="AQ66" s="20"/>
+      <c r="AR66" s="20"/>
+      <c r="AS66" s="20"/>
+      <c r="AT66" s="20"/>
+      <c r="AU66" s="20"/>
+      <c r="AV66" s="20"/>
+      <c r="AW66" s="20"/>
+      <c r="AX66" s="20"/>
+      <c r="AY66" s="20"/>
+      <c r="AZ66" s="20"/>
+      <c r="BA66" s="20"/>
+      <c r="BB66" s="20"/>
+      <c r="BC66" s="21"/>
+    </row>
+    <row r="67" spans="2:55">
+      <c r="B67" s="39">
+        <f t="shared" si="0"/>
+        <v>56</v>
+      </c>
+      <c r="C67" s="119" t="s">
+        <v>167</v>
+      </c>
+      <c r="D67" s="20"/>
+      <c r="E67" s="20"/>
+      <c r="F67" s="20"/>
+      <c r="G67" s="20"/>
+      <c r="H67" s="20"/>
+      <c r="I67" s="20"/>
+      <c r="J67" s="20"/>
+      <c r="K67" s="21"/>
+      <c r="L67" s="119" t="s">
+        <v>115</v>
+      </c>
+      <c r="M67" s="20"/>
+      <c r="N67" s="20"/>
+      <c r="O67" s="20"/>
+      <c r="P67" s="20"/>
+      <c r="Q67" s="20"/>
+      <c r="R67" s="20"/>
+      <c r="S67" s="20"/>
+      <c r="T67" s="21"/>
+      <c r="U67" s="120" t="s">
+        <v>82</v>
+      </c>
+      <c r="V67" s="121"/>
+      <c r="W67" s="121"/>
+      <c r="X67" s="121"/>
+      <c r="Y67" s="121"/>
+      <c r="Z67" s="122"/>
+      <c r="AA67" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB67" s="124"/>
+      <c r="AC67" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD67" s="124"/>
+      <c r="AE67" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AF67" s="124"/>
+      <c r="AG67" s="120" t="s">
+        <v>71</v>
+      </c>
+      <c r="AH67" s="121"/>
+      <c r="AI67" s="121"/>
+      <c r="AJ67" s="121"/>
+      <c r="AK67" s="122"/>
+      <c r="AL67" s="120" t="s">
+        <v>69</v>
+      </c>
+      <c r="AM67" s="20"/>
+      <c r="AN67" s="20"/>
+      <c r="AO67" s="20"/>
+      <c r="AP67" s="20"/>
+      <c r="AQ67" s="20"/>
+      <c r="AR67" s="20"/>
+      <c r="AS67" s="20"/>
+      <c r="AT67" s="20"/>
+      <c r="AU67" s="20"/>
+      <c r="AV67" s="20"/>
+      <c r="AW67" s="20"/>
+      <c r="AX67" s="20"/>
+      <c r="AY67" s="20"/>
+      <c r="AZ67" s="20"/>
+      <c r="BA67" s="20"/>
+      <c r="BB67" s="20"/>
+      <c r="BC67" s="21"/>
+    </row>
+    <row r="68" spans="2:55">
+      <c r="B68" s="39">
+        <f t="shared" si="0"/>
+        <v>57</v>
+      </c>
+      <c r="C68" s="119" t="s">
+        <v>168</v>
+      </c>
+      <c r="D68" s="20"/>
+      <c r="E68" s="20"/>
+      <c r="F68" s="20"/>
+      <c r="G68" s="20"/>
+      <c r="H68" s="20"/>
+      <c r="I68" s="20"/>
+      <c r="J68" s="20"/>
+      <c r="K68" s="21"/>
+      <c r="L68" s="119" t="s">
+        <v>116</v>
+      </c>
+      <c r="M68" s="20"/>
+      <c r="N68" s="20"/>
+      <c r="O68" s="20"/>
+      <c r="P68" s="20"/>
+      <c r="Q68" s="20"/>
+      <c r="R68" s="20"/>
+      <c r="S68" s="20"/>
+      <c r="T68" s="21"/>
+      <c r="U68" s="120" t="s">
+        <v>82</v>
+      </c>
+      <c r="V68" s="121"/>
+      <c r="W68" s="121"/>
+      <c r="X68" s="121"/>
+      <c r="Y68" s="121"/>
+      <c r="Z68" s="122"/>
+      <c r="AA68" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB68" s="124"/>
+      <c r="AC68" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD68" s="124"/>
+      <c r="AE68" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AF68" s="124"/>
+      <c r="AG68" s="120" t="s">
+        <v>71</v>
+      </c>
+      <c r="AH68" s="121"/>
+      <c r="AI68" s="121"/>
+      <c r="AJ68" s="121"/>
+      <c r="AK68" s="122"/>
+      <c r="AL68" s="120" t="s">
+        <v>69</v>
+      </c>
+      <c r="AM68" s="20"/>
+      <c r="AN68" s="20"/>
+      <c r="AO68" s="20"/>
+      <c r="AP68" s="20"/>
+      <c r="AQ68" s="20"/>
+      <c r="AR68" s="20"/>
+      <c r="AS68" s="20"/>
+      <c r="AT68" s="20"/>
+      <c r="AU68" s="20"/>
+      <c r="AV68" s="20"/>
+      <c r="AW68" s="20"/>
+      <c r="AX68" s="20"/>
+      <c r="AY68" s="20"/>
+      <c r="AZ68" s="20"/>
+      <c r="BA68" s="20"/>
+      <c r="BB68" s="20"/>
+      <c r="BC68" s="21"/>
+    </row>
+    <row r="69" spans="2:55">
+      <c r="B69" s="39">
+        <f t="shared" si="0"/>
+        <v>58</v>
+      </c>
+      <c r="C69" s="119" t="s">
+        <v>169</v>
+      </c>
+      <c r="D69" s="20"/>
+      <c r="E69" s="20"/>
+      <c r="F69" s="20"/>
+      <c r="G69" s="20"/>
+      <c r="H69" s="20"/>
+      <c r="I69" s="20"/>
+      <c r="J69" s="20"/>
+      <c r="K69" s="21"/>
+      <c r="L69" s="119" t="s">
+        <v>117</v>
+      </c>
+      <c r="M69" s="20"/>
+      <c r="N69" s="20"/>
+      <c r="O69" s="20"/>
+      <c r="P69" s="20"/>
+      <c r="Q69" s="20"/>
+      <c r="R69" s="20"/>
+      <c r="S69" s="20"/>
+      <c r="T69" s="21"/>
+      <c r="U69" s="120" t="s">
+        <v>82</v>
+      </c>
+      <c r="V69" s="121"/>
+      <c r="W69" s="121"/>
+      <c r="X69" s="121"/>
+      <c r="Y69" s="121"/>
+      <c r="Z69" s="122"/>
+      <c r="AA69" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB69" s="124"/>
+      <c r="AC69" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD69" s="124"/>
+      <c r="AE69" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AF69" s="124"/>
+      <c r="AG69" s="120" t="s">
+        <v>71</v>
+      </c>
+      <c r="AH69" s="121"/>
+      <c r="AI69" s="121"/>
+      <c r="AJ69" s="121"/>
+      <c r="AK69" s="122"/>
+      <c r="AL69" s="120" t="s">
+        <v>69</v>
+      </c>
+      <c r="AM69" s="20"/>
+      <c r="AN69" s="20"/>
+      <c r="AO69" s="20"/>
+      <c r="AP69" s="20"/>
+      <c r="AQ69" s="20"/>
+      <c r="AR69" s="20"/>
+      <c r="AS69" s="20"/>
+      <c r="AT69" s="20"/>
+      <c r="AU69" s="20"/>
+      <c r="AV69" s="20"/>
+      <c r="AW69" s="20"/>
+      <c r="AX69" s="20"/>
+      <c r="AY69" s="20"/>
+      <c r="AZ69" s="20"/>
+      <c r="BA69" s="20"/>
+      <c r="BB69" s="20"/>
+      <c r="BC69" s="21"/>
+    </row>
+    <row r="70" spans="2:55">
+      <c r="B70" s="39">
+        <f t="shared" si="0"/>
+        <v>59</v>
+      </c>
+      <c r="C70" s="119" t="s">
+        <v>170</v>
+      </c>
+      <c r="D70" s="20"/>
+      <c r="E70" s="20"/>
+      <c r="F70" s="20"/>
+      <c r="G70" s="20"/>
+      <c r="H70" s="20"/>
+      <c r="I70" s="20"/>
+      <c r="J70" s="20"/>
+      <c r="K70" s="21"/>
+      <c r="L70" s="119" t="s">
+        <v>118</v>
+      </c>
+      <c r="M70" s="20"/>
+      <c r="N70" s="20"/>
+      <c r="O70" s="20"/>
+      <c r="P70" s="20"/>
+      <c r="Q70" s="20"/>
+      <c r="R70" s="20"/>
+      <c r="S70" s="20"/>
+      <c r="T70" s="21"/>
+      <c r="U70" s="120" t="s">
+        <v>82</v>
+      </c>
+      <c r="V70" s="121"/>
+      <c r="W70" s="121"/>
+      <c r="X70" s="121"/>
+      <c r="Y70" s="121"/>
+      <c r="Z70" s="122"/>
+      <c r="AA70" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB70" s="124"/>
+      <c r="AC70" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD70" s="124"/>
+      <c r="AE70" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AF70" s="124"/>
+      <c r="AG70" s="120" t="s">
+        <v>71</v>
+      </c>
+      <c r="AH70" s="121"/>
+      <c r="AI70" s="121"/>
+      <c r="AJ70" s="121"/>
+      <c r="AK70" s="122"/>
+      <c r="AL70" s="120" t="s">
+        <v>69</v>
+      </c>
+      <c r="AM70" s="20"/>
+      <c r="AN70" s="20"/>
+      <c r="AO70" s="20"/>
+      <c r="AP70" s="20"/>
+      <c r="AQ70" s="20"/>
+      <c r="AR70" s="20"/>
+      <c r="AS70" s="20"/>
+      <c r="AT70" s="20"/>
+      <c r="AU70" s="20"/>
+      <c r="AV70" s="20"/>
+      <c r="AW70" s="20"/>
+      <c r="AX70" s="20"/>
+      <c r="AY70" s="20"/>
+      <c r="AZ70" s="20"/>
+      <c r="BA70" s="20"/>
+      <c r="BB70" s="20"/>
+      <c r="BC70" s="21"/>
+    </row>
+    <row r="71" spans="2:55">
+      <c r="B71" s="39">
+        <f t="shared" si="0"/>
+        <v>60</v>
+      </c>
+      <c r="C71" s="119" t="s">
+        <v>171</v>
+      </c>
+      <c r="D71" s="20"/>
+      <c r="E71" s="20"/>
+      <c r="F71" s="20"/>
+      <c r="G71" s="20"/>
+      <c r="H71" s="20"/>
+      <c r="I71" s="20"/>
+      <c r="J71" s="20"/>
+      <c r="K71" s="21"/>
+      <c r="L71" s="119" t="s">
+        <v>119</v>
+      </c>
+      <c r="M71" s="20"/>
+      <c r="N71" s="20"/>
+      <c r="O71" s="20"/>
+      <c r="P71" s="20"/>
+      <c r="Q71" s="20"/>
+      <c r="R71" s="20"/>
+      <c r="S71" s="20"/>
+      <c r="T71" s="21"/>
+      <c r="U71" s="120" t="s">
+        <v>82</v>
+      </c>
+      <c r="V71" s="121"/>
+      <c r="W71" s="121"/>
+      <c r="X71" s="121"/>
+      <c r="Y71" s="121"/>
+      <c r="Z71" s="122"/>
+      <c r="AA71" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB71" s="124"/>
+      <c r="AC71" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD71" s="124"/>
+      <c r="AE71" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AF71" s="124"/>
+      <c r="AG71" s="120" t="s">
+        <v>71</v>
+      </c>
+      <c r="AH71" s="121"/>
+      <c r="AI71" s="121"/>
+      <c r="AJ71" s="121"/>
+      <c r="AK71" s="122"/>
+      <c r="AL71" s="120" t="s">
+        <v>69</v>
+      </c>
+      <c r="AM71" s="20"/>
+      <c r="AN71" s="20"/>
+      <c r="AO71" s="20"/>
+      <c r="AP71" s="20"/>
+      <c r="AQ71" s="20"/>
+      <c r="AR71" s="20"/>
+      <c r="AS71" s="20"/>
+      <c r="AT71" s="20"/>
+      <c r="AU71" s="20"/>
+      <c r="AV71" s="20"/>
+      <c r="AW71" s="20"/>
+      <c r="AX71" s="20"/>
+      <c r="AY71" s="20"/>
+      <c r="AZ71" s="20"/>
+      <c r="BA71" s="20"/>
+      <c r="BB71" s="20"/>
+      <c r="BC71" s="21"/>
+    </row>
+    <row r="72" spans="2:55">
+      <c r="B72" s="39">
+        <f t="shared" si="0"/>
+        <v>61</v>
+      </c>
+      <c r="C72" s="119" t="s">
+        <v>172</v>
+      </c>
+      <c r="D72" s="20"/>
+      <c r="E72" s="20"/>
+      <c r="F72" s="20"/>
+      <c r="G72" s="20"/>
+      <c r="H72" s="20"/>
+      <c r="I72" s="20"/>
+      <c r="J72" s="20"/>
+      <c r="K72" s="21"/>
+      <c r="L72" s="119" t="s">
+        <v>120</v>
+      </c>
+      <c r="M72" s="20"/>
+      <c r="N72" s="20"/>
+      <c r="O72" s="20"/>
+      <c r="P72" s="20"/>
+      <c r="Q72" s="20"/>
+      <c r="R72" s="20"/>
+      <c r="S72" s="20"/>
+      <c r="T72" s="21"/>
+      <c r="U72" s="120" t="s">
+        <v>82</v>
+      </c>
+      <c r="V72" s="121"/>
+      <c r="W72" s="121"/>
+      <c r="X72" s="121"/>
+      <c r="Y72" s="121"/>
+      <c r="Z72" s="122"/>
+      <c r="AA72" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB72" s="124"/>
+      <c r="AC72" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD72" s="124"/>
+      <c r="AE72" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AF72" s="124"/>
+      <c r="AG72" s="120" t="s">
+        <v>71</v>
+      </c>
+      <c r="AH72" s="121"/>
+      <c r="AI72" s="121"/>
+      <c r="AJ72" s="121"/>
+      <c r="AK72" s="122"/>
+      <c r="AL72" s="120" t="s">
+        <v>69</v>
+      </c>
+      <c r="AM72" s="20"/>
+      <c r="AN72" s="20"/>
+      <c r="AO72" s="20"/>
+      <c r="AP72" s="20"/>
+      <c r="AQ72" s="20"/>
+      <c r="AR72" s="20"/>
+      <c r="AS72" s="20"/>
+      <c r="AT72" s="20"/>
+      <c r="AU72" s="20"/>
+      <c r="AV72" s="20"/>
+      <c r="AW72" s="20"/>
+      <c r="AX72" s="20"/>
+      <c r="AY72" s="20"/>
+      <c r="AZ72" s="20"/>
+      <c r="BA72" s="20"/>
+      <c r="BB72" s="20"/>
+      <c r="BC72" s="21"/>
+    </row>
+    <row r="73" spans="2:55">
+      <c r="B73" s="39">
+        <f t="shared" si="0"/>
+        <v>62</v>
+      </c>
+      <c r="C73" s="119" t="s">
+        <v>173</v>
+      </c>
+      <c r="D73" s="20"/>
+      <c r="E73" s="20"/>
+      <c r="F73" s="20"/>
+      <c r="G73" s="20"/>
+      <c r="H73" s="20"/>
+      <c r="I73" s="20"/>
+      <c r="J73" s="20"/>
+      <c r="K73" s="21"/>
+      <c r="L73" s="119" t="s">
+        <v>121</v>
+      </c>
+      <c r="M73" s="20"/>
+      <c r="N73" s="20"/>
+      <c r="O73" s="20"/>
+      <c r="P73" s="20"/>
+      <c r="Q73" s="20"/>
+      <c r="R73" s="20"/>
+      <c r="S73" s="20"/>
+      <c r="T73" s="21"/>
+      <c r="U73" s="120" t="s">
+        <v>82</v>
+      </c>
+      <c r="V73" s="121"/>
+      <c r="W73" s="121"/>
+      <c r="X73" s="121"/>
+      <c r="Y73" s="121"/>
+      <c r="Z73" s="122"/>
+      <c r="AA73" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB73" s="124"/>
+      <c r="AC73" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD73" s="124"/>
+      <c r="AE73" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AF73" s="124"/>
+      <c r="AG73" s="120" t="s">
+        <v>71</v>
+      </c>
+      <c r="AH73" s="121"/>
+      <c r="AI73" s="121"/>
+      <c r="AJ73" s="121"/>
+      <c r="AK73" s="122"/>
+      <c r="AL73" s="120" t="s">
+        <v>69</v>
+      </c>
+      <c r="AM73" s="20"/>
+      <c r="AN73" s="20"/>
+      <c r="AO73" s="20"/>
+      <c r="AP73" s="20"/>
+      <c r="AQ73" s="20"/>
+      <c r="AR73" s="20"/>
+      <c r="AS73" s="20"/>
+      <c r="AT73" s="20"/>
+      <c r="AU73" s="20"/>
+      <c r="AV73" s="20"/>
+      <c r="AW73" s="20"/>
+      <c r="AX73" s="20"/>
+      <c r="AY73" s="20"/>
+      <c r="AZ73" s="20"/>
+      <c r="BA73" s="20"/>
+      <c r="BB73" s="20"/>
+      <c r="BC73" s="21"/>
+    </row>
+    <row r="74" spans="2:55">
+      <c r="B74" s="39">
+        <f t="shared" si="0"/>
+        <v>63</v>
+      </c>
+      <c r="C74" s="119" t="s">
+        <v>174</v>
+      </c>
+      <c r="D74" s="20"/>
+      <c r="E74" s="20"/>
+      <c r="F74" s="20"/>
+      <c r="G74" s="20"/>
+      <c r="H74" s="20"/>
+      <c r="I74" s="20"/>
+      <c r="J74" s="20"/>
+      <c r="K74" s="21"/>
+      <c r="L74" s="119" t="s">
+        <v>215</v>
+      </c>
+      <c r="M74" s="20"/>
+      <c r="N74" s="20"/>
+      <c r="O74" s="20"/>
+      <c r="P74" s="20"/>
+      <c r="Q74" s="20"/>
+      <c r="R74" s="20"/>
+      <c r="S74" s="20"/>
+      <c r="T74" s="21"/>
+      <c r="U74" s="120" t="s">
+        <v>82</v>
+      </c>
+      <c r="V74" s="121"/>
+      <c r="W74" s="121"/>
+      <c r="X74" s="121"/>
+      <c r="Y74" s="121"/>
+      <c r="Z74" s="122"/>
+      <c r="AA74" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB74" s="124"/>
+      <c r="AC74" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD74" s="124"/>
+      <c r="AE74" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AF74" s="124"/>
+      <c r="AG74" s="120" t="s">
+        <v>71</v>
+      </c>
+      <c r="AH74" s="121"/>
+      <c r="AI74" s="121"/>
+      <c r="AJ74" s="121"/>
+      <c r="AK74" s="122"/>
+      <c r="AL74" s="120" t="s">
+        <v>69</v>
+      </c>
+      <c r="AM74" s="20"/>
+      <c r="AN74" s="20"/>
+      <c r="AO74" s="20"/>
+      <c r="AP74" s="20"/>
+      <c r="AQ74" s="20"/>
+      <c r="AR74" s="20"/>
+      <c r="AS74" s="20"/>
+      <c r="AT74" s="20"/>
+      <c r="AU74" s="20"/>
+      <c r="AV74" s="20"/>
+      <c r="AW74" s="20"/>
+      <c r="AX74" s="20"/>
+      <c r="AY74" s="20"/>
+      <c r="AZ74" s="20"/>
+      <c r="BA74" s="20"/>
+      <c r="BB74" s="20"/>
+      <c r="BC74" s="21"/>
+    </row>
+    <row r="75" spans="2:55">
+      <c r="B75" s="39">
+        <f t="shared" si="0"/>
+        <v>64</v>
+      </c>
+      <c r="C75" s="119" t="s">
+        <v>175</v>
+      </c>
+      <c r="D75" s="20"/>
+      <c r="E75" s="20"/>
+      <c r="F75" s="20"/>
+      <c r="G75" s="20"/>
+      <c r="H75" s="20"/>
+      <c r="I75" s="20"/>
+      <c r="J75" s="20"/>
+      <c r="K75" s="21"/>
+      <c r="L75" s="119" t="s">
+        <v>122</v>
+      </c>
+      <c r="M75" s="20"/>
+      <c r="N75" s="20"/>
+      <c r="O75" s="20"/>
+      <c r="P75" s="20"/>
+      <c r="Q75" s="20"/>
+      <c r="R75" s="20"/>
+      <c r="S75" s="20"/>
+      <c r="T75" s="21"/>
+      <c r="U75" s="120" t="s">
+        <v>82</v>
+      </c>
+      <c r="V75" s="121"/>
+      <c r="W75" s="121"/>
+      <c r="X75" s="121"/>
+      <c r="Y75" s="121"/>
+      <c r="Z75" s="122"/>
+      <c r="AA75" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB75" s="124"/>
+      <c r="AC75" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD75" s="124"/>
+      <c r="AE75" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AF75" s="124"/>
+      <c r="AG75" s="120" t="s">
+        <v>71</v>
+      </c>
+      <c r="AH75" s="121"/>
+      <c r="AI75" s="121"/>
+      <c r="AJ75" s="121"/>
+      <c r="AK75" s="122"/>
+      <c r="AL75" s="120" t="s">
+        <v>69</v>
+      </c>
+      <c r="AM75" s="20"/>
+      <c r="AN75" s="20"/>
+      <c r="AO75" s="20"/>
+      <c r="AP75" s="20"/>
+      <c r="AQ75" s="20"/>
+      <c r="AR75" s="20"/>
+      <c r="AS75" s="20"/>
+      <c r="AT75" s="20"/>
+      <c r="AU75" s="20"/>
+      <c r="AV75" s="20"/>
+      <c r="AW75" s="20"/>
+      <c r="AX75" s="20"/>
+      <c r="AY75" s="20"/>
+      <c r="AZ75" s="20"/>
+      <c r="BA75" s="20"/>
+      <c r="BB75" s="20"/>
+      <c r="BC75" s="21"/>
+    </row>
+    <row r="76" spans="2:55">
+      <c r="B76" s="39">
+        <f t="shared" si="0"/>
+        <v>65</v>
+      </c>
+      <c r="C76" s="119" t="s">
+        <v>176</v>
+      </c>
+      <c r="D76" s="20"/>
+      <c r="E76" s="20"/>
+      <c r="F76" s="20"/>
+      <c r="G76" s="20"/>
+      <c r="H76" s="20"/>
+      <c r="I76" s="20"/>
+      <c r="J76" s="20"/>
+      <c r="K76" s="21"/>
+      <c r="L76" s="119" t="s">
+        <v>123</v>
+      </c>
+      <c r="M76" s="20"/>
+      <c r="N76" s="20"/>
+      <c r="O76" s="20"/>
+      <c r="P76" s="20"/>
+      <c r="Q76" s="20"/>
+      <c r="R76" s="20"/>
+      <c r="S76" s="20"/>
+      <c r="T76" s="21"/>
+      <c r="U76" s="120" t="s">
+        <v>82</v>
+      </c>
+      <c r="V76" s="121"/>
+      <c r="W76" s="121"/>
+      <c r="X76" s="121"/>
+      <c r="Y76" s="121"/>
+      <c r="Z76" s="122"/>
+      <c r="AA76" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB76" s="124"/>
+      <c r="AC76" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD76" s="124"/>
+      <c r="AE76" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AF76" s="124"/>
+      <c r="AG76" s="120" t="s">
+        <v>71</v>
+      </c>
+      <c r="AH76" s="121"/>
+      <c r="AI76" s="121"/>
+      <c r="AJ76" s="121"/>
+      <c r="AK76" s="122"/>
+      <c r="AL76" s="120" t="s">
+        <v>69</v>
+      </c>
+      <c r="AM76" s="20"/>
+      <c r="AN76" s="20"/>
+      <c r="AO76" s="20"/>
+      <c r="AP76" s="20"/>
+      <c r="AQ76" s="20"/>
+      <c r="AR76" s="20"/>
+      <c r="AS76" s="20"/>
+      <c r="AT76" s="20"/>
+      <c r="AU76" s="20"/>
+      <c r="AV76" s="20"/>
+      <c r="AW76" s="20"/>
+      <c r="AX76" s="20"/>
+      <c r="AY76" s="20"/>
+      <c r="AZ76" s="20"/>
+      <c r="BA76" s="20"/>
+      <c r="BB76" s="20"/>
+      <c r="BC76" s="21"/>
+    </row>
+    <row r="77" spans="2:55">
+      <c r="B77" s="39">
+        <f t="shared" si="0"/>
+        <v>66</v>
+      </c>
+      <c r="C77" s="119" t="s">
+        <v>177</v>
+      </c>
+      <c r="D77" s="20"/>
+      <c r="E77" s="20"/>
+      <c r="F77" s="20"/>
+      <c r="G77" s="20"/>
+      <c r="H77" s="20"/>
+      <c r="I77" s="20"/>
+      <c r="J77" s="20"/>
+      <c r="K77" s="21"/>
+      <c r="L77" s="119" t="s">
+        <v>124</v>
+      </c>
+      <c r="M77" s="20"/>
+      <c r="N77" s="20"/>
+      <c r="O77" s="20"/>
+      <c r="P77" s="20"/>
+      <c r="Q77" s="20"/>
+      <c r="R77" s="20"/>
+      <c r="S77" s="20"/>
+      <c r="T77" s="21"/>
+      <c r="U77" s="120" t="s">
+        <v>82</v>
+      </c>
+      <c r="V77" s="121"/>
+      <c r="W77" s="121"/>
+      <c r="X77" s="121"/>
+      <c r="Y77" s="121"/>
+      <c r="Z77" s="122"/>
+      <c r="AA77" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB77" s="124"/>
+      <c r="AC77" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD77" s="124"/>
+      <c r="AE77" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AF77" s="124"/>
+      <c r="AG77" s="120" t="s">
+        <v>71</v>
+      </c>
+      <c r="AH77" s="121"/>
+      <c r="AI77" s="121"/>
+      <c r="AJ77" s="121"/>
+      <c r="AK77" s="122"/>
+      <c r="AL77" s="120" t="s">
+        <v>69</v>
+      </c>
+      <c r="AM77" s="20"/>
+      <c r="AN77" s="20"/>
+      <c r="AO77" s="20"/>
+      <c r="AP77" s="20"/>
+      <c r="AQ77" s="20"/>
+      <c r="AR77" s="20"/>
+      <c r="AS77" s="20"/>
+      <c r="AT77" s="20"/>
+      <c r="AU77" s="20"/>
+      <c r="AV77" s="20"/>
+      <c r="AW77" s="20"/>
+      <c r="AX77" s="20"/>
+      <c r="AY77" s="20"/>
+      <c r="AZ77" s="20"/>
+      <c r="BA77" s="20"/>
+      <c r="BB77" s="20"/>
+      <c r="BC77" s="21"/>
+    </row>
+    <row r="78" spans="2:55">
+      <c r="B78" s="39">
+        <f t="shared" si="0"/>
+        <v>67</v>
+      </c>
+      <c r="C78" s="119" t="s">
+        <v>90</v>
+      </c>
+      <c r="D78" s="20"/>
+      <c r="E78" s="20"/>
+      <c r="F78" s="20"/>
+      <c r="G78" s="20"/>
+      <c r="H78" s="20"/>
+      <c r="I78" s="20"/>
+      <c r="J78" s="20"/>
+      <c r="K78" s="21"/>
+      <c r="L78" s="120" t="s">
+        <v>91</v>
+      </c>
+      <c r="M78" s="121"/>
+      <c r="N78" s="121"/>
+      <c r="O78" s="121"/>
+      <c r="P78" s="121"/>
+      <c r="Q78" s="121"/>
+      <c r="R78" s="121"/>
+      <c r="S78" s="121"/>
+      <c r="T78" s="122"/>
+      <c r="U78" s="120" t="s">
+        <v>81</v>
+      </c>
+      <c r="V78" s="121"/>
+      <c r="W78" s="121"/>
+      <c r="X78" s="121"/>
+      <c r="Y78" s="121"/>
+      <c r="Z78" s="122"/>
+      <c r="AA78" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB78" s="124"/>
+      <c r="AC78" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD78" s="124"/>
+      <c r="AE78" s="123" t="s">
+        <v>68</v>
+      </c>
+      <c r="AF78" s="124"/>
+      <c r="AG78" s="120" t="s">
+        <v>71</v>
+      </c>
+      <c r="AH78" s="121"/>
+      <c r="AI78" s="121"/>
+      <c r="AJ78" s="121"/>
+      <c r="AK78" s="122"/>
+      <c r="AL78" s="120" t="s">
+        <v>92</v>
+      </c>
+      <c r="AM78" s="121"/>
+      <c r="AN78" s="20"/>
+      <c r="AO78" s="20"/>
+      <c r="AP78" s="20"/>
+      <c r="AQ78" s="20"/>
+      <c r="AR78" s="20"/>
+      <c r="AS78" s="20"/>
+      <c r="AT78" s="20"/>
+      <c r="AU78" s="20"/>
+      <c r="AV78" s="20"/>
+      <c r="AW78" s="20"/>
+      <c r="AX78" s="20"/>
+      <c r="AY78" s="20"/>
+      <c r="AZ78" s="20"/>
+      <c r="BA78" s="20"/>
+      <c r="BB78" s="20"/>
+      <c r="BC78" s="21"/>
+    </row>
+    <row r="79" spans="2:55">
+      <c r="B79" s="39">
+        <f t="shared" si="0"/>
+        <v>68</v>
+      </c>
+      <c r="C79" s="119" t="s">
+        <v>93</v>
+      </c>
+      <c r="D79" s="119"/>
+      <c r="E79" s="20"/>
+      <c r="F79" s="20"/>
+      <c r="G79" s="20"/>
+      <c r="H79" s="20"/>
+      <c r="I79" s="20"/>
+      <c r="J79" s="20"/>
+      <c r="K79" s="21"/>
+      <c r="L79" s="119" t="s">
+        <v>97</v>
+      </c>
+      <c r="M79" s="20"/>
+      <c r="N79" s="20"/>
+      <c r="O79" s="20"/>
+      <c r="P79" s="20"/>
+      <c r="Q79" s="20"/>
+      <c r="R79" s="20"/>
+      <c r="S79" s="20"/>
+      <c r="T79" s="21"/>
+      <c r="U79" s="119" t="s">
+        <v>101</v>
+      </c>
+      <c r="V79" s="121"/>
+      <c r="W79" s="121"/>
+      <c r="X79" s="121"/>
+      <c r="Y79" s="121"/>
+      <c r="Z79" s="122"/>
+      <c r="AA79" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB79" s="124"/>
+      <c r="AC79" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD79" s="124"/>
+      <c r="AE79" s="123" t="s">
+        <v>68</v>
+      </c>
+      <c r="AF79" s="124"/>
+      <c r="AG79" s="120" t="s">
+        <v>71</v>
+      </c>
+      <c r="AH79" s="121"/>
+      <c r="AI79" s="121"/>
+      <c r="AJ79" s="121"/>
+      <c r="AK79" s="122"/>
+      <c r="AL79" s="120" t="s">
+        <v>69</v>
+      </c>
+      <c r="AM79" s="121"/>
+      <c r="AN79" s="20"/>
+      <c r="AO79" s="20"/>
+      <c r="AP79" s="20"/>
+      <c r="AQ79" s="20"/>
+      <c r="AR79" s="20"/>
+      <c r="AS79" s="20"/>
+      <c r="AT79" s="20"/>
+      <c r="AU79" s="20"/>
+      <c r="AV79" s="20"/>
+      <c r="AW79" s="20"/>
+      <c r="AX79" s="20"/>
+      <c r="AY79" s="20"/>
+      <c r="AZ79" s="20"/>
+      <c r="BA79" s="20"/>
+      <c r="BB79" s="20"/>
+      <c r="BC79" s="21"/>
+    </row>
+    <row r="80" spans="2:55">
+      <c r="B80" s="39">
+        <f t="shared" si="0"/>
+        <v>69</v>
+      </c>
+      <c r="C80" s="119" t="s">
+        <v>94</v>
+      </c>
+      <c r="D80" s="119"/>
+      <c r="E80" s="20"/>
+      <c r="F80" s="20"/>
+      <c r="G80" s="20"/>
+      <c r="H80" s="20"/>
+      <c r="I80" s="20"/>
+      <c r="J80" s="20"/>
+      <c r="K80" s="21"/>
+      <c r="L80" s="120" t="s">
+        <v>98</v>
+      </c>
+      <c r="M80" s="20"/>
+      <c r="N80" s="20"/>
+      <c r="O80" s="20"/>
+      <c r="P80" s="20"/>
+      <c r="Q80" s="20"/>
+      <c r="R80" s="20"/>
+      <c r="S80" s="20"/>
+      <c r="T80" s="21"/>
+      <c r="U80" s="119" t="s">
+        <v>82</v>
+      </c>
+      <c r="V80" s="121"/>
+      <c r="W80" s="121"/>
+      <c r="X80" s="121"/>
+      <c r="Y80" s="121"/>
+      <c r="Z80" s="122"/>
+      <c r="AA80" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB80" s="124"/>
+      <c r="AC80" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD80" s="124"/>
+      <c r="AE80" s="123" t="s">
+        <v>68</v>
+      </c>
+      <c r="AF80" s="124"/>
+      <c r="AG80" s="120" t="s">
+        <v>71</v>
+      </c>
+      <c r="AH80" s="121"/>
+      <c r="AI80" s="121"/>
+      <c r="AJ80" s="121"/>
+      <c r="AK80" s="122"/>
+      <c r="AL80" s="120" t="s">
+        <v>69</v>
+      </c>
+      <c r="AM80" s="121"/>
+      <c r="AN80" s="20"/>
+      <c r="AO80" s="20"/>
+      <c r="AP80" s="20"/>
+      <c r="AQ80" s="20"/>
+      <c r="AR80" s="20"/>
+      <c r="AS80" s="20"/>
+      <c r="AT80" s="20"/>
+      <c r="AU80" s="20"/>
+      <c r="AV80" s="20"/>
+      <c r="AW80" s="20"/>
+      <c r="AX80" s="20"/>
+      <c r="AY80" s="20"/>
+      <c r="AZ80" s="20"/>
+      <c r="BA80" s="20"/>
+      <c r="BB80" s="20"/>
+      <c r="BC80" s="21"/>
+    </row>
+    <row r="81" spans="1:55">
+      <c r="B81" s="39">
+        <f t="shared" si="0"/>
+        <v>70</v>
+      </c>
+      <c r="C81" s="119" t="s">
+        <v>95</v>
+      </c>
+      <c r="D81" s="119"/>
+      <c r="E81" s="20"/>
+      <c r="F81" s="20"/>
+      <c r="G81" s="20"/>
+      <c r="H81" s="20"/>
+      <c r="I81" s="20"/>
+      <c r="J81" s="20"/>
+      <c r="K81" s="21"/>
+      <c r="L81" s="120" t="s">
+        <v>99</v>
+      </c>
+      <c r="M81" s="20"/>
+      <c r="N81" s="20"/>
+      <c r="O81" s="20"/>
+      <c r="P81" s="20"/>
+      <c r="Q81" s="20"/>
+      <c r="R81" s="20"/>
+      <c r="S81" s="20"/>
+      <c r="T81" s="21"/>
+      <c r="U81" s="119" t="s">
+        <v>101</v>
+      </c>
+      <c r="V81" s="121"/>
+      <c r="W81" s="121"/>
+      <c r="X81" s="121"/>
+      <c r="Y81" s="121"/>
+      <c r="Z81" s="122"/>
+      <c r="AA81" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB81" s="124"/>
+      <c r="AC81" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD81" s="124"/>
+      <c r="AE81" s="123" t="s">
+        <v>68</v>
+      </c>
+      <c r="AF81" s="124"/>
+      <c r="AG81" s="120" t="s">
+        <v>71</v>
+      </c>
+      <c r="AH81" s="121"/>
+      <c r="AI81" s="121"/>
+      <c r="AJ81" s="121"/>
+      <c r="AK81" s="122"/>
+      <c r="AL81" s="120" t="s">
+        <v>69</v>
+      </c>
+      <c r="AM81" s="121"/>
+      <c r="AN81" s="20"/>
+      <c r="AO81" s="20"/>
+      <c r="AP81" s="20"/>
+      <c r="AQ81" s="20"/>
+      <c r="AR81" s="20"/>
+      <c r="AS81" s="20"/>
+      <c r="AT81" s="20"/>
+      <c r="AU81" s="20"/>
+      <c r="AV81" s="20"/>
+      <c r="AW81" s="20"/>
+      <c r="AX81" s="20"/>
+      <c r="AY81" s="20"/>
+      <c r="AZ81" s="20"/>
+      <c r="BA81" s="20"/>
+      <c r="BB81" s="20"/>
+      <c r="BC81" s="21"/>
+    </row>
+    <row r="82" spans="1:55">
+      <c r="B82" s="39">
+        <f t="shared" si="0"/>
+        <v>71</v>
+      </c>
+      <c r="C82" s="119" t="s">
+        <v>96</v>
+      </c>
+      <c r="D82" s="119"/>
+      <c r="E82" s="20"/>
+      <c r="F82" s="20"/>
+      <c r="G82" s="20"/>
+      <c r="H82" s="20"/>
+      <c r="I82" s="20"/>
+      <c r="J82" s="20"/>
+      <c r="K82" s="21"/>
+      <c r="L82" s="120" t="s">
+        <v>100</v>
+      </c>
+      <c r="M82" s="20"/>
+      <c r="N82" s="20"/>
+      <c r="O82" s="20"/>
+      <c r="P82" s="20"/>
+      <c r="Q82" s="20"/>
+      <c r="R82" s="20"/>
+      <c r="S82" s="20"/>
+      <c r="T82" s="21"/>
+      <c r="U82" s="119" t="s">
+        <v>82</v>
+      </c>
+      <c r="V82" s="121"/>
+      <c r="W82" s="121"/>
+      <c r="X82" s="121"/>
+      <c r="Y82" s="121"/>
+      <c r="Z82" s="122"/>
+      <c r="AA82" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB82" s="124"/>
+      <c r="AC82" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD82" s="124"/>
+      <c r="AE82" s="123" t="s">
+        <v>68</v>
+      </c>
+      <c r="AF82" s="124"/>
+      <c r="AG82" s="120" t="s">
+        <v>71</v>
+      </c>
+      <c r="AH82" s="121"/>
+      <c r="AI82" s="121"/>
+      <c r="AJ82" s="121"/>
+      <c r="AK82" s="122"/>
+      <c r="AL82" s="120" t="s">
+        <v>69</v>
+      </c>
+      <c r="AM82" s="121"/>
+      <c r="AN82" s="20"/>
+      <c r="AO82" s="20"/>
+      <c r="AP82" s="20"/>
+      <c r="AQ82" s="20"/>
+      <c r="AR82" s="20"/>
+      <c r="AS82" s="20"/>
+      <c r="AT82" s="20"/>
+      <c r="AU82" s="20"/>
+      <c r="AV82" s="20"/>
+      <c r="AW82" s="20"/>
+      <c r="AX82" s="20"/>
+      <c r="AY82" s="20"/>
+      <c r="AZ82" s="20"/>
+      <c r="BA82" s="20"/>
+      <c r="BB82" s="20"/>
+      <c r="BC82" s="21"/>
+    </row>
+    <row r="83" spans="1:55">
+      <c r="B83" s="39">
+        <f t="shared" si="0"/>
+        <v>72</v>
+      </c>
+      <c r="C83" s="19"/>
+      <c r="D83" s="20"/>
+      <c r="E83" s="20"/>
+      <c r="F83" s="20"/>
+      <c r="G83" s="20"/>
+      <c r="H83" s="20"/>
+      <c r="I83" s="20"/>
+      <c r="J83" s="20"/>
+      <c r="K83" s="21"/>
+      <c r="L83" s="19"/>
+      <c r="M83" s="20"/>
+      <c r="N83" s="20"/>
+      <c r="O83" s="20"/>
+      <c r="P83" s="20"/>
+      <c r="Q83" s="20"/>
+      <c r="R83" s="20"/>
+      <c r="S83" s="20"/>
+      <c r="T83" s="21"/>
+      <c r="U83" s="19"/>
+      <c r="V83" s="20"/>
+      <c r="W83" s="20"/>
+      <c r="X83" s="20"/>
+      <c r="Y83" s="20"/>
+      <c r="Z83" s="21"/>
+      <c r="AA83" s="43"/>
+      <c r="AB83" s="44"/>
+      <c r="AC83" s="43"/>
+      <c r="AD83" s="44"/>
+      <c r="AE83" s="43"/>
+      <c r="AF83" s="44"/>
+      <c r="AG83" s="19"/>
+      <c r="AH83" s="20"/>
+      <c r="AI83" s="20"/>
+      <c r="AJ83" s="20"/>
+      <c r="AK83" s="21"/>
+      <c r="AL83" s="19"/>
+      <c r="AM83" s="20"/>
+      <c r="AN83" s="20"/>
+      <c r="AO83" s="20"/>
+      <c r="AP83" s="20"/>
+      <c r="AQ83" s="20"/>
+      <c r="AR83" s="20"/>
+      <c r="AS83" s="20"/>
+      <c r="AT83" s="20"/>
+      <c r="AU83" s="20"/>
+      <c r="AV83" s="20"/>
+      <c r="AW83" s="20"/>
+      <c r="AX83" s="20"/>
+      <c r="AY83" s="20"/>
+      <c r="AZ83" s="20"/>
+      <c r="BA83" s="20"/>
+      <c r="BB83" s="20"/>
+      <c r="BC83" s="21"/>
+    </row>
+    <row r="84" spans="1:55">
+      <c r="B84" s="39">
+        <f t="shared" si="0"/>
+        <v>73</v>
+      </c>
+      <c r="C84" s="19"/>
+      <c r="D84" s="20"/>
+      <c r="E84" s="20"/>
+      <c r="F84" s="20"/>
+      <c r="G84" s="20"/>
+      <c r="H84" s="20"/>
+      <c r="I84" s="20"/>
+      <c r="J84" s="20"/>
+      <c r="K84" s="21"/>
+      <c r="L84" s="19"/>
+      <c r="M84" s="20"/>
+      <c r="N84" s="20"/>
+      <c r="O84" s="20"/>
+      <c r="P84" s="20"/>
+      <c r="Q84" s="20"/>
+      <c r="R84" s="20"/>
+      <c r="S84" s="20"/>
+      <c r="T84" s="21"/>
+      <c r="U84" s="19"/>
+      <c r="V84" s="20"/>
+      <c r="W84" s="20"/>
+      <c r="X84" s="20"/>
+      <c r="Y84" s="20"/>
+      <c r="Z84" s="21"/>
+      <c r="AA84" s="43"/>
+      <c r="AB84" s="44"/>
+      <c r="AC84" s="43"/>
+      <c r="AD84" s="44"/>
+      <c r="AE84" s="43"/>
+      <c r="AF84" s="44"/>
+      <c r="AG84" s="19"/>
+      <c r="AH84" s="20"/>
+      <c r="AI84" s="20"/>
+      <c r="AJ84" s="20"/>
+      <c r="AK84" s="21"/>
+      <c r="AL84" s="19"/>
+      <c r="AM84" s="20"/>
+      <c r="AN84" s="20"/>
+      <c r="AO84" s="20"/>
+      <c r="AP84" s="20"/>
+      <c r="AQ84" s="20"/>
+      <c r="AR84" s="20"/>
+      <c r="AS84" s="20"/>
+      <c r="AT84" s="20"/>
+      <c r="AU84" s="20"/>
+      <c r="AV84" s="20"/>
+      <c r="AW84" s="20"/>
+      <c r="AX84" s="20"/>
+      <c r="AY84" s="20"/>
+      <c r="AZ84" s="20"/>
+      <c r="BA84" s="20"/>
+      <c r="BB84" s="20"/>
+      <c r="BC84" s="21"/>
+    </row>
+    <row r="85" spans="1:55">
+      <c r="B85" s="39">
+        <f t="shared" si="0"/>
+        <v>74</v>
+      </c>
+      <c r="C85" s="19"/>
+      <c r="D85" s="20"/>
+      <c r="E85" s="20"/>
+      <c r="F85" s="20"/>
+      <c r="G85" s="20"/>
+      <c r="H85" s="20"/>
+      <c r="I85" s="20"/>
+      <c r="J85" s="20"/>
+      <c r="K85" s="21"/>
+      <c r="L85" s="19"/>
+      <c r="M85" s="20"/>
+      <c r="N85" s="20"/>
+      <c r="O85" s="20"/>
+      <c r="P85" s="20"/>
+      <c r="Q85" s="20"/>
+      <c r="R85" s="20"/>
+      <c r="S85" s="20"/>
+      <c r="T85" s="21"/>
+      <c r="U85" s="19"/>
+      <c r="V85" s="20"/>
+      <c r="W85" s="20"/>
+      <c r="X85" s="20"/>
+      <c r="Y85" s="20"/>
+      <c r="Z85" s="21"/>
+      <c r="AA85" s="113"/>
+      <c r="AB85" s="114"/>
+      <c r="AC85" s="113"/>
+      <c r="AD85" s="114"/>
+      <c r="AE85" s="113"/>
+      <c r="AF85" s="114"/>
+      <c r="AG85" s="19"/>
+      <c r="AH85" s="20"/>
+      <c r="AI85" s="20"/>
+      <c r="AJ85" s="20"/>
+      <c r="AK85" s="21"/>
+      <c r="AL85" s="19"/>
+      <c r="AM85" s="20"/>
+      <c r="AN85" s="20"/>
+      <c r="AO85" s="20"/>
+      <c r="AP85" s="20"/>
+      <c r="AQ85" s="20"/>
+      <c r="AR85" s="20"/>
+      <c r="AS85" s="20"/>
+      <c r="AT85" s="20"/>
+      <c r="AU85" s="20"/>
+      <c r="AV85" s="20"/>
+      <c r="AW85" s="20"/>
+      <c r="AX85" s="20"/>
+      <c r="AY85" s="20"/>
+      <c r="AZ85" s="20"/>
+      <c r="BA85" s="20"/>
+      <c r="BB85" s="20"/>
+      <c r="BC85" s="21"/>
+    </row>
+    <row r="86" spans="1:55">
+      <c r="B86" s="39">
+        <f t="shared" si="0"/>
+        <v>75</v>
+      </c>
+      <c r="C86" s="19"/>
+      <c r="D86" s="20"/>
+      <c r="E86" s="20"/>
+      <c r="F86" s="20"/>
+      <c r="G86" s="20"/>
+      <c r="H86" s="20"/>
+      <c r="I86" s="20"/>
+      <c r="J86" s="20"/>
+      <c r="K86" s="21"/>
+      <c r="L86" s="19"/>
+      <c r="M86" s="20"/>
+      <c r="N86" s="20"/>
+      <c r="O86" s="20"/>
+      <c r="P86" s="20"/>
+      <c r="Q86" s="20"/>
+      <c r="R86" s="20"/>
+      <c r="S86" s="20"/>
+      <c r="T86" s="21"/>
+      <c r="U86" s="19"/>
+      <c r="V86" s="20"/>
+      <c r="W86" s="20"/>
+      <c r="X86" s="20"/>
+      <c r="Y86" s="20"/>
+      <c r="Z86" s="21"/>
+      <c r="AA86" s="113"/>
+      <c r="AB86" s="114"/>
+      <c r="AC86" s="113"/>
+      <c r="AD86" s="114"/>
+      <c r="AE86" s="113"/>
+      <c r="AF86" s="114"/>
+      <c r="AG86" s="19"/>
+      <c r="AH86" s="20"/>
+      <c r="AI86" s="20"/>
+      <c r="AJ86" s="20"/>
+      <c r="AK86" s="21"/>
+      <c r="AL86" s="19"/>
+      <c r="AM86" s="20"/>
+      <c r="AN86" s="20"/>
+      <c r="AO86" s="20"/>
+      <c r="AP86" s="20"/>
+      <c r="AQ86" s="20"/>
+      <c r="AR86" s="20"/>
+      <c r="AS86" s="20"/>
+      <c r="AT86" s="20"/>
+      <c r="AU86" s="20"/>
+      <c r="AV86" s="20"/>
+      <c r="AW86" s="20"/>
+      <c r="AX86" s="20"/>
+      <c r="AY86" s="20"/>
+      <c r="AZ86" s="20"/>
+      <c r="BA86" s="20"/>
+      <c r="BB86" s="20"/>
+      <c r="BC86" s="21"/>
+    </row>
+    <row r="87" spans="1:55">
+      <c r="B87" s="39">
+        <f t="shared" si="0"/>
+        <v>76</v>
+      </c>
+      <c r="C87" s="19"/>
+      <c r="D87" s="20"/>
+      <c r="E87" s="20"/>
+      <c r="F87" s="20"/>
+      <c r="G87" s="20"/>
+      <c r="H87" s="20"/>
+      <c r="I87" s="20"/>
+      <c r="J87" s="20"/>
+      <c r="K87" s="21"/>
+      <c r="L87" s="19"/>
+      <c r="M87" s="20"/>
+      <c r="N87" s="20"/>
+      <c r="O87" s="20"/>
+      <c r="P87" s="20"/>
+      <c r="Q87" s="20"/>
+      <c r="R87" s="20"/>
+      <c r="S87" s="20"/>
+      <c r="T87" s="21"/>
+      <c r="U87" s="19"/>
+      <c r="V87" s="20"/>
+      <c r="W87" s="20"/>
+      <c r="X87" s="20"/>
+      <c r="Y87" s="20"/>
+      <c r="Z87" s="21"/>
+      <c r="AA87" s="113"/>
+      <c r="AB87" s="114"/>
+      <c r="AC87" s="113"/>
+      <c r="AD87" s="114"/>
+      <c r="AE87" s="113"/>
+      <c r="AF87" s="114"/>
+      <c r="AG87" s="19"/>
+      <c r="AH87" s="20"/>
+      <c r="AI87" s="20"/>
+      <c r="AJ87" s="20"/>
+      <c r="AK87" s="21"/>
+      <c r="AL87" s="19"/>
+      <c r="AM87" s="20"/>
+      <c r="AN87" s="20"/>
+      <c r="AO87" s="20"/>
+      <c r="AP87" s="20"/>
+      <c r="AQ87" s="20"/>
+      <c r="AR87" s="20"/>
+      <c r="AS87" s="20"/>
+      <c r="AT87" s="20"/>
+      <c r="AU87" s="20"/>
+      <c r="AV87" s="20"/>
+      <c r="AW87" s="20"/>
+      <c r="AX87" s="20"/>
+      <c r="AY87" s="20"/>
+      <c r="AZ87" s="20"/>
+      <c r="BA87" s="20"/>
+      <c r="BB87" s="20"/>
+      <c r="BC87" s="21"/>
+    </row>
+    <row r="88" spans="1:55">
+      <c r="B88" s="39">
+        <f t="shared" si="0"/>
+        <v>77</v>
+      </c>
+      <c r="C88" s="19"/>
+      <c r="D88" s="20"/>
+      <c r="E88" s="20"/>
+      <c r="F88" s="20"/>
+      <c r="G88" s="20"/>
+      <c r="H88" s="20"/>
+      <c r="I88" s="20"/>
+      <c r="J88" s="20"/>
+      <c r="K88" s="21"/>
+      <c r="L88" s="19"/>
+      <c r="M88" s="20"/>
+      <c r="N88" s="20"/>
+      <c r="O88" s="20"/>
+      <c r="P88" s="20"/>
+      <c r="Q88" s="20"/>
+      <c r="R88" s="20"/>
+      <c r="S88" s="20"/>
+      <c r="T88" s="21"/>
+      <c r="U88" s="19"/>
+      <c r="V88" s="20"/>
+      <c r="W88" s="20"/>
+      <c r="X88" s="20"/>
+      <c r="Y88" s="20"/>
+      <c r="Z88" s="21"/>
+      <c r="AA88" s="113"/>
+      <c r="AB88" s="114"/>
+      <c r="AC88" s="113"/>
+      <c r="AD88" s="114"/>
+      <c r="AE88" s="113"/>
+      <c r="AF88" s="114"/>
+      <c r="AG88" s="19"/>
+      <c r="AH88" s="20"/>
+      <c r="AI88" s="20"/>
+      <c r="AJ88" s="20"/>
+      <c r="AK88" s="21"/>
+      <c r="AL88" s="19"/>
+      <c r="AM88" s="20"/>
+      <c r="AN88" s="20"/>
+      <c r="AO88" s="20"/>
+      <c r="AP88" s="20"/>
+      <c r="AQ88" s="20"/>
+      <c r="AR88" s="20"/>
+      <c r="AS88" s="20"/>
+      <c r="AT88" s="20"/>
+      <c r="AU88" s="20"/>
+      <c r="AV88" s="20"/>
+      <c r="AW88" s="20"/>
+      <c r="AX88" s="20"/>
+      <c r="AY88" s="20"/>
+      <c r="AZ88" s="20"/>
+      <c r="BA88" s="20"/>
+      <c r="BB88" s="20"/>
+      <c r="BC88" s="21"/>
+    </row>
+    <row r="89" spans="1:55">
+      <c r="B89" s="39">
+        <f t="shared" si="0"/>
+        <v>78</v>
+      </c>
+      <c r="C89" s="19"/>
+      <c r="D89" s="20"/>
+      <c r="E89" s="20"/>
+      <c r="F89" s="20"/>
+      <c r="G89" s="20"/>
+      <c r="H89" s="20"/>
+      <c r="I89" s="20"/>
+      <c r="J89" s="20"/>
+      <c r="K89" s="21"/>
+      <c r="L89" s="19"/>
+      <c r="M89" s="20"/>
+      <c r="N89" s="20"/>
+      <c r="O89" s="20"/>
+      <c r="P89" s="20"/>
+      <c r="Q89" s="20"/>
+      <c r="R89" s="20"/>
+      <c r="S89" s="20"/>
+      <c r="T89" s="21"/>
+      <c r="U89" s="19"/>
+      <c r="V89" s="20"/>
+      <c r="W89" s="20"/>
+      <c r="X89" s="20"/>
+      <c r="Y89" s="20"/>
+      <c r="Z89" s="21"/>
+      <c r="AA89" s="113"/>
+      <c r="AB89" s="114"/>
+      <c r="AC89" s="113"/>
+      <c r="AD89" s="114"/>
+      <c r="AE89" s="113"/>
+      <c r="AF89" s="114"/>
+      <c r="AG89" s="19"/>
+      <c r="AH89" s="20"/>
+      <c r="AI89" s="20"/>
+      <c r="AJ89" s="20"/>
+      <c r="AK89" s="21"/>
+      <c r="AL89" s="19"/>
+      <c r="AM89" s="20"/>
+      <c r="AN89" s="20"/>
+      <c r="AO89" s="20"/>
+      <c r="AP89" s="20"/>
+      <c r="AQ89" s="20"/>
+      <c r="AR89" s="20"/>
+      <c r="AS89" s="20"/>
+      <c r="AT89" s="20"/>
+      <c r="AU89" s="20"/>
+      <c r="AV89" s="20"/>
+      <c r="AW89" s="20"/>
+      <c r="AX89" s="20"/>
+      <c r="AY89" s="20"/>
+      <c r="AZ89" s="20"/>
+      <c r="BA89" s="20"/>
+      <c r="BB89" s="20"/>
+      <c r="BC89" s="21"/>
+    </row>
+    <row r="90" spans="1:55">
+      <c r="B90" s="39">
+        <f t="shared" si="0"/>
+        <v>79</v>
+      </c>
+      <c r="C90" s="19"/>
+      <c r="D90" s="20"/>
+      <c r="E90" s="20"/>
+      <c r="F90" s="20"/>
+      <c r="G90" s="20"/>
+      <c r="H90" s="20"/>
+      <c r="I90" s="20"/>
+      <c r="J90" s="20"/>
+      <c r="K90" s="21"/>
+      <c r="L90" s="19"/>
+      <c r="M90" s="20"/>
+      <c r="N90" s="20"/>
+      <c r="O90" s="20"/>
+      <c r="P90" s="20"/>
+      <c r="Q90" s="20"/>
+      <c r="R90" s="20"/>
+      <c r="S90" s="20"/>
+      <c r="T90" s="21"/>
+      <c r="U90" s="19"/>
+      <c r="V90" s="20"/>
+      <c r="W90" s="20"/>
+      <c r="X90" s="20"/>
+      <c r="Y90" s="20"/>
+      <c r="Z90" s="21"/>
+      <c r="AA90" s="113"/>
+      <c r="AB90" s="114"/>
+      <c r="AC90" s="113"/>
+      <c r="AD90" s="114"/>
+      <c r="AE90" s="113"/>
+      <c r="AF90" s="114"/>
+      <c r="AG90" s="19"/>
+      <c r="AH90" s="20"/>
+      <c r="AI90" s="20"/>
+      <c r="AJ90" s="20"/>
+      <c r="AK90" s="21"/>
+      <c r="AL90" s="19"/>
+      <c r="AM90" s="20"/>
+      <c r="AN90" s="20"/>
+      <c r="AO90" s="20"/>
+      <c r="AP90" s="20"/>
+      <c r="AQ90" s="20"/>
+      <c r="AR90" s="20"/>
+      <c r="AS90" s="20"/>
+      <c r="AT90" s="20"/>
+      <c r="AU90" s="20"/>
+      <c r="AV90" s="20"/>
+      <c r="AW90" s="20"/>
+      <c r="AX90" s="20"/>
+      <c r="AY90" s="20"/>
+      <c r="AZ90" s="20"/>
+      <c r="BA90" s="20"/>
+      <c r="BB90" s="20"/>
+      <c r="BC90" s="21"/>
+    </row>
+    <row r="91" spans="1:55">
+      <c r="B91" s="39">
+        <f t="shared" si="0"/>
+        <v>80</v>
+      </c>
+      <c r="C91" s="19"/>
+      <c r="D91" s="20"/>
+      <c r="E91" s="20"/>
+      <c r="F91" s="20"/>
+      <c r="G91" s="20"/>
+      <c r="H91" s="20"/>
+      <c r="I91" s="20"/>
+      <c r="J91" s="20"/>
+      <c r="K91" s="21"/>
+      <c r="L91" s="19"/>
+      <c r="M91" s="20"/>
+      <c r="N91" s="20"/>
+      <c r="O91" s="20"/>
+      <c r="P91" s="20"/>
+      <c r="Q91" s="20"/>
+      <c r="R91" s="20"/>
+      <c r="S91" s="20"/>
+      <c r="T91" s="21"/>
+      <c r="U91" s="19"/>
+      <c r="V91" s="20"/>
+      <c r="W91" s="20"/>
+      <c r="X91" s="20"/>
+      <c r="Y91" s="20"/>
+      <c r="Z91" s="21"/>
+      <c r="AA91" s="113"/>
+      <c r="AB91" s="114"/>
+      <c r="AC91" s="113"/>
+      <c r="AD91" s="114"/>
+      <c r="AE91" s="113"/>
+      <c r="AF91" s="114"/>
+      <c r="AG91" s="19"/>
+      <c r="AH91" s="20"/>
+      <c r="AI91" s="20"/>
+      <c r="AJ91" s="20"/>
+      <c r="AK91" s="21"/>
+      <c r="AL91" s="19"/>
+      <c r="AM91" s="20"/>
+      <c r="AN91" s="20"/>
+      <c r="AO91" s="20"/>
+      <c r="AP91" s="20"/>
+      <c r="AQ91" s="20"/>
+      <c r="AR91" s="20"/>
+      <c r="AS91" s="20"/>
+      <c r="AT91" s="20"/>
+      <c r="AU91" s="20"/>
+      <c r="AV91" s="20"/>
+      <c r="AW91" s="20"/>
+      <c r="AX91" s="20"/>
+      <c r="AY91" s="20"/>
+      <c r="AZ91" s="20"/>
+      <c r="BA91" s="20"/>
+      <c r="BB91" s="20"/>
+      <c r="BC91" s="21"/>
+    </row>
+    <row r="92" spans="1:55">
+      <c r="B92" s="39">
+        <f t="shared" si="0"/>
+        <v>81</v>
+      </c>
+      <c r="C92" s="19"/>
+      <c r="D92" s="20"/>
+      <c r="E92" s="20"/>
+      <c r="F92" s="20"/>
+      <c r="G92" s="20"/>
+      <c r="H92" s="20"/>
+      <c r="I92" s="20"/>
+      <c r="J92" s="20"/>
+      <c r="K92" s="21"/>
+      <c r="L92" s="19"/>
+      <c r="M92" s="20"/>
+      <c r="N92" s="20"/>
+      <c r="O92" s="20"/>
+      <c r="P92" s="20"/>
+      <c r="Q92" s="20"/>
+      <c r="R92" s="20"/>
+      <c r="S92" s="20"/>
+      <c r="T92" s="21"/>
+      <c r="U92" s="19"/>
+      <c r="V92" s="20"/>
+      <c r="W92" s="20"/>
+      <c r="X92" s="20"/>
+      <c r="Y92" s="20"/>
+      <c r="Z92" s="21"/>
+      <c r="AA92" s="113"/>
+      <c r="AB92" s="114"/>
+      <c r="AC92" s="113"/>
+      <c r="AD92" s="114"/>
+      <c r="AE92" s="113"/>
+      <c r="AF92" s="114"/>
+      <c r="AG92" s="19"/>
+      <c r="AH92" s="20"/>
+      <c r="AI92" s="20"/>
+      <c r="AJ92" s="20"/>
+      <c r="AK92" s="21"/>
+      <c r="AL92" s="19"/>
+      <c r="AM92" s="20"/>
+      <c r="AN92" s="20"/>
+      <c r="AO92" s="20"/>
+      <c r="AP92" s="20"/>
+      <c r="AQ92" s="20"/>
+      <c r="AR92" s="20"/>
+      <c r="AS92" s="20"/>
+      <c r="AT92" s="20"/>
+      <c r="AU92" s="20"/>
+      <c r="AV92" s="20"/>
+      <c r="AW92" s="20"/>
+      <c r="AX92" s="20"/>
+      <c r="AY92" s="20"/>
+      <c r="AZ92" s="20"/>
+      <c r="BA92" s="20"/>
+      <c r="BB92" s="20"/>
+      <c r="BC92" s="21"/>
+    </row>
+    <row r="94" spans="1:55" ht="20">
+      <c r="A94" s="41" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="95" spans="1:55">
+      <c r="B95" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="C95" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="D95" s="27"/>
+      <c r="E95" s="27"/>
+      <c r="F95" s="27"/>
+      <c r="G95" s="27"/>
+      <c r="H95" s="27"/>
+      <c r="I95" s="27"/>
+      <c r="J95" s="27"/>
+      <c r="K95" s="28"/>
+      <c r="L95" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="M95" s="27"/>
+      <c r="N95" s="27"/>
+      <c r="O95" s="27"/>
+      <c r="P95" s="27"/>
+      <c r="Q95" s="27"/>
+      <c r="R95" s="27"/>
+      <c r="S95" s="27"/>
+      <c r="T95" s="28"/>
+      <c r="U95" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="V95" s="27"/>
+      <c r="W95" s="27"/>
+      <c r="X95" s="27"/>
+      <c r="Y95" s="27"/>
+      <c r="Z95" s="27"/>
+      <c r="AA95" s="27"/>
+      <c r="AB95" s="27"/>
+      <c r="AC95" s="28"/>
+      <c r="AD95" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="AE95" s="27"/>
+      <c r="AF95" s="27"/>
+      <c r="AG95" s="27"/>
+      <c r="AH95" s="27"/>
+      <c r="AI95" s="27"/>
+      <c r="AJ95" s="27"/>
+      <c r="AK95" s="27"/>
+      <c r="AL95" s="28"/>
+    </row>
+    <row r="96" spans="1:55">
+      <c r="B96" s="39" t="s">
+        <v>71</v>
+      </c>
+      <c r="C96" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="D96" s="20"/>
+      <c r="E96" s="20"/>
+      <c r="F96" s="20"/>
+      <c r="G96" s="20"/>
+      <c r="H96" s="20"/>
+      <c r="I96" s="20"/>
+      <c r="J96" s="20"/>
+      <c r="K96" s="21"/>
+      <c r="L96" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="M96" s="20"/>
+      <c r="N96" s="20"/>
+      <c r="O96" s="20"/>
+      <c r="P96" s="20"/>
+      <c r="Q96" s="20"/>
+      <c r="R96" s="20"/>
+      <c r="S96" s="20"/>
+      <c r="T96" s="21"/>
+      <c r="U96" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="V96" s="20"/>
+      <c r="W96" s="20"/>
+      <c r="X96" s="20"/>
+      <c r="Y96" s="20"/>
+      <c r="Z96" s="20"/>
+      <c r="AA96" s="20"/>
+      <c r="AB96" s="20"/>
+      <c r="AC96" s="21"/>
+      <c r="AD96" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="AE96" s="20"/>
+      <c r="AF96" s="20"/>
+      <c r="AG96" s="20"/>
+      <c r="AH96" s="20"/>
+      <c r="AI96" s="20"/>
+      <c r="AJ96" s="20"/>
+      <c r="AK96" s="20"/>
+      <c r="AL96" s="21"/>
+    </row>
+  </sheetData>
+  <mergeCells count="249">
+    <mergeCell ref="AC66:AD66"/>
+    <mergeCell ref="AE66:AF66"/>
+    <mergeCell ref="AA74:AB74"/>
+    <mergeCell ref="AC74:AD74"/>
+    <mergeCell ref="AE74:AF74"/>
+    <mergeCell ref="AA72:AB72"/>
+    <mergeCell ref="AC72:AD72"/>
+    <mergeCell ref="AE72:AF72"/>
+    <mergeCell ref="AA62:AB62"/>
+    <mergeCell ref="AC62:AD62"/>
+    <mergeCell ref="AE62:AF62"/>
+    <mergeCell ref="AA63:AB63"/>
+    <mergeCell ref="AC63:AD63"/>
+    <mergeCell ref="AE63:AF63"/>
+    <mergeCell ref="AA64:AB64"/>
+    <mergeCell ref="AC64:AD64"/>
+    <mergeCell ref="AE64:AF64"/>
+    <mergeCell ref="AA65:AB65"/>
+    <mergeCell ref="AC65:AD65"/>
+    <mergeCell ref="AE65:AF65"/>
+    <mergeCell ref="AA66:AB66"/>
+    <mergeCell ref="AA70:AB70"/>
+    <mergeCell ref="AC70:AD70"/>
+    <mergeCell ref="AE70:AF70"/>
+    <mergeCell ref="AA71:AB71"/>
+    <mergeCell ref="AC71:AD71"/>
+    <mergeCell ref="AE71:AF71"/>
+    <mergeCell ref="AA73:AB73"/>
+    <mergeCell ref="AC73:AD73"/>
+    <mergeCell ref="AE73:AF73"/>
+    <mergeCell ref="AA69:AB69"/>
+    <mergeCell ref="AC69:AD69"/>
+    <mergeCell ref="AE69:AF69"/>
+    <mergeCell ref="AA75:AB75"/>
+    <mergeCell ref="AC75:AD75"/>
+    <mergeCell ref="AE75:AF75"/>
+    <mergeCell ref="AA76:AB76"/>
+    <mergeCell ref="AC76:AD76"/>
+    <mergeCell ref="AE76:AF76"/>
+    <mergeCell ref="AA77:AB77"/>
+    <mergeCell ref="AC77:AD77"/>
+    <mergeCell ref="AE77:AF77"/>
+    <mergeCell ref="AA67:AB67"/>
+    <mergeCell ref="AC67:AD67"/>
+    <mergeCell ref="AE67:AF67"/>
+    <mergeCell ref="AA68:AB68"/>
+    <mergeCell ref="AC68:AD68"/>
+    <mergeCell ref="AE68:AF68"/>
+    <mergeCell ref="AA44:AB44"/>
+    <mergeCell ref="AC44:AD44"/>
+    <mergeCell ref="AE44:AF44"/>
+    <mergeCell ref="AA45:AB45"/>
+    <mergeCell ref="AC45:AD45"/>
+    <mergeCell ref="AE45:AF45"/>
+    <mergeCell ref="AA42:AB42"/>
+    <mergeCell ref="AC42:AD42"/>
+    <mergeCell ref="AE42:AF42"/>
+    <mergeCell ref="AA43:AB43"/>
+    <mergeCell ref="AC43:AD43"/>
+    <mergeCell ref="AE43:AF43"/>
+    <mergeCell ref="AC40:AD40"/>
+    <mergeCell ref="AE40:AF40"/>
+    <mergeCell ref="AA41:AB41"/>
+    <mergeCell ref="AC41:AD41"/>
+    <mergeCell ref="AE41:AF41"/>
+    <mergeCell ref="AA53:AB53"/>
+    <mergeCell ref="AC53:AD53"/>
+    <mergeCell ref="AE53:AF53"/>
+    <mergeCell ref="AA54:AB54"/>
+    <mergeCell ref="AC54:AD54"/>
+    <mergeCell ref="AE54:AF54"/>
+    <mergeCell ref="AA51:AB51"/>
+    <mergeCell ref="AC51:AD51"/>
+    <mergeCell ref="AE51:AF51"/>
+    <mergeCell ref="AA52:AB52"/>
+    <mergeCell ref="AC52:AD52"/>
+    <mergeCell ref="AE52:AF52"/>
+    <mergeCell ref="AA49:AB49"/>
+    <mergeCell ref="AC49:AD49"/>
+    <mergeCell ref="AE49:AF49"/>
+    <mergeCell ref="AA50:AB50"/>
+    <mergeCell ref="AC50:AD50"/>
+    <mergeCell ref="AE50:AF50"/>
+    <mergeCell ref="AA47:AB47"/>
+    <mergeCell ref="AC47:AD47"/>
+    <mergeCell ref="AE47:AF47"/>
+    <mergeCell ref="AA48:AB48"/>
+    <mergeCell ref="AC48:AD48"/>
+    <mergeCell ref="AE48:AF48"/>
+    <mergeCell ref="AA61:AB61"/>
+    <mergeCell ref="AC61:AD61"/>
+    <mergeCell ref="AE61:AF61"/>
+    <mergeCell ref="AA46:AB46"/>
+    <mergeCell ref="AC46:AD46"/>
+    <mergeCell ref="AE46:AF46"/>
+    <mergeCell ref="AA37:AB37"/>
+    <mergeCell ref="AC37:AD37"/>
+    <mergeCell ref="AE37:AF37"/>
+    <mergeCell ref="AA38:AB38"/>
+    <mergeCell ref="AC38:AD38"/>
+    <mergeCell ref="AE38:AF38"/>
+    <mergeCell ref="AA39:AB39"/>
+    <mergeCell ref="AC39:AD39"/>
+    <mergeCell ref="AE39:AF39"/>
+    <mergeCell ref="AA40:AB40"/>
+    <mergeCell ref="AA59:AB59"/>
+    <mergeCell ref="AC59:AD59"/>
+    <mergeCell ref="AE59:AF59"/>
+    <mergeCell ref="AA60:AB60"/>
+    <mergeCell ref="AC60:AD60"/>
+    <mergeCell ref="AE60:AF60"/>
+    <mergeCell ref="AA57:AB57"/>
+    <mergeCell ref="AC57:AD57"/>
+    <mergeCell ref="AE57:AF57"/>
+    <mergeCell ref="AA58:AB58"/>
+    <mergeCell ref="AC58:AD58"/>
+    <mergeCell ref="AE58:AF58"/>
+    <mergeCell ref="AE34:AF34"/>
+    <mergeCell ref="AA35:AB35"/>
+    <mergeCell ref="AC35:AD35"/>
+    <mergeCell ref="AE35:AF35"/>
+    <mergeCell ref="AA36:AB36"/>
+    <mergeCell ref="AC36:AD36"/>
+    <mergeCell ref="AE36:AF36"/>
+    <mergeCell ref="AA91:AB91"/>
+    <mergeCell ref="AC91:AD91"/>
+    <mergeCell ref="AE91:AF91"/>
+    <mergeCell ref="AA55:AB55"/>
+    <mergeCell ref="AC55:AD55"/>
+    <mergeCell ref="AE55:AF55"/>
+    <mergeCell ref="AA56:AB56"/>
+    <mergeCell ref="AC56:AD56"/>
+    <mergeCell ref="AE56:AF56"/>
+    <mergeCell ref="AA85:AB85"/>
+    <mergeCell ref="AC85:AD85"/>
+    <mergeCell ref="AE85:AF85"/>
+    <mergeCell ref="AA86:AB86"/>
+    <mergeCell ref="AC86:AD86"/>
+    <mergeCell ref="AE86:AF86"/>
+    <mergeCell ref="AA87:AB87"/>
+    <mergeCell ref="AA89:AB89"/>
+    <mergeCell ref="AC89:AD89"/>
+    <mergeCell ref="AE89:AF89"/>
+    <mergeCell ref="AA90:AB90"/>
+    <mergeCell ref="AC90:AD90"/>
+    <mergeCell ref="AE90:AF90"/>
+    <mergeCell ref="AA31:AB31"/>
+    <mergeCell ref="AC31:AD31"/>
+    <mergeCell ref="AE31:AF31"/>
+    <mergeCell ref="AA88:AB88"/>
+    <mergeCell ref="AC88:AD88"/>
+    <mergeCell ref="AE88:AF88"/>
+    <mergeCell ref="AC87:AD87"/>
+    <mergeCell ref="AE87:AF87"/>
+    <mergeCell ref="AA32:AB32"/>
+    <mergeCell ref="AC32:AD32"/>
+    <mergeCell ref="AE32:AF32"/>
+    <mergeCell ref="AA33:AB33"/>
+    <mergeCell ref="AC33:AD33"/>
+    <mergeCell ref="AE33:AF33"/>
+    <mergeCell ref="AA34:AB34"/>
+    <mergeCell ref="AC34:AD34"/>
+    <mergeCell ref="AA29:AB29"/>
+    <mergeCell ref="AC29:AD29"/>
+    <mergeCell ref="AE29:AF29"/>
+    <mergeCell ref="AA30:AB30"/>
+    <mergeCell ref="AC30:AD30"/>
+    <mergeCell ref="AE30:AF30"/>
+    <mergeCell ref="AA27:AB27"/>
+    <mergeCell ref="AC27:AD27"/>
+    <mergeCell ref="AE27:AF27"/>
+    <mergeCell ref="AA28:AB28"/>
+    <mergeCell ref="AC28:AD28"/>
+    <mergeCell ref="AE28:AF28"/>
+    <mergeCell ref="AA25:AB25"/>
+    <mergeCell ref="AC25:AD25"/>
+    <mergeCell ref="AE25:AF25"/>
+    <mergeCell ref="AA26:AB26"/>
+    <mergeCell ref="AC26:AD26"/>
+    <mergeCell ref="AE26:AF26"/>
+    <mergeCell ref="AA23:AB23"/>
+    <mergeCell ref="AC23:AD23"/>
+    <mergeCell ref="AE23:AF23"/>
+    <mergeCell ref="AA24:AB24"/>
+    <mergeCell ref="AC24:AD24"/>
+    <mergeCell ref="AE24:AF24"/>
+    <mergeCell ref="AC21:AD21"/>
+    <mergeCell ref="AE21:AF21"/>
+    <mergeCell ref="AA22:AB22"/>
+    <mergeCell ref="AC22:AD22"/>
+    <mergeCell ref="AE22:AF22"/>
+    <mergeCell ref="AA78:AB78"/>
+    <mergeCell ref="AC78:AD78"/>
+    <mergeCell ref="AE78:AF78"/>
+    <mergeCell ref="AA79:AB79"/>
+    <mergeCell ref="AC79:AD79"/>
+    <mergeCell ref="AE79:AF79"/>
+    <mergeCell ref="AA92:AB92"/>
+    <mergeCell ref="AC92:AD92"/>
+    <mergeCell ref="AE92:AF92"/>
+    <mergeCell ref="AA80:AB80"/>
+    <mergeCell ref="AC80:AD80"/>
+    <mergeCell ref="AE80:AF80"/>
+    <mergeCell ref="AA81:AB81"/>
+    <mergeCell ref="AC81:AD81"/>
+    <mergeCell ref="AE81:AF81"/>
+    <mergeCell ref="AA82:AB82"/>
+    <mergeCell ref="AC82:AD82"/>
+    <mergeCell ref="AE82:AF82"/>
+    <mergeCell ref="AA20:AB20"/>
+    <mergeCell ref="AC20:AD20"/>
+    <mergeCell ref="AE20:AF20"/>
+    <mergeCell ref="AA21:AB21"/>
+    <mergeCell ref="AC13:AD13"/>
+    <mergeCell ref="AE13:AF13"/>
+    <mergeCell ref="AA12:AB12"/>
+    <mergeCell ref="AC12:AD12"/>
+    <mergeCell ref="AE12:AF12"/>
+    <mergeCell ref="AA19:AB19"/>
+    <mergeCell ref="AC19:AD19"/>
+    <mergeCell ref="AE19:AF19"/>
+    <mergeCell ref="AA17:AB17"/>
+    <mergeCell ref="AC17:AD17"/>
+    <mergeCell ref="AE17:AF17"/>
+    <mergeCell ref="AA18:AB18"/>
+    <mergeCell ref="AC18:AD18"/>
+    <mergeCell ref="AE18:AF18"/>
+    <mergeCell ref="AA13:AB13"/>
+    <mergeCell ref="AE15:AF15"/>
+    <mergeCell ref="AA14:AB14"/>
+    <mergeCell ref="AC14:AD14"/>
+    <mergeCell ref="AE14:AF14"/>
+    <mergeCell ref="AA16:AB16"/>
+    <mergeCell ref="AC16:AD16"/>
+    <mergeCell ref="AE16:AF16"/>
+    <mergeCell ref="AC15:AD15"/>
+    <mergeCell ref="B4:G4"/>
+    <mergeCell ref="B5:G5"/>
+    <mergeCell ref="B6:G8"/>
+    <mergeCell ref="H6:Y8"/>
+    <mergeCell ref="AA15:AB15"/>
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="H2:M2"/>
+    <mergeCell ref="N2:S2"/>
+    <mergeCell ref="T2:Y2"/>
+    <mergeCell ref="B3:G3"/>
+    <mergeCell ref="H3:M3"/>
+    <mergeCell ref="N3:S3"/>
+    <mergeCell ref="T3:Y3"/>
+  </mergeCells>
+  <phoneticPr fontId="1"/>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AE19:AF77 AA17:AD77 AA12:AF16 AA78:AF92" xr:uid="{185F62DD-DD48-0446-94A1-F28EB9AD87E2}">
+      <formula1>"-,○"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFC5E6C4-D731-A540-B94A-4345628B6AAE}">
+  <dimension ref="A1:BC40"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="4.33203125" defaultRowHeight="18"/>
+  <cols>
+    <col min="1" max="16384" width="4.33203125" style="18"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:55" ht="20">
+      <c r="A1" s="40" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:55">
+      <c r="B2" s="78" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2" s="85" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="85" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="85" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" s="85" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="79" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" s="88">
+        <v>45459</v>
+      </c>
+      <c r="I2" s="89"/>
+      <c r="J2" s="89"/>
+      <c r="K2" s="89"/>
+      <c r="L2" s="89"/>
+      <c r="M2" s="90"/>
+      <c r="N2" s="78" t="s">
+        <v>26</v>
+      </c>
+      <c r="O2" s="85" t="s">
+        <v>15</v>
+      </c>
+      <c r="P2" s="85" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q2" s="85" t="s">
+        <v>15</v>
+      </c>
+      <c r="R2" s="85" t="s">
+        <v>15</v>
+      </c>
+      <c r="S2" s="79" t="s">
+        <v>15</v>
+      </c>
+      <c r="T2" s="91" t="s">
+        <v>45</v>
+      </c>
+      <c r="U2" s="89"/>
+      <c r="V2" s="89"/>
+      <c r="W2" s="89"/>
+      <c r="X2" s="89"/>
+      <c r="Y2" s="90"/>
+    </row>
+    <row r="3" spans="1:55">
+      <c r="B3" s="86" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" s="87" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="87" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="87" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="87" t="s">
+        <v>16</v>
+      </c>
+      <c r="G3" s="87" t="s">
+        <v>16</v>
+      </c>
+      <c r="H3" s="92"/>
+      <c r="I3" s="93"/>
+      <c r="J3" s="93"/>
+      <c r="K3" s="93"/>
+      <c r="L3" s="93"/>
+      <c r="M3" s="93"/>
+      <c r="N3" s="86" t="s">
+        <v>29</v>
+      </c>
+      <c r="O3" s="87" t="s">
+        <v>16</v>
+      </c>
+      <c r="P3" s="87" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q3" s="87" t="s">
+        <v>16</v>
+      </c>
+      <c r="R3" s="87" t="s">
+        <v>16</v>
+      </c>
+      <c r="S3" s="87" t="s">
+        <v>16</v>
+      </c>
+      <c r="T3" s="92"/>
+      <c r="U3" s="93"/>
+      <c r="V3" s="93"/>
+      <c r="W3" s="93"/>
+      <c r="X3" s="93"/>
+      <c r="Y3" s="94"/>
+    </row>
+    <row r="4" spans="1:55">
+      <c r="B4" s="95" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="96" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="96" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="96" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" s="96" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" s="97" t="s">
+        <v>15</v>
+      </c>
+      <c r="H4" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="I4" s="20"/>
+      <c r="J4" s="20"/>
+      <c r="K4" s="20"/>
+      <c r="L4" s="20"/>
+      <c r="M4" s="20"/>
+      <c r="N4" s="20"/>
+      <c r="O4" s="20"/>
+      <c r="P4" s="20"/>
+      <c r="Q4" s="20"/>
+      <c r="R4" s="20"/>
+      <c r="S4" s="20"/>
+      <c r="T4" s="20"/>
+      <c r="U4" s="20"/>
+      <c r="V4" s="20"/>
+      <c r="W4" s="20"/>
+      <c r="X4" s="20"/>
+      <c r="Y4" s="21"/>
+    </row>
+    <row r="5" spans="1:55">
+      <c r="B5" s="86" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="87" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="87" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" s="87" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" s="87" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5" s="87" t="s">
+        <v>16</v>
+      </c>
+      <c r="H5" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="I5" s="23"/>
+      <c r="J5" s="23"/>
+      <c r="K5" s="23"/>
+      <c r="L5" s="23"/>
+      <c r="M5" s="23"/>
+      <c r="N5" s="23"/>
+      <c r="O5" s="23"/>
+      <c r="P5" s="23"/>
+      <c r="Q5" s="23"/>
+      <c r="R5" s="23"/>
+      <c r="S5" s="23"/>
+      <c r="T5" s="23"/>
+      <c r="U5" s="23"/>
+      <c r="V5" s="23"/>
+      <c r="W5" s="23"/>
+      <c r="X5" s="23"/>
+      <c r="Y5" s="24"/>
+    </row>
+    <row r="6" spans="1:55">
+      <c r="B6" s="78" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" s="85"/>
+      <c r="D6" s="85"/>
+      <c r="E6" s="85"/>
+      <c r="F6" s="85"/>
+      <c r="G6" s="79"/>
+      <c r="H6" s="104" t="s">
+        <v>77</v>
+      </c>
+      <c r="I6" s="105"/>
+      <c r="J6" s="105"/>
+      <c r="K6" s="105"/>
+      <c r="L6" s="105"/>
+      <c r="M6" s="105"/>
+      <c r="N6" s="105"/>
+      <c r="O6" s="105"/>
+      <c r="P6" s="105"/>
+      <c r="Q6" s="105"/>
+      <c r="R6" s="105"/>
+      <c r="S6" s="105"/>
+      <c r="T6" s="105"/>
+      <c r="U6" s="105"/>
+      <c r="V6" s="105"/>
+      <c r="W6" s="105"/>
+      <c r="X6" s="105"/>
+      <c r="Y6" s="106"/>
+    </row>
+    <row r="7" spans="1:55">
+      <c r="B7" s="98"/>
+      <c r="C7" s="99"/>
+      <c r="D7" s="99"/>
+      <c r="E7" s="99"/>
+      <c r="F7" s="99"/>
+      <c r="G7" s="100"/>
+      <c r="H7" s="107"/>
+      <c r="I7" s="108"/>
+      <c r="J7" s="108"/>
+      <c r="K7" s="108"/>
+      <c r="L7" s="108"/>
+      <c r="M7" s="108"/>
+      <c r="N7" s="108"/>
+      <c r="O7" s="108"/>
+      <c r="P7" s="108"/>
+      <c r="Q7" s="108"/>
+      <c r="R7" s="108"/>
+      <c r="S7" s="108"/>
+      <c r="T7" s="108"/>
+      <c r="U7" s="108"/>
+      <c r="V7" s="108"/>
+      <c r="W7" s="108"/>
+      <c r="X7" s="108"/>
+      <c r="Y7" s="109"/>
+    </row>
+    <row r="8" spans="1:55">
+      <c r="B8" s="101"/>
+      <c r="C8" s="102"/>
+      <c r="D8" s="102"/>
+      <c r="E8" s="102"/>
+      <c r="F8" s="102"/>
+      <c r="G8" s="103"/>
+      <c r="H8" s="110"/>
+      <c r="I8" s="111"/>
+      <c r="J8" s="111"/>
+      <c r="K8" s="111"/>
+      <c r="L8" s="111"/>
+      <c r="M8" s="111"/>
+      <c r="N8" s="111"/>
+      <c r="O8" s="111"/>
+      <c r="P8" s="111"/>
+      <c r="Q8" s="111"/>
+      <c r="R8" s="111"/>
+      <c r="S8" s="111"/>
+      <c r="T8" s="111"/>
+      <c r="U8" s="111"/>
+      <c r="V8" s="111"/>
+      <c r="W8" s="111"/>
+      <c r="X8" s="111"/>
+      <c r="Y8" s="112"/>
+    </row>
+    <row r="10" spans="1:55" ht="20">
+      <c r="A10" s="41" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11" spans="1:55">
+      <c r="B11" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="D11" s="27"/>
+      <c r="E11" s="27"/>
+      <c r="F11" s="27"/>
+      <c r="G11" s="27"/>
+      <c r="H11" s="27"/>
+      <c r="I11" s="27"/>
+      <c r="J11" s="27"/>
+      <c r="K11" s="28"/>
+      <c r="L11" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="M11" s="27"/>
+      <c r="N11" s="27"/>
+      <c r="O11" s="27"/>
+      <c r="P11" s="27"/>
+      <c r="Q11" s="27"/>
+      <c r="R11" s="27"/>
+      <c r="S11" s="27"/>
+      <c r="T11" s="28"/>
+      <c r="U11" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="V11" s="27"/>
+      <c r="W11" s="27"/>
+      <c r="X11" s="27"/>
+      <c r="Y11" s="27"/>
+      <c r="Z11" s="28"/>
+      <c r="AA11" s="27" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB11" s="27"/>
+      <c r="AC11" s="26" t="s">
+        <v>39</v>
+      </c>
+      <c r="AD11" s="27"/>
+      <c r="AE11" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="AF11" s="28"/>
+      <c r="AG11" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="AH11" s="27"/>
+      <c r="AI11" s="27"/>
+      <c r="AJ11" s="27"/>
+      <c r="AK11" s="28"/>
+      <c r="AL11" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="AM11" s="27"/>
+      <c r="AN11" s="27"/>
+      <c r="AO11" s="27"/>
+      <c r="AP11" s="27"/>
+      <c r="AQ11" s="27"/>
+      <c r="AR11" s="27"/>
+      <c r="AS11" s="27"/>
+      <c r="AT11" s="27"/>
+      <c r="AU11" s="27"/>
+      <c r="AV11" s="27"/>
+      <c r="AW11" s="27"/>
+      <c r="AX11" s="27"/>
+      <c r="AY11" s="27"/>
+      <c r="AZ11" s="27"/>
+      <c r="BA11" s="27"/>
+      <c r="BB11" s="27"/>
+      <c r="BC11" s="28"/>
+    </row>
+    <row r="12" spans="1:55">
+      <c r="B12" s="39">
+        <f>ROW()-11</f>
+        <v>1</v>
+      </c>
+      <c r="C12" s="19" t="s">
+        <v>85</v>
+      </c>
+      <c r="D12" s="20"/>
+      <c r="E12" s="20"/>
+      <c r="F12" s="20"/>
+      <c r="G12" s="20"/>
+      <c r="H12" s="20"/>
+      <c r="I12" s="20"/>
+      <c r="J12" s="20"/>
+      <c r="K12" s="21"/>
+      <c r="L12" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="M12" s="20"/>
+      <c r="N12" s="20"/>
+      <c r="O12" s="20"/>
+      <c r="P12" s="20"/>
+      <c r="Q12" s="20"/>
+      <c r="R12" s="20"/>
+      <c r="S12" s="20"/>
+      <c r="T12" s="21"/>
+      <c r="U12" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="V12" s="20"/>
+      <c r="W12" s="20"/>
+      <c r="X12" s="20"/>
+      <c r="Y12" s="20"/>
+      <c r="Z12" s="21"/>
+      <c r="AA12" s="113" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB12" s="114"/>
+      <c r="AC12" s="113" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD12" s="114"/>
+      <c r="AE12" s="113" t="s">
+        <v>68</v>
+      </c>
+      <c r="AF12" s="114"/>
+      <c r="AG12" s="19"/>
+      <c r="AH12" s="20"/>
+      <c r="AI12" s="20"/>
+      <c r="AJ12" s="20"/>
+      <c r="AK12" s="21"/>
+      <c r="AL12" s="19"/>
+      <c r="AM12" s="20"/>
+      <c r="AN12" s="20"/>
+      <c r="AO12" s="20"/>
+      <c r="AP12" s="20"/>
+      <c r="AQ12" s="20"/>
+      <c r="AR12" s="20"/>
+      <c r="AS12" s="20"/>
+      <c r="AT12" s="20"/>
+      <c r="AU12" s="20"/>
+      <c r="AV12" s="20"/>
+      <c r="AW12" s="20"/>
+      <c r="AX12" s="20"/>
+      <c r="AY12" s="20"/>
+      <c r="AZ12" s="20"/>
+      <c r="BA12" s="20"/>
+      <c r="BB12" s="20"/>
+      <c r="BC12" s="21"/>
+    </row>
+    <row r="13" spans="1:55">
+      <c r="B13" s="39">
+        <f t="shared" ref="B13:B25" si="0">ROW()-11</f>
+        <v>2</v>
+      </c>
+      <c r="C13" s="19" t="s">
+        <v>83</v>
+      </c>
+      <c r="D13" s="20"/>
+      <c r="E13" s="20"/>
+      <c r="F13" s="20"/>
+      <c r="G13" s="20"/>
+      <c r="H13" s="20"/>
+      <c r="I13" s="20"/>
+      <c r="J13" s="20"/>
+      <c r="K13" s="21"/>
+      <c r="L13" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="M13" s="20"/>
+      <c r="N13" s="20"/>
+      <c r="O13" s="20"/>
+      <c r="P13" s="20"/>
+      <c r="Q13" s="20"/>
+      <c r="R13" s="20"/>
+      <c r="S13" s="20"/>
+      <c r="T13" s="21"/>
+      <c r="U13" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="V13" s="20"/>
+      <c r="W13" s="20"/>
+      <c r="X13" s="20"/>
+      <c r="Y13" s="20"/>
+      <c r="Z13" s="21"/>
+      <c r="AA13" s="113" t="s">
+        <v>68</v>
+      </c>
+      <c r="AB13" s="114"/>
+      <c r="AC13" s="113" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD13" s="114"/>
+      <c r="AE13" s="113" t="s">
+        <v>68</v>
+      </c>
+      <c r="AF13" s="114"/>
+      <c r="AG13" s="19"/>
+      <c r="AH13" s="20"/>
+      <c r="AI13" s="20"/>
+      <c r="AJ13" s="20"/>
+      <c r="AK13" s="21"/>
+      <c r="AL13" s="42"/>
+      <c r="AM13" s="20"/>
+      <c r="AN13" s="20"/>
+      <c r="AO13" s="20"/>
+      <c r="AP13" s="20"/>
+      <c r="AQ13" s="20"/>
+      <c r="AR13" s="20"/>
+      <c r="AS13" s="20"/>
+      <c r="AT13" s="20"/>
+      <c r="AU13" s="20"/>
+      <c r="AV13" s="20"/>
+      <c r="AW13" s="20"/>
+      <c r="AX13" s="20"/>
+      <c r="AY13" s="20"/>
+      <c r="AZ13" s="20"/>
+      <c r="BA13" s="20"/>
+      <c r="BB13" s="20"/>
+      <c r="BC13" s="21"/>
+    </row>
+    <row r="14" spans="1:55">
+      <c r="B14" s="39">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="C14" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="D14" s="20"/>
+      <c r="E14" s="20"/>
+      <c r="F14" s="20"/>
+      <c r="G14" s="20"/>
+      <c r="H14" s="20"/>
+      <c r="I14" s="20"/>
+      <c r="J14" s="20"/>
+      <c r="K14" s="21"/>
+      <c r="L14" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="M14" s="20"/>
+      <c r="N14" s="20"/>
+      <c r="O14" s="20"/>
+      <c r="P14" s="20"/>
+      <c r="Q14" s="20"/>
+      <c r="R14" s="20"/>
+      <c r="S14" s="20"/>
+      <c r="T14" s="21"/>
+      <c r="U14" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="V14" s="20"/>
+      <c r="W14" s="20"/>
+      <c r="X14" s="20"/>
+      <c r="Y14" s="20"/>
+      <c r="Z14" s="21"/>
+      <c r="AA14" s="113" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB14" s="114"/>
+      <c r="AC14" s="113" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD14" s="114"/>
+      <c r="AE14" s="113" t="s">
+        <v>69</v>
+      </c>
+      <c r="AF14" s="114"/>
+      <c r="AG14" s="19"/>
+      <c r="AH14" s="20"/>
+      <c r="AI14" s="20"/>
+      <c r="AJ14" s="20"/>
+      <c r="AK14" s="21"/>
+      <c r="AL14" s="42"/>
+      <c r="AM14" s="20"/>
+      <c r="AN14" s="20"/>
+      <c r="AO14" s="20"/>
+      <c r="AP14" s="20"/>
+      <c r="AQ14" s="20"/>
+      <c r="AR14" s="20"/>
+      <c r="AS14" s="20"/>
+      <c r="AT14" s="20"/>
+      <c r="AU14" s="20"/>
+      <c r="AV14" s="20"/>
+      <c r="AW14" s="20"/>
+      <c r="AX14" s="20"/>
+      <c r="AY14" s="20"/>
+      <c r="AZ14" s="20"/>
+      <c r="BA14" s="20"/>
+      <c r="BB14" s="20"/>
+      <c r="BC14" s="21"/>
+    </row>
+    <row r="15" spans="1:55">
+      <c r="B15" s="39">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="C15" s="119" t="s">
+        <v>87</v>
+      </c>
+      <c r="D15" s="20"/>
+      <c r="E15" s="20"/>
+      <c r="F15" s="20"/>
+      <c r="G15" s="20"/>
+      <c r="H15" s="20"/>
+      <c r="I15" s="20"/>
+      <c r="J15" s="20"/>
+      <c r="K15" s="21"/>
+      <c r="L15" s="119" t="s">
+        <v>89</v>
+      </c>
+      <c r="M15" s="121"/>
+      <c r="N15" s="121"/>
+      <c r="O15" s="121"/>
+      <c r="P15" s="121"/>
+      <c r="Q15" s="121"/>
+      <c r="R15" s="121"/>
+      <c r="S15" s="121"/>
+      <c r="T15" s="122"/>
+      <c r="U15" s="119" t="s">
+        <v>82</v>
+      </c>
+      <c r="V15" s="121"/>
+      <c r="W15" s="121"/>
+      <c r="X15" s="121"/>
+      <c r="Y15" s="121"/>
+      <c r="Z15" s="122"/>
+      <c r="AA15" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB15" s="124"/>
+      <c r="AC15" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD15" s="124"/>
+      <c r="AE15" s="123" t="s">
+        <v>68</v>
+      </c>
+      <c r="AF15" s="124"/>
+      <c r="AG15" s="19"/>
+      <c r="AH15" s="20"/>
+      <c r="AI15" s="20"/>
+      <c r="AJ15" s="20"/>
+      <c r="AK15" s="21"/>
+      <c r="AL15" s="120" t="s">
+        <v>88</v>
+      </c>
+      <c r="AM15" s="20"/>
+      <c r="AN15" s="20"/>
+      <c r="AO15" s="20"/>
+      <c r="AP15" s="20"/>
+      <c r="AQ15" s="20"/>
+      <c r="AR15" s="20"/>
+      <c r="AS15" s="20"/>
+      <c r="AT15" s="20"/>
+      <c r="AU15" s="20"/>
+      <c r="AV15" s="20"/>
+      <c r="AW15" s="20"/>
+      <c r="AX15" s="20"/>
+      <c r="AY15" s="20"/>
+      <c r="AZ15" s="20"/>
+      <c r="BA15" s="20"/>
+      <c r="BB15" s="20"/>
+      <c r="BC15" s="21"/>
+    </row>
+    <row r="16" spans="1:55">
+      <c r="B16" s="39">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="C16" s="119" t="s">
+        <v>90</v>
+      </c>
+      <c r="D16" s="20"/>
+      <c r="E16" s="20"/>
+      <c r="F16" s="20"/>
+      <c r="G16" s="20"/>
+      <c r="H16" s="20"/>
+      <c r="I16" s="20"/>
+      <c r="J16" s="20"/>
+      <c r="K16" s="21"/>
+      <c r="L16" s="120" t="s">
+        <v>91</v>
+      </c>
+      <c r="M16" s="121"/>
+      <c r="N16" s="121"/>
+      <c r="O16" s="121"/>
+      <c r="P16" s="121"/>
+      <c r="Q16" s="121"/>
+      <c r="R16" s="121"/>
+      <c r="S16" s="121"/>
+      <c r="T16" s="122"/>
+      <c r="U16" s="120" t="s">
+        <v>81</v>
+      </c>
+      <c r="V16" s="121"/>
+      <c r="W16" s="121"/>
+      <c r="X16" s="121"/>
+      <c r="Y16" s="121"/>
+      <c r="Z16" s="122"/>
+      <c r="AA16" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB16" s="124"/>
+      <c r="AC16" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD16" s="124"/>
+      <c r="AE16" s="123" t="s">
+        <v>68</v>
+      </c>
+      <c r="AF16" s="124"/>
+      <c r="AG16" s="120"/>
+      <c r="AH16" s="121"/>
+      <c r="AI16" s="121"/>
+      <c r="AJ16" s="121"/>
+      <c r="AK16" s="122"/>
+      <c r="AL16" s="120" t="s">
+        <v>92</v>
+      </c>
+      <c r="AM16" s="20"/>
+      <c r="AN16" s="20"/>
+      <c r="AO16" s="20"/>
+      <c r="AP16" s="20"/>
+      <c r="AQ16" s="20"/>
+      <c r="AR16" s="20"/>
+      <c r="AS16" s="20"/>
+      <c r="AT16" s="20"/>
+      <c r="AU16" s="20"/>
+      <c r="AV16" s="20"/>
+      <c r="AW16" s="20"/>
+      <c r="AX16" s="20"/>
+      <c r="AY16" s="20"/>
+      <c r="AZ16" s="20"/>
+      <c r="BA16" s="20"/>
+      <c r="BB16" s="20"/>
+      <c r="BC16" s="21"/>
+    </row>
+    <row r="17" spans="1:55">
+      <c r="B17" s="39">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="C17" s="119" t="s">
+        <v>93</v>
+      </c>
+      <c r="D17" s="119"/>
+      <c r="E17" s="20"/>
+      <c r="F17" s="20"/>
+      <c r="G17" s="20"/>
+      <c r="H17" s="20"/>
+      <c r="I17" s="20"/>
+      <c r="J17" s="20"/>
+      <c r="K17" s="21"/>
+      <c r="L17" s="119" t="s">
+        <v>97</v>
+      </c>
+      <c r="M17" s="20"/>
+      <c r="N17" s="20"/>
+      <c r="O17" s="20"/>
+      <c r="P17" s="20"/>
+      <c r="Q17" s="20"/>
+      <c r="R17" s="20"/>
+      <c r="S17" s="20"/>
+      <c r="T17" s="21"/>
+      <c r="U17" s="119" t="s">
+        <v>101</v>
+      </c>
+      <c r="V17" s="121"/>
+      <c r="W17" s="121"/>
+      <c r="X17" s="121"/>
+      <c r="Y17" s="121"/>
+      <c r="Z17" s="122"/>
+      <c r="AA17" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB17" s="124"/>
+      <c r="AC17" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD17" s="124"/>
+      <c r="AE17" s="123" t="s">
+        <v>68</v>
+      </c>
+      <c r="AF17" s="124"/>
+      <c r="AG17" s="19"/>
+      <c r="AH17" s="20"/>
+      <c r="AI17" s="20"/>
+      <c r="AJ17" s="20"/>
+      <c r="AK17" s="21"/>
+      <c r="AL17" s="42"/>
+      <c r="AM17" s="20"/>
+      <c r="AN17" s="20"/>
+      <c r="AO17" s="20"/>
+      <c r="AP17" s="20"/>
+      <c r="AQ17" s="20"/>
+      <c r="AR17" s="20"/>
+      <c r="AS17" s="20"/>
+      <c r="AT17" s="20"/>
+      <c r="AU17" s="20"/>
+      <c r="AV17" s="20"/>
+      <c r="AW17" s="20"/>
+      <c r="AX17" s="20"/>
+      <c r="AY17" s="20"/>
+      <c r="AZ17" s="20"/>
+      <c r="BA17" s="20"/>
+      <c r="BB17" s="20"/>
+      <c r="BC17" s="21"/>
+    </row>
+    <row r="18" spans="1:55">
+      <c r="B18" s="39">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="C18" s="119" t="s">
+        <v>94</v>
+      </c>
+      <c r="D18" s="119"/>
+      <c r="E18" s="20"/>
+      <c r="F18" s="20"/>
+      <c r="G18" s="20"/>
+      <c r="H18" s="20"/>
+      <c r="I18" s="20"/>
+      <c r="J18" s="20"/>
+      <c r="K18" s="21"/>
+      <c r="L18" s="120" t="s">
+        <v>98</v>
+      </c>
+      <c r="M18" s="20"/>
+      <c r="N18" s="20"/>
+      <c r="O18" s="20"/>
+      <c r="P18" s="20"/>
+      <c r="Q18" s="20"/>
+      <c r="R18" s="20"/>
+      <c r="S18" s="20"/>
+      <c r="T18" s="21"/>
+      <c r="U18" s="119" t="s">
+        <v>82</v>
+      </c>
+      <c r="V18" s="121"/>
+      <c r="W18" s="121"/>
+      <c r="X18" s="121"/>
+      <c r="Y18" s="121"/>
+      <c r="Z18" s="122"/>
+      <c r="AA18" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB18" s="124"/>
+      <c r="AC18" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD18" s="124"/>
+      <c r="AE18" s="123" t="s">
+        <v>68</v>
+      </c>
+      <c r="AF18" s="124"/>
+      <c r="AG18" s="19"/>
+      <c r="AH18" s="20"/>
+      <c r="AI18" s="20"/>
+      <c r="AJ18" s="20"/>
+      <c r="AK18" s="21"/>
+      <c r="AL18" s="42"/>
+      <c r="AM18" s="20"/>
+      <c r="AN18" s="20"/>
+      <c r="AO18" s="20"/>
+      <c r="AP18" s="20"/>
+      <c r="AQ18" s="20"/>
+      <c r="AR18" s="20"/>
+      <c r="AS18" s="20"/>
+      <c r="AT18" s="20"/>
+      <c r="AU18" s="20"/>
+      <c r="AV18" s="20"/>
+      <c r="AW18" s="20"/>
+      <c r="AX18" s="20"/>
+      <c r="AY18" s="20"/>
+      <c r="AZ18" s="20"/>
+      <c r="BA18" s="20"/>
+      <c r="BB18" s="20"/>
+      <c r="BC18" s="21"/>
+    </row>
+    <row r="19" spans="1:55">
+      <c r="B19" s="39">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="C19" s="119" t="s">
+        <v>95</v>
+      </c>
+      <c r="D19" s="119"/>
+      <c r="E19" s="20"/>
+      <c r="F19" s="20"/>
+      <c r="G19" s="20"/>
+      <c r="H19" s="20"/>
+      <c r="I19" s="20"/>
+      <c r="J19" s="20"/>
+      <c r="K19" s="21"/>
+      <c r="L19" s="120" t="s">
+        <v>99</v>
+      </c>
+      <c r="M19" s="20"/>
+      <c r="N19" s="20"/>
+      <c r="O19" s="20"/>
+      <c r="P19" s="20"/>
+      <c r="Q19" s="20"/>
+      <c r="R19" s="20"/>
+      <c r="S19" s="20"/>
+      <c r="T19" s="21"/>
+      <c r="U19" s="119" t="s">
+        <v>101</v>
+      </c>
+      <c r="V19" s="121"/>
+      <c r="W19" s="121"/>
+      <c r="X19" s="121"/>
+      <c r="Y19" s="121"/>
+      <c r="Z19" s="122"/>
+      <c r="AA19" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB19" s="124"/>
+      <c r="AC19" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD19" s="124"/>
+      <c r="AE19" s="123" t="s">
+        <v>68</v>
+      </c>
+      <c r="AF19" s="124"/>
+      <c r="AG19" s="19"/>
+      <c r="AH19" s="20"/>
+      <c r="AI19" s="20"/>
+      <c r="AJ19" s="20"/>
+      <c r="AK19" s="21"/>
+      <c r="AL19" s="42"/>
+      <c r="AM19" s="20"/>
+      <c r="AN19" s="20"/>
+      <c r="AO19" s="20"/>
+      <c r="AP19" s="20"/>
+      <c r="AQ19" s="20"/>
+      <c r="AR19" s="20"/>
+      <c r="AS19" s="20"/>
+      <c r="AT19" s="20"/>
+      <c r="AU19" s="20"/>
+      <c r="AV19" s="20"/>
+      <c r="AW19" s="20"/>
+      <c r="AX19" s="20"/>
+      <c r="AY19" s="20"/>
+      <c r="AZ19" s="20"/>
+      <c r="BA19" s="20"/>
+      <c r="BB19" s="20"/>
+      <c r="BC19" s="21"/>
+    </row>
+    <row r="20" spans="1:55">
+      <c r="B20" s="39">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="C20" s="119" t="s">
+        <v>96</v>
+      </c>
+      <c r="D20" s="119"/>
+      <c r="E20" s="20"/>
+      <c r="F20" s="20"/>
+      <c r="G20" s="20"/>
+      <c r="H20" s="20"/>
+      <c r="I20" s="20"/>
+      <c r="J20" s="20"/>
+      <c r="K20" s="21"/>
+      <c r="L20" s="120" t="s">
+        <v>100</v>
+      </c>
+      <c r="M20" s="20"/>
+      <c r="N20" s="20"/>
+      <c r="O20" s="20"/>
+      <c r="P20" s="20"/>
+      <c r="Q20" s="20"/>
+      <c r="R20" s="20"/>
+      <c r="S20" s="20"/>
+      <c r="T20" s="21"/>
+      <c r="U20" s="119" t="s">
+        <v>82</v>
+      </c>
+      <c r="V20" s="121"/>
+      <c r="W20" s="121"/>
+      <c r="X20" s="121"/>
+      <c r="Y20" s="121"/>
+      <c r="Z20" s="122"/>
+      <c r="AA20" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB20" s="124"/>
+      <c r="AC20" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD20" s="124"/>
+      <c r="AE20" s="123" t="s">
+        <v>68</v>
+      </c>
+      <c r="AF20" s="124"/>
       <c r="AG20" s="19"/>
       <c r="AH20" s="20"/>
       <c r="AI20" s="20"/>
@@ -5769,12 +12987,12 @@
       <c r="X21" s="20"/>
       <c r="Y21" s="20"/>
       <c r="Z21" s="21"/>
-      <c r="AA21" s="111"/>
-      <c r="AB21" s="112"/>
-      <c r="AC21" s="111"/>
-      <c r="AD21" s="112"/>
-      <c r="AE21" s="111"/>
-      <c r="AF21" s="112"/>
+      <c r="AA21" s="113"/>
+      <c r="AB21" s="114"/>
+      <c r="AC21" s="113"/>
+      <c r="AD21" s="114"/>
+      <c r="AE21" s="113"/>
+      <c r="AF21" s="114"/>
       <c r="AG21" s="19"/>
       <c r="AH21" s="20"/>
       <c r="AI21" s="20"/>
@@ -5828,12 +13046,12 @@
       <c r="X22" s="20"/>
       <c r="Y22" s="20"/>
       <c r="Z22" s="21"/>
-      <c r="AA22" s="111"/>
-      <c r="AB22" s="112"/>
-      <c r="AC22" s="111"/>
-      <c r="AD22" s="112"/>
-      <c r="AE22" s="111"/>
-      <c r="AF22" s="112"/>
+      <c r="AA22" s="113"/>
+      <c r="AB22" s="114"/>
+      <c r="AC22" s="113"/>
+      <c r="AD22" s="114"/>
+      <c r="AE22" s="113"/>
+      <c r="AF22" s="114"/>
       <c r="AG22" s="19"/>
       <c r="AH22" s="20"/>
       <c r="AI22" s="20"/>
@@ -5887,12 +13105,12 @@
       <c r="X23" s="20"/>
       <c r="Y23" s="20"/>
       <c r="Z23" s="21"/>
-      <c r="AA23" s="111"/>
-      <c r="AB23" s="112"/>
-      <c r="AC23" s="111"/>
-      <c r="AD23" s="112"/>
-      <c r="AE23" s="111"/>
-      <c r="AF23" s="112"/>
+      <c r="AA23" s="113"/>
+      <c r="AB23" s="114"/>
+      <c r="AC23" s="113"/>
+      <c r="AD23" s="114"/>
+      <c r="AE23" s="113"/>
+      <c r="AF23" s="114"/>
       <c r="AG23" s="19"/>
       <c r="AH23" s="20"/>
       <c r="AI23" s="20"/>
@@ -5946,12 +13164,12 @@
       <c r="X24" s="20"/>
       <c r="Y24" s="20"/>
       <c r="Z24" s="21"/>
-      <c r="AA24" s="111"/>
-      <c r="AB24" s="112"/>
-      <c r="AC24" s="111"/>
-      <c r="AD24" s="112"/>
-      <c r="AE24" s="111"/>
-      <c r="AF24" s="112"/>
+      <c r="AA24" s="113"/>
+      <c r="AB24" s="114"/>
+      <c r="AC24" s="113"/>
+      <c r="AD24" s="114"/>
+      <c r="AE24" s="113"/>
+      <c r="AF24" s="114"/>
       <c r="AG24" s="19"/>
       <c r="AH24" s="20"/>
       <c r="AI24" s="20"/>
@@ -6005,12 +13223,12 @@
       <c r="X25" s="20"/>
       <c r="Y25" s="20"/>
       <c r="Z25" s="21"/>
-      <c r="AA25" s="111"/>
-      <c r="AB25" s="112"/>
-      <c r="AC25" s="111"/>
-      <c r="AD25" s="112"/>
-      <c r="AE25" s="111"/>
-      <c r="AF25" s="112"/>
+      <c r="AA25" s="113"/>
+      <c r="AB25" s="114"/>
+      <c r="AC25" s="113"/>
+      <c r="AD25" s="114"/>
+      <c r="AE25" s="113"/>
+      <c r="AF25" s="114"/>
       <c r="AG25" s="19"/>
       <c r="AH25" s="20"/>
       <c r="AI25" s="20"/>
@@ -6091,10 +13309,10 @@
     </row>
     <row r="29" spans="1:55">
       <c r="B29" s="39" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C29" s="19" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D29" s="20"/>
       <c r="E29" s="20"/>
@@ -6105,7 +13323,7 @@
       <c r="J29" s="20"/>
       <c r="K29" s="21"/>
       <c r="L29" s="19" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="M29" s="20"/>
       <c r="N29" s="20"/>
@@ -6116,7 +13334,7 @@
       <c r="S29" s="20"/>
       <c r="T29" s="21"/>
       <c r="U29" s="19" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="V29" s="20"/>
       <c r="W29" s="20"/>
@@ -6127,7 +13345,7 @@
       <c r="AB29" s="20"/>
       <c r="AC29" s="21"/>
       <c r="AD29" s="19" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AE29" s="20"/>
       <c r="AF29" s="20"/>
@@ -6138,41 +13356,65 @@
       <c r="AK29" s="20"/>
       <c r="AL29" s="21"/>
     </row>
+    <row r="33" spans="5:5" ht="19">
+      <c r="E33" s="117"/>
+    </row>
+    <row r="34" spans="5:5" ht="20">
+      <c r="E34" s="41"/>
+    </row>
+    <row r="35" spans="5:5" ht="20">
+      <c r="E35" s="41"/>
+    </row>
+    <row r="36" spans="5:5" ht="19">
+      <c r="E36" s="117"/>
+    </row>
+    <row r="37" spans="5:5" ht="20">
+      <c r="E37" s="41"/>
+    </row>
+    <row r="38" spans="5:5" ht="20">
+      <c r="E38" s="41"/>
+    </row>
+    <row r="39" spans="5:5" ht="19">
+      <c r="E39" s="117"/>
+    </row>
+    <row r="40" spans="5:5" ht="20">
+      <c r="E40" s="41"/>
+    </row>
   </sheetData>
   <mergeCells count="54">
-    <mergeCell ref="AA20:AB20"/>
-    <mergeCell ref="AC20:AD20"/>
-    <mergeCell ref="AE20:AF20"/>
-    <mergeCell ref="AA21:AB21"/>
-    <mergeCell ref="AC21:AD21"/>
-    <mergeCell ref="AE21:AF21"/>
     <mergeCell ref="AA25:AB25"/>
     <mergeCell ref="AC25:AD25"/>
     <mergeCell ref="AE25:AF25"/>
-    <mergeCell ref="AA22:AB22"/>
-    <mergeCell ref="AC22:AD22"/>
-    <mergeCell ref="AE22:AF22"/>
     <mergeCell ref="AA23:AB23"/>
     <mergeCell ref="AC23:AD23"/>
     <mergeCell ref="AE23:AF23"/>
     <mergeCell ref="AA24:AB24"/>
     <mergeCell ref="AC24:AD24"/>
     <mergeCell ref="AE24:AF24"/>
+    <mergeCell ref="AA21:AB21"/>
+    <mergeCell ref="AC21:AD21"/>
+    <mergeCell ref="AE21:AF21"/>
+    <mergeCell ref="AA22:AB22"/>
+    <mergeCell ref="AC22:AD22"/>
+    <mergeCell ref="AE22:AF22"/>
+    <mergeCell ref="AA19:AB19"/>
     <mergeCell ref="AC19:AD19"/>
     <mergeCell ref="AE19:AF19"/>
+    <mergeCell ref="AA20:AB20"/>
+    <mergeCell ref="AC20:AD20"/>
+    <mergeCell ref="AE20:AF20"/>
+    <mergeCell ref="AA17:AB17"/>
+    <mergeCell ref="AC17:AD17"/>
+    <mergeCell ref="AE17:AF17"/>
+    <mergeCell ref="AA18:AB18"/>
+    <mergeCell ref="AC18:AD18"/>
+    <mergeCell ref="AE18:AF18"/>
     <mergeCell ref="AA15:AB15"/>
     <mergeCell ref="AC15:AD15"/>
     <mergeCell ref="AE15:AF15"/>
     <mergeCell ref="AA16:AB16"/>
     <mergeCell ref="AC16:AD16"/>
     <mergeCell ref="AE16:AF16"/>
-    <mergeCell ref="AA17:AB17"/>
-    <mergeCell ref="AC17:AD17"/>
-    <mergeCell ref="AE17:AF17"/>
-    <mergeCell ref="AA18:AB18"/>
-    <mergeCell ref="AC18:AD18"/>
-    <mergeCell ref="AE18:AF18"/>
-    <mergeCell ref="AA19:AB19"/>
     <mergeCell ref="AE12:AF12"/>
     <mergeCell ref="AA13:AB13"/>
     <mergeCell ref="AC13:AD13"/>
@@ -6180,12 +13422,12 @@
     <mergeCell ref="AA14:AB14"/>
     <mergeCell ref="AC14:AD14"/>
     <mergeCell ref="AE14:AF14"/>
-    <mergeCell ref="AC12:AD12"/>
     <mergeCell ref="B4:G4"/>
     <mergeCell ref="B5:G5"/>
     <mergeCell ref="B6:G8"/>
     <mergeCell ref="H6:Y8"/>
     <mergeCell ref="AA12:AB12"/>
+    <mergeCell ref="AC12:AD12"/>
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="H2:M2"/>
     <mergeCell ref="N2:S2"/>
@@ -6197,7 +13439,7 @@
   </mergeCells>
   <phoneticPr fontId="1"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AE20:AF25 AE12:AF16 AA12:AD25" xr:uid="{185F62DD-DD48-0446-94A1-F28EB9AD87E2}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AA12:AF25" xr:uid="{48085B70-8294-6B4E-AF7E-22235E6EC5DE}">
       <formula1>"-,○"</formula1>
     </dataValidation>
   </dataValidations>
@@ -6205,7 +13447,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1D040FF-B059-154F-810C-B5876E7214BF}">
   <dimension ref="A1:BC28"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="4.33203125" defaultRowHeight="18"/>
@@ -6219,122 +13461,122 @@
       </c>
     </row>
     <row r="2" spans="1:55">
-      <c r="B2" s="76" t="s">
+      <c r="B2" s="78" t="s">
         <v>27</v>
       </c>
-      <c r="C2" s="83" t="s">
+      <c r="C2" s="85" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="83" t="s">
+      <c r="D2" s="85" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="83" t="s">
+      <c r="E2" s="85" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="83" t="s">
+      <c r="F2" s="85" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="77" t="s">
+      <c r="G2" s="79" t="s">
         <v>15</v>
       </c>
-      <c r="H2" s="89"/>
-      <c r="I2" s="87"/>
-      <c r="J2" s="87"/>
-      <c r="K2" s="87"/>
-      <c r="L2" s="87"/>
-      <c r="M2" s="88"/>
-      <c r="N2" s="76" t="s">
+      <c r="H2" s="91"/>
+      <c r="I2" s="89"/>
+      <c r="J2" s="89"/>
+      <c r="K2" s="89"/>
+      <c r="L2" s="89"/>
+      <c r="M2" s="90"/>
+      <c r="N2" s="78" t="s">
         <v>26</v>
       </c>
-      <c r="O2" s="83" t="s">
+      <c r="O2" s="85" t="s">
         <v>15</v>
       </c>
-      <c r="P2" s="83" t="s">
+      <c r="P2" s="85" t="s">
         <v>15</v>
       </c>
-      <c r="Q2" s="83" t="s">
+      <c r="Q2" s="85" t="s">
         <v>15</v>
       </c>
-      <c r="R2" s="83" t="s">
+      <c r="R2" s="85" t="s">
         <v>15</v>
       </c>
-      <c r="S2" s="77" t="s">
+      <c r="S2" s="79" t="s">
         <v>15</v>
       </c>
-      <c r="T2" s="89"/>
-      <c r="U2" s="87"/>
-      <c r="V2" s="87"/>
-      <c r="W2" s="87"/>
-      <c r="X2" s="87"/>
-      <c r="Y2" s="88"/>
+      <c r="T2" s="91"/>
+      <c r="U2" s="89"/>
+      <c r="V2" s="89"/>
+      <c r="W2" s="89"/>
+      <c r="X2" s="89"/>
+      <c r="Y2" s="90"/>
     </row>
     <row r="3" spans="1:55">
-      <c r="B3" s="84" t="s">
+      <c r="B3" s="86" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="85" t="s">
+      <c r="C3" s="87" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="85" t="s">
+      <c r="D3" s="87" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="85" t="s">
+      <c r="E3" s="87" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="85" t="s">
+      <c r="F3" s="87" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="85" t="s">
+      <c r="G3" s="87" t="s">
         <v>16</v>
       </c>
-      <c r="H3" s="90"/>
-      <c r="I3" s="91"/>
-      <c r="J3" s="91"/>
-      <c r="K3" s="91"/>
-      <c r="L3" s="91"/>
-      <c r="M3" s="91"/>
-      <c r="N3" s="84" t="s">
+      <c r="H3" s="92"/>
+      <c r="I3" s="93"/>
+      <c r="J3" s="93"/>
+      <c r="K3" s="93"/>
+      <c r="L3" s="93"/>
+      <c r="M3" s="93"/>
+      <c r="N3" s="86" t="s">
         <v>29</v>
       </c>
-      <c r="O3" s="85" t="s">
+      <c r="O3" s="87" t="s">
         <v>16</v>
       </c>
-      <c r="P3" s="85" t="s">
+      <c r="P3" s="87" t="s">
         <v>16</v>
       </c>
-      <c r="Q3" s="85" t="s">
+      <c r="Q3" s="87" t="s">
         <v>16</v>
       </c>
-      <c r="R3" s="85" t="s">
+      <c r="R3" s="87" t="s">
         <v>16</v>
       </c>
-      <c r="S3" s="85" t="s">
+      <c r="S3" s="87" t="s">
         <v>16</v>
       </c>
-      <c r="T3" s="90"/>
-      <c r="U3" s="91"/>
-      <c r="V3" s="91"/>
-      <c r="W3" s="91"/>
-      <c r="X3" s="91"/>
-      <c r="Y3" s="92"/>
+      <c r="T3" s="92"/>
+      <c r="U3" s="93"/>
+      <c r="V3" s="93"/>
+      <c r="W3" s="93"/>
+      <c r="X3" s="93"/>
+      <c r="Y3" s="94"/>
     </row>
     <row r="4" spans="1:55">
-      <c r="B4" s="93" t="s">
+      <c r="B4" s="95" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="94" t="s">
+      <c r="C4" s="96" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="94" t="s">
+      <c r="D4" s="96" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="94" t="s">
+      <c r="E4" s="96" t="s">
         <v>15</v>
       </c>
-      <c r="F4" s="94" t="s">
+      <c r="F4" s="96" t="s">
         <v>15</v>
       </c>
-      <c r="G4" s="95" t="s">
+      <c r="G4" s="97" t="s">
         <v>15</v>
       </c>
       <c r="H4" s="19"/>
@@ -6357,22 +13599,22 @@
       <c r="Y4" s="21"/>
     </row>
     <row r="5" spans="1:55">
-      <c r="B5" s="84" t="s">
+      <c r="B5" s="86" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="85" t="s">
+      <c r="C5" s="87" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="85" t="s">
+      <c r="D5" s="87" t="s">
         <v>16</v>
       </c>
-      <c r="E5" s="85" t="s">
+      <c r="E5" s="87" t="s">
         <v>16</v>
       </c>
-      <c r="F5" s="85" t="s">
+      <c r="F5" s="87" t="s">
         <v>16</v>
       </c>
-      <c r="G5" s="85" t="s">
+      <c r="G5" s="87" t="s">
         <v>16</v>
       </c>
       <c r="H5" s="22"/>
@@ -6395,84 +13637,84 @@
       <c r="Y5" s="24"/>
     </row>
     <row r="6" spans="1:55">
-      <c r="B6" s="76" t="s">
+      <c r="B6" s="78" t="s">
         <v>30</v>
       </c>
-      <c r="C6" s="83"/>
-      <c r="D6" s="83"/>
-      <c r="E6" s="83"/>
-      <c r="F6" s="83"/>
-      <c r="G6" s="77"/>
-      <c r="H6" s="102"/>
-      <c r="I6" s="103"/>
-      <c r="J6" s="103"/>
-      <c r="K6" s="103"/>
-      <c r="L6" s="103"/>
-      <c r="M6" s="103"/>
-      <c r="N6" s="103"/>
-      <c r="O6" s="103"/>
-      <c r="P6" s="103"/>
-      <c r="Q6" s="103"/>
-      <c r="R6" s="103"/>
-      <c r="S6" s="103"/>
-      <c r="T6" s="103"/>
-      <c r="U6" s="103"/>
-      <c r="V6" s="103"/>
-      <c r="W6" s="103"/>
-      <c r="X6" s="103"/>
-      <c r="Y6" s="104"/>
+      <c r="C6" s="85"/>
+      <c r="D6" s="85"/>
+      <c r="E6" s="85"/>
+      <c r="F6" s="85"/>
+      <c r="G6" s="79"/>
+      <c r="H6" s="104"/>
+      <c r="I6" s="105"/>
+      <c r="J6" s="105"/>
+      <c r="K6" s="105"/>
+      <c r="L6" s="105"/>
+      <c r="M6" s="105"/>
+      <c r="N6" s="105"/>
+      <c r="O6" s="105"/>
+      <c r="P6" s="105"/>
+      <c r="Q6" s="105"/>
+      <c r="R6" s="105"/>
+      <c r="S6" s="105"/>
+      <c r="T6" s="105"/>
+      <c r="U6" s="105"/>
+      <c r="V6" s="105"/>
+      <c r="W6" s="105"/>
+      <c r="X6" s="105"/>
+      <c r="Y6" s="106"/>
     </row>
     <row r="7" spans="1:55">
-      <c r="B7" s="96"/>
-      <c r="C7" s="97"/>
-      <c r="D7" s="97"/>
-      <c r="E7" s="97"/>
-      <c r="F7" s="97"/>
-      <c r="G7" s="98"/>
-      <c r="H7" s="105"/>
-      <c r="I7" s="106"/>
-      <c r="J7" s="106"/>
-      <c r="K7" s="106"/>
-      <c r="L7" s="106"/>
-      <c r="M7" s="106"/>
-      <c r="N7" s="106"/>
-      <c r="O7" s="106"/>
-      <c r="P7" s="106"/>
-      <c r="Q7" s="106"/>
-      <c r="R7" s="106"/>
-      <c r="S7" s="106"/>
-      <c r="T7" s="106"/>
-      <c r="U7" s="106"/>
-      <c r="V7" s="106"/>
-      <c r="W7" s="106"/>
-      <c r="X7" s="106"/>
-      <c r="Y7" s="107"/>
+      <c r="B7" s="98"/>
+      <c r="C7" s="99"/>
+      <c r="D7" s="99"/>
+      <c r="E7" s="99"/>
+      <c r="F7" s="99"/>
+      <c r="G7" s="100"/>
+      <c r="H7" s="107"/>
+      <c r="I7" s="108"/>
+      <c r="J7" s="108"/>
+      <c r="K7" s="108"/>
+      <c r="L7" s="108"/>
+      <c r="M7" s="108"/>
+      <c r="N7" s="108"/>
+      <c r="O7" s="108"/>
+      <c r="P7" s="108"/>
+      <c r="Q7" s="108"/>
+      <c r="R7" s="108"/>
+      <c r="S7" s="108"/>
+      <c r="T7" s="108"/>
+      <c r="U7" s="108"/>
+      <c r="V7" s="108"/>
+      <c r="W7" s="108"/>
+      <c r="X7" s="108"/>
+      <c r="Y7" s="109"/>
     </row>
     <row r="8" spans="1:55">
-      <c r="B8" s="99"/>
-      <c r="C8" s="100"/>
-      <c r="D8" s="100"/>
-      <c r="E8" s="100"/>
-      <c r="F8" s="100"/>
-      <c r="G8" s="101"/>
-      <c r="H8" s="108"/>
-      <c r="I8" s="109"/>
-      <c r="J8" s="109"/>
-      <c r="K8" s="109"/>
-      <c r="L8" s="109"/>
-      <c r="M8" s="109"/>
-      <c r="N8" s="109"/>
-      <c r="O8" s="109"/>
-      <c r="P8" s="109"/>
-      <c r="Q8" s="109"/>
-      <c r="R8" s="109"/>
-      <c r="S8" s="109"/>
-      <c r="T8" s="109"/>
-      <c r="U8" s="109"/>
-      <c r="V8" s="109"/>
-      <c r="W8" s="109"/>
-      <c r="X8" s="109"/>
-      <c r="Y8" s="110"/>
+      <c r="B8" s="101"/>
+      <c r="C8" s="102"/>
+      <c r="D8" s="102"/>
+      <c r="E8" s="102"/>
+      <c r="F8" s="102"/>
+      <c r="G8" s="103"/>
+      <c r="H8" s="110"/>
+      <c r="I8" s="111"/>
+      <c r="J8" s="111"/>
+      <c r="K8" s="111"/>
+      <c r="L8" s="111"/>
+      <c r="M8" s="111"/>
+      <c r="N8" s="111"/>
+      <c r="O8" s="111"/>
+      <c r="P8" s="111"/>
+      <c r="Q8" s="111"/>
+      <c r="R8" s="111"/>
+      <c r="S8" s="111"/>
+      <c r="T8" s="111"/>
+      <c r="U8" s="111"/>
+      <c r="V8" s="111"/>
+      <c r="W8" s="111"/>
+      <c r="X8" s="111"/>
+      <c r="Y8" s="112"/>
     </row>
     <row r="10" spans="1:55" ht="20">
       <c r="A10" s="41" t="s">
@@ -6579,12 +13821,12 @@
       <c r="X12" s="20"/>
       <c r="Y12" s="20"/>
       <c r="Z12" s="21"/>
-      <c r="AA12" s="111"/>
-      <c r="AB12" s="112"/>
-      <c r="AC12" s="111"/>
-      <c r="AD12" s="112"/>
-      <c r="AE12" s="111"/>
-      <c r="AF12" s="112"/>
+      <c r="AA12" s="113"/>
+      <c r="AB12" s="114"/>
+      <c r="AC12" s="113"/>
+      <c r="AD12" s="114"/>
+      <c r="AE12" s="113"/>
+      <c r="AF12" s="114"/>
       <c r="AG12" s="19"/>
       <c r="AH12" s="20"/>
       <c r="AI12" s="20"/>
@@ -6635,12 +13877,12 @@
       <c r="X13" s="20"/>
       <c r="Y13" s="20"/>
       <c r="Z13" s="21"/>
-      <c r="AA13" s="111"/>
-      <c r="AB13" s="112"/>
-      <c r="AC13" s="111"/>
-      <c r="AD13" s="112"/>
-      <c r="AE13" s="111"/>
-      <c r="AF13" s="112"/>
+      <c r="AA13" s="113"/>
+      <c r="AB13" s="114"/>
+      <c r="AC13" s="113"/>
+      <c r="AD13" s="114"/>
+      <c r="AE13" s="113"/>
+      <c r="AF13" s="114"/>
       <c r="AG13" s="19"/>
       <c r="AH13" s="20"/>
       <c r="AI13" s="20"/>
@@ -6691,12 +13933,12 @@
       <c r="X14" s="20"/>
       <c r="Y14" s="20"/>
       <c r="Z14" s="21"/>
-      <c r="AA14" s="111"/>
-      <c r="AB14" s="112"/>
-      <c r="AC14" s="111"/>
-      <c r="AD14" s="112"/>
-      <c r="AE14" s="111"/>
-      <c r="AF14" s="112"/>
+      <c r="AA14" s="113"/>
+      <c r="AB14" s="114"/>
+      <c r="AC14" s="113"/>
+      <c r="AD14" s="114"/>
+      <c r="AE14" s="113"/>
+      <c r="AF14" s="114"/>
       <c r="AG14" s="19"/>
       <c r="AH14" s="20"/>
       <c r="AI14" s="20"/>
@@ -6747,12 +13989,12 @@
       <c r="X15" s="20"/>
       <c r="Y15" s="20"/>
       <c r="Z15" s="21"/>
-      <c r="AA15" s="111"/>
-      <c r="AB15" s="112"/>
-      <c r="AC15" s="111"/>
-      <c r="AD15" s="112"/>
-      <c r="AE15" s="111"/>
-      <c r="AF15" s="112"/>
+      <c r="AA15" s="113"/>
+      <c r="AB15" s="114"/>
+      <c r="AC15" s="113"/>
+      <c r="AD15" s="114"/>
+      <c r="AE15" s="113"/>
+      <c r="AF15" s="114"/>
       <c r="AG15" s="19"/>
       <c r="AH15" s="20"/>
       <c r="AI15" s="20"/>
@@ -6803,12 +14045,12 @@
       <c r="X16" s="20"/>
       <c r="Y16" s="20"/>
       <c r="Z16" s="21"/>
-      <c r="AA16" s="111"/>
-      <c r="AB16" s="112"/>
-      <c r="AC16" s="111"/>
-      <c r="AD16" s="112"/>
-      <c r="AE16" s="111"/>
-      <c r="AF16" s="112"/>
+      <c r="AA16" s="113"/>
+      <c r="AB16" s="114"/>
+      <c r="AC16" s="113"/>
+      <c r="AD16" s="114"/>
+      <c r="AE16" s="113"/>
+      <c r="AF16" s="114"/>
       <c r="AG16" s="19"/>
       <c r="AH16" s="20"/>
       <c r="AI16" s="20"/>
@@ -6859,12 +14101,12 @@
       <c r="X17" s="20"/>
       <c r="Y17" s="20"/>
       <c r="Z17" s="21"/>
-      <c r="AA17" s="111"/>
-      <c r="AB17" s="112"/>
-      <c r="AC17" s="111"/>
-      <c r="AD17" s="112"/>
-      <c r="AE17" s="111"/>
-      <c r="AF17" s="112"/>
+      <c r="AA17" s="113"/>
+      <c r="AB17" s="114"/>
+      <c r="AC17" s="113"/>
+      <c r="AD17" s="114"/>
+      <c r="AE17" s="113"/>
+      <c r="AF17" s="114"/>
       <c r="AG17" s="19"/>
       <c r="AH17" s="20"/>
       <c r="AI17" s="20"/>
@@ -6915,12 +14157,12 @@
       <c r="X18" s="20"/>
       <c r="Y18" s="20"/>
       <c r="Z18" s="21"/>
-      <c r="AA18" s="111"/>
-      <c r="AB18" s="112"/>
-      <c r="AC18" s="111"/>
-      <c r="AD18" s="112"/>
-      <c r="AE18" s="111"/>
-      <c r="AF18" s="112"/>
+      <c r="AA18" s="113"/>
+      <c r="AB18" s="114"/>
+      <c r="AC18" s="113"/>
+      <c r="AD18" s="114"/>
+      <c r="AE18" s="113"/>
+      <c r="AF18" s="114"/>
       <c r="AG18" s="19"/>
       <c r="AH18" s="20"/>
       <c r="AI18" s="20"/>
@@ -6971,12 +14213,12 @@
       <c r="X19" s="20"/>
       <c r="Y19" s="20"/>
       <c r="Z19" s="21"/>
-      <c r="AA19" s="111"/>
-      <c r="AB19" s="112"/>
-      <c r="AC19" s="111"/>
-      <c r="AD19" s="112"/>
-      <c r="AE19" s="111"/>
-      <c r="AF19" s="112"/>
+      <c r="AA19" s="113"/>
+      <c r="AB19" s="114"/>
+      <c r="AC19" s="113"/>
+      <c r="AD19" s="114"/>
+      <c r="AE19" s="113"/>
+      <c r="AF19" s="114"/>
       <c r="AG19" s="19"/>
       <c r="AH19" s="20"/>
       <c r="AI19" s="20"/>
@@ -7027,12 +14269,12 @@
       <c r="X20" s="20"/>
       <c r="Y20" s="20"/>
       <c r="Z20" s="21"/>
-      <c r="AA20" s="111"/>
-      <c r="AB20" s="112"/>
-      <c r="AC20" s="111"/>
-      <c r="AD20" s="112"/>
-      <c r="AE20" s="111"/>
-      <c r="AF20" s="112"/>
+      <c r="AA20" s="113"/>
+      <c r="AB20" s="114"/>
+      <c r="AC20" s="113"/>
+      <c r="AD20" s="114"/>
+      <c r="AE20" s="113"/>
+      <c r="AF20" s="114"/>
       <c r="AG20" s="19"/>
       <c r="AH20" s="20"/>
       <c r="AI20" s="20"/>
@@ -7083,12 +14325,12 @@
       <c r="X21" s="20"/>
       <c r="Y21" s="20"/>
       <c r="Z21" s="21"/>
-      <c r="AA21" s="111"/>
-      <c r="AB21" s="112"/>
-      <c r="AC21" s="111"/>
-      <c r="AD21" s="112"/>
-      <c r="AE21" s="111"/>
-      <c r="AF21" s="112"/>
+      <c r="AA21" s="113"/>
+      <c r="AB21" s="114"/>
+      <c r="AC21" s="113"/>
+      <c r="AD21" s="114"/>
+      <c r="AE21" s="113"/>
+      <c r="AF21" s="114"/>
       <c r="AG21" s="19"/>
       <c r="AH21" s="20"/>
       <c r="AI21" s="20"/>
@@ -7139,12 +14381,12 @@
       <c r="X22" s="20"/>
       <c r="Y22" s="20"/>
       <c r="Z22" s="21"/>
-      <c r="AA22" s="111"/>
-      <c r="AB22" s="112"/>
-      <c r="AC22" s="111"/>
-      <c r="AD22" s="112"/>
-      <c r="AE22" s="111"/>
-      <c r="AF22" s="112"/>
+      <c r="AA22" s="113"/>
+      <c r="AB22" s="114"/>
+      <c r="AC22" s="113"/>
+      <c r="AD22" s="114"/>
+      <c r="AE22" s="113"/>
+      <c r="AF22" s="114"/>
       <c r="AG22" s="19"/>
       <c r="AH22" s="20"/>
       <c r="AI22" s="20"/>
@@ -7195,12 +14437,12 @@
       <c r="X23" s="20"/>
       <c r="Y23" s="20"/>
       <c r="Z23" s="21"/>
-      <c r="AA23" s="111"/>
-      <c r="AB23" s="112"/>
-      <c r="AC23" s="111"/>
-      <c r="AD23" s="112"/>
-      <c r="AE23" s="111"/>
-      <c r="AF23" s="112"/>
+      <c r="AA23" s="113"/>
+      <c r="AB23" s="114"/>
+      <c r="AC23" s="113"/>
+      <c r="AD23" s="114"/>
+      <c r="AE23" s="113"/>
+      <c r="AF23" s="114"/>
       <c r="AG23" s="19"/>
       <c r="AH23" s="20"/>
       <c r="AI23" s="20"/>
@@ -7251,12 +14493,12 @@
       <c r="X24" s="20"/>
       <c r="Y24" s="20"/>
       <c r="Z24" s="21"/>
-      <c r="AA24" s="111"/>
-      <c r="AB24" s="112"/>
-      <c r="AC24" s="111"/>
-      <c r="AD24" s="112"/>
-      <c r="AE24" s="111"/>
-      <c r="AF24" s="112"/>
+      <c r="AA24" s="113"/>
+      <c r="AB24" s="114"/>
+      <c r="AC24" s="113"/>
+      <c r="AD24" s="114"/>
+      <c r="AE24" s="113"/>
+      <c r="AF24" s="114"/>
       <c r="AG24" s="19"/>
       <c r="AH24" s="20"/>
       <c r="AI24" s="20"/>
@@ -7337,10 +14579,10 @@
     </row>
     <row r="28" spans="1:55">
       <c r="B28" s="39" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C28" s="19" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D28" s="20"/>
       <c r="E28" s="20"/>
@@ -7351,7 +14593,7 @@
       <c r="J28" s="20"/>
       <c r="K28" s="21"/>
       <c r="L28" s="19" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="M28" s="20"/>
       <c r="N28" s="20"/>
@@ -7362,7 +14604,7 @@
       <c r="S28" s="20"/>
       <c r="T28" s="21"/>
       <c r="U28" s="19" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="V28" s="20"/>
       <c r="W28" s="20"/>
@@ -7373,7 +14615,7 @@
       <c r="AB28" s="20"/>
       <c r="AC28" s="21"/>
       <c r="AD28" s="19" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AE28" s="20"/>
       <c r="AF28" s="20"/>
